--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gersou\Downloads\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219C4A4F-9401-4FFE-8FFC-F544830EC1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3A9941-6A7B-49E9-B144-840724CCC9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36810" yWindow="4320" windowWidth="13830" windowHeight="7110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -469,8 +469,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -3669,6 +3672,210 @@
         <v>25</v>
       </c>
       <c r="V46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>168</v>
+      </c>
+      <c r="D47">
+        <v>169</v>
+      </c>
+      <c r="E47" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47">
+        <v>23150</v>
+      </c>
+      <c r="G47">
+        <v>38</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+      <c r="I47">
+        <v>5174</v>
+      </c>
+      <c r="J47">
+        <v>68</v>
+      </c>
+      <c r="K47">
+        <v>13</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>8</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>8.7962962962962962E-4</v>
+      </c>
+      <c r="P47" s="3">
+        <v>1.3425925925925925E-3</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="R47" s="4">
+        <v>0.19120000000000001</v>
+      </c>
+      <c r="S47" s="5">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>5</v>
+      </c>
+      <c r="U47" s="4">
+        <v>0.3846</v>
+      </c>
+      <c r="V47" s="4">
+        <v>0.83330000000000004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B48">
+        <v>9</v>
+      </c>
+      <c r="C48">
+        <v>168</v>
+      </c>
+      <c r="D48">
+        <v>169</v>
+      </c>
+      <c r="E48" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48">
+        <v>23150</v>
+      </c>
+      <c r="G48">
+        <v>38</v>
+      </c>
+      <c r="H48">
+        <v>3</v>
+      </c>
+      <c r="I48">
+        <v>22701</v>
+      </c>
+      <c r="J48">
+        <v>279</v>
+      </c>
+      <c r="K48">
+        <v>32</v>
+      </c>
+      <c r="L48">
+        <v>15</v>
+      </c>
+      <c r="M48">
+        <v>8</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+      <c r="O48" s="3">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="P48" s="3">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>1.23E-2</v>
+      </c>
+      <c r="R48" s="4">
+        <v>0.1147</v>
+      </c>
+      <c r="S48" s="4">
+        <v>0.46879999999999999</v>
+      </c>
+      <c r="T48">
+        <v>9</v>
+      </c>
+      <c r="U48" s="4">
+        <v>0.52939999999999998</v>
+      </c>
+      <c r="V48" s="4">
+        <v>1</v>
+      </c>
+      <c r="W48">
+        <v>0.16500000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B49">
+        <v>10</v>
+      </c>
+      <c r="C49">
+        <v>168</v>
+      </c>
+      <c r="D49">
+        <v>169</v>
+      </c>
+      <c r="E49" t="s">
+        <v>23</v>
+      </c>
+      <c r="F49">
+        <v>23150</v>
+      </c>
+      <c r="G49">
+        <v>3</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>275</v>
+      </c>
+      <c r="J49">
+        <v>3</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>1.0532407407407407E-3</v>
+      </c>
+      <c r="P49" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>1.09E-2</v>
+      </c>
+      <c r="R49" s="5">
+        <v>0</v>
+      </c>
+      <c r="S49" t="s">
+        <v>25</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3A9941-6A7B-49E9-B144-840724CCC9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D6598F-AC6C-44E6-928D-C516F7D5C693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -469,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -3766,46 +3766,46 @@
         <v>38</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48">
-        <v>22701</v>
+        <v>22703</v>
       </c>
       <c r="J48">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K48">
         <v>32</v>
       </c>
       <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
         <v>15</v>
       </c>
-      <c r="M48">
-        <v>8</v>
-      </c>
       <c r="N48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" s="3">
-        <v>9.3749999999999997E-4</v>
+        <v>9.2592592592592596E-4</v>
       </c>
       <c r="P48" s="3">
-        <v>1.3773148148148147E-3</v>
+        <v>1.4467592592592592E-3</v>
       </c>
       <c r="Q48" s="4">
-        <v>1.23E-2</v>
+        <v>1.24E-2</v>
       </c>
       <c r="R48" s="4">
-        <v>0.1147</v>
+        <v>0.1139</v>
       </c>
       <c r="S48" s="4">
-        <v>0.46879999999999999</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="U48" s="4">
-        <v>0.52939999999999998</v>
+        <v>0.53129999999999999</v>
       </c>
       <c r="V48" s="4">
         <v>1</v>
@@ -3814,7 +3814,7 @@
         <v>0.16500000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>46182</v>
       </c>
@@ -3834,48 +3834,400 @@
         <v>23150</v>
       </c>
       <c r="G49">
+        <v>38</v>
+      </c>
+      <c r="H49">
+        <v>4</v>
+      </c>
+      <c r="I49">
+        <v>24759</v>
+      </c>
+      <c r="J49">
+        <v>286</v>
+      </c>
+      <c r="K49">
+        <v>53</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49">
+        <v>37</v>
+      </c>
+      <c r="N49">
+        <v>5</v>
+      </c>
+      <c r="O49" s="3">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="P49" s="3">
+        <v>1.6435185185185185E-3</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="R49" s="5">
+        <v>0.18529999999999999</v>
+      </c>
+      <c r="S49" s="4">
+        <v>1.89E-2</v>
+      </c>
+      <c r="T49">
+        <v>15</v>
+      </c>
+      <c r="U49" s="4">
+        <v>0.28849999999999998</v>
+      </c>
+      <c r="V49" s="4">
+        <v>1</v>
+      </c>
+      <c r="W49">
+        <v>0.42899999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B50">
+        <v>11</v>
+      </c>
+      <c r="C50">
+        <v>168</v>
+      </c>
+      <c r="D50">
+        <v>169</v>
+      </c>
+      <c r="E50" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50">
+        <v>23150</v>
+      </c>
+      <c r="G50">
+        <v>38</v>
+      </c>
+      <c r="H50">
+        <v>4</v>
+      </c>
+      <c r="I50">
+        <v>21974</v>
+      </c>
+      <c r="J50">
+        <v>262</v>
+      </c>
+      <c r="K50">
+        <v>50</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>32</v>
+      </c>
+      <c r="N50">
+        <v>10</v>
+      </c>
+      <c r="O50" s="3">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="P50" s="3">
+        <v>1.9328703703703704E-3</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="R50" s="4">
+        <v>0.1908</v>
+      </c>
+      <c r="S50" s="5">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>18</v>
+      </c>
+      <c r="U50" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="V50" s="4">
+        <v>1</v>
+      </c>
+      <c r="W50">
+        <v>0.23100000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B51">
+        <v>12</v>
+      </c>
+      <c r="C51">
+        <v>168</v>
+      </c>
+      <c r="D51">
+        <v>169</v>
+      </c>
+      <c r="E51" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51">
+        <v>23150</v>
+      </c>
+      <c r="G51">
+        <v>38</v>
+      </c>
+      <c r="H51">
+        <v>4</v>
+      </c>
+      <c r="I51">
+        <v>18186</v>
+      </c>
+      <c r="J51">
+        <v>1835</v>
+      </c>
+      <c r="K51">
+        <v>144</v>
+      </c>
+      <c r="L51">
         <v>3</v>
       </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>275</v>
-      </c>
-      <c r="J49">
+      <c r="M51">
+        <v>51</v>
+      </c>
+      <c r="N51">
+        <v>6</v>
+      </c>
+      <c r="O51" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P51" s="3">
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>0.1009</v>
+      </c>
+      <c r="R51" s="4">
+        <v>7.85E-2</v>
+      </c>
+      <c r="S51" s="4">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="T51">
+        <v>90</v>
+      </c>
+      <c r="U51" s="4">
+        <v>0.63829999999999998</v>
+      </c>
+      <c r="V51" s="4">
+        <v>1</v>
+      </c>
+      <c r="W51">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B52">
+        <v>13</v>
+      </c>
+      <c r="C52">
+        <v>168</v>
+      </c>
+      <c r="D52">
+        <v>169</v>
+      </c>
+      <c r="E52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52">
+        <v>23150</v>
+      </c>
+      <c r="G52">
+        <v>30</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>186</v>
+      </c>
+      <c r="J52">
+        <v>30</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="P52" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>0.1613</v>
+      </c>
+      <c r="R52" s="4">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="S52" s="5">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+      <c r="U52" s="5">
+        <v>1</v>
+      </c>
+      <c r="V52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B53">
+        <v>14</v>
+      </c>
+      <c r="C53">
+        <v>168</v>
+      </c>
+      <c r="D53">
+        <v>169</v>
+      </c>
+      <c r="E53" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53">
+        <v>23150</v>
+      </c>
+      <c r="G53">
+        <v>38</v>
+      </c>
+      <c r="H53">
         <v>3</v>
       </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1.0532407407407407E-3</v>
-      </c>
-      <c r="P49" t="s">
+      <c r="I53">
+        <v>4188</v>
+      </c>
+      <c r="J53">
+        <v>840</v>
+      </c>
+      <c r="K53">
+        <v>36</v>
+      </c>
+      <c r="L53">
+        <v>23</v>
+      </c>
+      <c r="M53">
+        <v>5</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+      <c r="O53" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="P53" s="3">
+        <v>7.7546296296296293E-4</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>0.2006</v>
+      </c>
+      <c r="R53" s="4">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="S53" s="4">
+        <v>0.63890000000000002</v>
+      </c>
+      <c r="T53">
+        <v>8</v>
+      </c>
+      <c r="U53" s="4">
+        <v>0.61539999999999995</v>
+      </c>
+      <c r="V53" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B54">
+        <v>15</v>
+      </c>
+      <c r="C54">
+        <v>168</v>
+      </c>
+      <c r="D54">
+        <v>169</v>
+      </c>
+      <c r="E54" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54">
+        <v>23150</v>
+      </c>
+      <c r="G54">
+        <v>13</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>113</v>
+      </c>
+      <c r="J54">
+        <v>13</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P54" t="s">
         <v>24</v>
       </c>
-      <c r="Q49" s="4">
-        <v>1.09E-2</v>
-      </c>
-      <c r="R49" s="5">
-        <v>0</v>
-      </c>
-      <c r="S49" t="s">
+      <c r="Q54" s="4">
+        <v>0.115</v>
+      </c>
+      <c r="R54" s="5">
+        <v>0</v>
+      </c>
+      <c r="S54" t="s">
         <v>25</v>
       </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49" t="s">
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54" t="s">
+        <v>25</v>
+      </c>
+      <c r="V54" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D6598F-AC6C-44E6-928D-C516F7D5C693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A758F0-4AF0-48F7-9279-010A12B6E904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="27">
   <si>
     <t>Data</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>%</t>
+  </si>
+  <si>
+    <t>Locator_Template</t>
   </si>
 </sst>
 </file>
@@ -469,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W54"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -4118,7 +4121,7 @@
         <v>38</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I53">
         <v>4188</v>
@@ -4127,37 +4130,37 @@
         <v>840</v>
       </c>
       <c r="K53">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L53">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O53" s="3">
         <v>4.6296296296296294E-5</v>
       </c>
       <c r="P53" s="3">
-        <v>7.7546296296296293E-4</v>
+        <v>9.837962962962962E-4</v>
       </c>
       <c r="Q53" s="4">
         <v>0.2006</v>
       </c>
       <c r="R53" s="4">
-        <v>4.2900000000000001E-2</v>
+        <v>4.5199999999999997E-2</v>
       </c>
       <c r="S53" s="4">
-        <v>0.63890000000000002</v>
+        <v>0</v>
       </c>
       <c r="T53">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="U53" s="4">
-        <v>0.61539999999999995</v>
+        <v>0.3947</v>
       </c>
       <c r="V53" s="4">
         <v>1</v>
@@ -4183,51 +4186,391 @@
         <v>23150</v>
       </c>
       <c r="G54">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I54">
-        <v>113</v>
+        <v>13153</v>
       </c>
       <c r="J54">
-        <v>13</v>
+        <v>1161</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O54" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="P54" s="3">
+        <v>1.4004629629629629E-3</v>
+      </c>
+      <c r="Q54" s="4">
+        <v>8.8300000000000003E-2</v>
+      </c>
+      <c r="R54" s="5">
+        <v>6.3700000000000007E-2</v>
+      </c>
+      <c r="S54" s="4">
+        <v>2.7E-2</v>
+      </c>
+      <c r="T54">
+        <v>15</v>
+      </c>
+      <c r="U54" s="4">
+        <v>0.20830000000000001</v>
+      </c>
+      <c r="V54" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B55">
+        <v>16</v>
+      </c>
+      <c r="C55">
+        <v>166</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
+        <v>26</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+      <c r="J55">
+        <v>2</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P55" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q55" s="5">
+        <v>1</v>
+      </c>
+      <c r="R55" s="5">
+        <v>0</v>
+      </c>
+      <c r="S55" t="s">
+        <v>25</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55" t="s">
+        <v>25</v>
+      </c>
+      <c r="W55">
+        <v>0.13750000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B56">
+        <v>16</v>
+      </c>
+      <c r="C56">
+        <v>168</v>
+      </c>
+      <c r="D56">
+        <v>169</v>
+      </c>
+      <c r="E56" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56">
+        <v>23150</v>
+      </c>
+      <c r="G56">
+        <v>38</v>
+      </c>
+      <c r="H56">
+        <v>6</v>
+      </c>
+      <c r="I56">
+        <v>14189</v>
+      </c>
+      <c r="J56">
+        <v>1490</v>
+      </c>
+      <c r="K56">
+        <v>103</v>
+      </c>
+      <c r="L56">
+        <v>3</v>
+      </c>
+      <c r="M56">
+        <v>54</v>
+      </c>
+      <c r="N56">
+        <v>7</v>
+      </c>
+      <c r="O56" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P56" s="3">
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="Q56" s="4">
+        <v>0.105</v>
+      </c>
+      <c r="R56" s="4">
+        <v>6.9099999999999995E-2</v>
+      </c>
+      <c r="S56" s="4">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="T56">
+        <v>46</v>
+      </c>
+      <c r="U56" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="V56" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B57">
+        <v>17</v>
+      </c>
+      <c r="C57">
+        <v>166</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>2</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
+        <v>2.3148148148148147E-5</v>
+      </c>
+      <c r="P57" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q57" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="R57" s="5">
+        <v>0</v>
+      </c>
+      <c r="S57" t="s">
+        <v>25</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57" t="s">
+        <v>25</v>
+      </c>
+      <c r="W57">
+        <v>2.75E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B58">
+        <v>17</v>
+      </c>
+      <c r="C58">
+        <v>168</v>
+      </c>
+      <c r="D58">
+        <v>169</v>
+      </c>
+      <c r="E58" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58">
+        <v>23150</v>
+      </c>
+      <c r="G58">
+        <v>38</v>
+      </c>
+      <c r="H58">
+        <v>3</v>
+      </c>
+      <c r="I58">
+        <v>14477</v>
+      </c>
+      <c r="J58">
+        <v>1550</v>
+      </c>
+      <c r="K58">
+        <v>99</v>
+      </c>
+      <c r="L58">
+        <v>21</v>
+      </c>
+      <c r="M58">
+        <v>24</v>
+      </c>
+      <c r="N58">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P58" s="3">
+        <v>2.3032407407407407E-3</v>
+      </c>
+      <c r="Q58" s="4">
+        <v>0.1071</v>
+      </c>
+      <c r="R58" s="4">
+        <v>6.3899999999999998E-2</v>
+      </c>
+      <c r="S58" s="4">
+        <v>0.21210000000000001</v>
+      </c>
+      <c r="T58">
+        <v>54</v>
+      </c>
+      <c r="U58" s="4">
+        <v>0.69230000000000003</v>
+      </c>
+      <c r="V58" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B59">
+        <v>18</v>
+      </c>
+      <c r="C59">
+        <v>168</v>
+      </c>
+      <c r="D59">
+        <v>169</v>
+      </c>
+      <c r="E59" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59">
+        <v>23150</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>16</v>
+      </c>
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>9.2592592592592588E-5</v>
       </c>
-      <c r="P54" t="s">
+      <c r="P59" t="s">
         <v>24</v>
       </c>
-      <c r="Q54" s="4">
-        <v>0.115</v>
-      </c>
-      <c r="R54" s="5">
-        <v>0</v>
-      </c>
-      <c r="S54" t="s">
+      <c r="Q59" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="R59" s="5">
+        <v>0</v>
+      </c>
+      <c r="S59" t="s">
         <v>25</v>
       </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54" t="s">
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59" t="s">
         <v>25</v>
       </c>
-      <c r="V54" t="s">
+      <c r="V59" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A758F0-4AF0-48F7-9279-010A12B6E904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF18749-0416-456B-85F2-814C6A171CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="27">
   <si>
     <t>Data</t>
   </si>
@@ -472,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W59"/>
+  <dimension ref="A1:W62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -4464,43 +4464,43 @@
         <v>3</v>
       </c>
       <c r="I58">
-        <v>14477</v>
+        <v>14504</v>
       </c>
       <c r="J58">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="K58">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L58">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M58">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="N58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O58" s="3">
         <v>1.0416666666666667E-4</v>
       </c>
       <c r="P58" s="3">
-        <v>2.3032407407407407E-3</v>
+        <v>1.9791666666666668E-3</v>
       </c>
       <c r="Q58" s="4">
         <v>0.1071</v>
       </c>
       <c r="R58" s="4">
-        <v>6.3899999999999998E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="S58" s="4">
-        <v>0.21210000000000001</v>
+        <v>9.9000000000000008E-3</v>
       </c>
       <c r="T58">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="U58" s="4">
-        <v>0.69230000000000003</v>
+        <v>0.65</v>
       </c>
       <c r="V58" s="4">
         <v>1</v>
@@ -4514,34 +4514,34 @@
         <v>18</v>
       </c>
       <c r="C59">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D59">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F59">
-        <v>23150</v>
+        <v>1</v>
       </c>
       <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
         <v>2</v>
       </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>16</v>
-      </c>
       <c r="J59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -4550,19 +4550,19 @@
         <v>0</v>
       </c>
       <c r="O59" s="3">
-        <v>9.2592592592592588E-5</v>
+        <v>2.3148148148148147E-5</v>
       </c>
       <c r="P59" t="s">
         <v>24</v>
       </c>
       <c r="Q59" s="4">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="R59" s="5">
-        <v>0</v>
-      </c>
-      <c r="S59" t="s">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="S59" s="5">
+        <v>1</v>
       </c>
       <c r="T59">
         <v>0</v>
@@ -4570,8 +4570,212 @@
       <c r="U59" t="s">
         <v>25</v>
       </c>
-      <c r="V59" t="s">
+      <c r="W59">
+        <v>3.85E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B60">
+        <v>18</v>
+      </c>
+      <c r="C60">
+        <v>168</v>
+      </c>
+      <c r="D60">
+        <v>169</v>
+      </c>
+      <c r="E60" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60">
+        <v>23150</v>
+      </c>
+      <c r="G60">
+        <v>38</v>
+      </c>
+      <c r="H60">
+        <v>3</v>
+      </c>
+      <c r="I60">
+        <v>14924</v>
+      </c>
+      <c r="J60">
+        <v>1497</v>
+      </c>
+      <c r="K60">
+        <v>90</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>28</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+      <c r="O60" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P60" s="3">
+        <v>1.3310185185185185E-3</v>
+      </c>
+      <c r="Q60" s="4">
+        <v>0.1003</v>
+      </c>
+      <c r="R60" s="4">
+        <v>6.0100000000000001E-2</v>
+      </c>
+      <c r="S60" s="5">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>62</v>
+      </c>
+      <c r="U60" s="4">
+        <v>0.68889999999999996</v>
+      </c>
+      <c r="V60" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B61">
+        <v>19</v>
+      </c>
+      <c r="C61">
+        <v>168</v>
+      </c>
+      <c r="D61">
+        <v>169</v>
+      </c>
+      <c r="E61" t="s">
+        <v>23</v>
+      </c>
+      <c r="F61">
+        <v>23150</v>
+      </c>
+      <c r="G61">
+        <v>38</v>
+      </c>
+      <c r="H61">
+        <v>3</v>
+      </c>
+      <c r="I61">
+        <v>15473</v>
+      </c>
+      <c r="J61">
+        <v>1418</v>
+      </c>
+      <c r="K61">
+        <v>94</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>39</v>
+      </c>
+      <c r="N61">
+        <v>2</v>
+      </c>
+      <c r="O61" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="P61" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="Q61" s="4">
+        <v>9.1600000000000001E-2</v>
+      </c>
+      <c r="R61" s="4">
+        <v>6.6299999999999998E-2</v>
+      </c>
+      <c r="S61" s="5">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>55</v>
+      </c>
+      <c r="U61" s="4">
+        <v>0.58509999999999995</v>
+      </c>
+      <c r="V61" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B62">
+        <v>20</v>
+      </c>
+      <c r="C62">
+        <v>168</v>
+      </c>
+      <c r="D62">
+        <v>169</v>
+      </c>
+      <c r="E62" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62">
+        <v>23150</v>
+      </c>
+      <c r="G62">
+        <v>38</v>
+      </c>
+      <c r="H62">
+        <v>2</v>
+      </c>
+      <c r="I62">
+        <v>10663</v>
+      </c>
+      <c r="J62">
+        <v>887</v>
+      </c>
+      <c r="K62">
+        <v>70</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
         <v>25</v>
+      </c>
+      <c r="N62">
+        <v>2</v>
+      </c>
+      <c r="O62" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="P62" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="Q62" s="4">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="R62" s="4">
+        <v>7.8899999999999998E-2</v>
+      </c>
+      <c r="S62" s="5">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>45</v>
+      </c>
+      <c r="U62" s="4">
+        <v>0.64290000000000003</v>
+      </c>
+      <c r="V62" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF18749-0416-456B-85F2-814C6A171CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79334607-DE91-497D-800F-D0F6E8AC3300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -4781,4 +4782,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FFF5342-4B63-4B01-A332-A226EA58A2DA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gersou\Downloads\OSPDataCommandCenter_MULTI_CLIENTES_v8_COMPARATIVO_EXECUTIVO_DATAS\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79334607-DE91-497D-800F-D0F6E8AC3300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB23A68-1D93-4BEA-923F-E84F377ECBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="50">
   <si>
     <t>Data</t>
   </si>
@@ -102,6 +102,75 @@
   </si>
   <si>
     <t>Locator_Template</t>
+  </si>
+  <si>
+    <t>ANIMA</t>
+  </si>
+  <si>
+    <t>CARREFOUR_2</t>
+  </si>
+  <si>
+    <t>CBK_181A740/SELLER</t>
+  </si>
+  <si>
+    <t>JEITTO_PRE_EG</t>
+  </si>
+  <si>
+    <t>JEITTO_RECOVERY</t>
+  </si>
+  <si>
+    <t>Link_Manual</t>
+  </si>
+  <si>
+    <t>SIMPLIC_FASE1</t>
+  </si>
+  <si>
+    <t>JEITTO_PRE_EJ</t>
+  </si>
+  <si>
+    <t>TIM_CONTROLE_FIXO</t>
+  </si>
+  <si>
+    <t>CARREFOUR_1</t>
+  </si>
+  <si>
+    <t>EXAME_B1</t>
+  </si>
+  <si>
+    <t>PAGBANK_DEVOLUCOES</t>
+  </si>
+  <si>
+    <t>SIMPLIC_FASE2</t>
+  </si>
+  <si>
+    <t>SIMPLIC_FASE2_SWAT</t>
+  </si>
+  <si>
+    <t>SOFISA</t>
+  </si>
+  <si>
+    <t>VALE_CONSIGNADO</t>
+  </si>
+  <si>
+    <t>BPP</t>
+  </si>
+  <si>
+    <t>VIS</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>Logados</t>
+  </si>
+  <si>
+    <t>Cpc</t>
+  </si>
+  <si>
+    <t>Loc</t>
+  </si>
+  <si>
+    <t>Conver</t>
   </si>
 </sst>
 </file>
@@ -4786,9 +4855,4572 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FFF5342-4B63-4B01-A332-A226EA58A2DA}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>54194</v>
+      </c>
+      <c r="E2">
+        <v>850</v>
+      </c>
+      <c r="F2">
+        <v>656</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+      <c r="H2" s="4">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0.77180000000000004</v>
+      </c>
+      <c r="J2" s="5">
+        <v>1.37E-2</v>
+      </c>
+      <c r="K2" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>51276</v>
+      </c>
+      <c r="E3">
+        <v>1618</v>
+      </c>
+      <c r="F3">
+        <v>363</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.22439999999999999</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>48955</v>
+      </c>
+      <c r="E4">
+        <v>2281</v>
+      </c>
+      <c r="F4">
+        <v>690</v>
+      </c>
+      <c r="G4">
+        <v>38</v>
+      </c>
+      <c r="H4" s="4">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="J4" s="4">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="K4" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>13393</v>
+      </c>
+      <c r="E5">
+        <v>329</v>
+      </c>
+      <c r="F5">
+        <v>296</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5" s="4">
+        <v>2.46E-2</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.89970000000000006</v>
+      </c>
+      <c r="J5" s="4">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="K5" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6">
+        <v>28299</v>
+      </c>
+      <c r="E6">
+        <v>1318</v>
+      </c>
+      <c r="F6">
+        <v>1142</v>
+      </c>
+      <c r="G6">
+        <v>43</v>
+      </c>
+      <c r="H6" s="5">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.86650000000000005</v>
+      </c>
+      <c r="J6" s="5">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="K6" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>38</v>
+      </c>
+      <c r="D7">
+        <v>407</v>
+      </c>
+      <c r="E7">
+        <v>407</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="K7" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>2154</v>
+      </c>
+      <c r="E8">
+        <v>39</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1.8100000000000002E-2</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.15379999999999999</v>
+      </c>
+      <c r="J8" s="4">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>16729</v>
+      </c>
+      <c r="E9">
+        <v>511</v>
+      </c>
+      <c r="F9">
+        <v>437</v>
+      </c>
+      <c r="G9">
+        <v>21</v>
+      </c>
+      <c r="H9" s="4">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.85519999999999996</v>
+      </c>
+      <c r="J9" s="4">
+        <v>4.8099999999999997E-2</v>
+      </c>
+      <c r="K9" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>33719</v>
+      </c>
+      <c r="E10">
+        <v>1449</v>
+      </c>
+      <c r="F10">
+        <v>116</v>
+      </c>
+      <c r="G10">
+        <v>63</v>
+      </c>
+      <c r="H10" s="4">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="I10" s="4">
+        <v>8.0100000000000005E-2</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0.54310000000000003</v>
+      </c>
+      <c r="K10" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>16547</v>
+      </c>
+      <c r="E11">
+        <v>312</v>
+      </c>
+      <c r="F11">
+        <v>127</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1.89E-2</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.40710000000000002</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>4877</v>
+      </c>
+      <c r="E12">
+        <v>84</v>
+      </c>
+      <c r="F12">
+        <v>68</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1.72E-2</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.8095</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.14710000000000001</v>
+      </c>
+      <c r="K12" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>19136</v>
+      </c>
+      <c r="E13">
+        <v>1215</v>
+      </c>
+      <c r="F13">
+        <v>469</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13" s="4">
+        <v>6.3500000000000001E-2</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="K13" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14">
+        <v>28</v>
+      </c>
+      <c r="D14">
+        <v>80762</v>
+      </c>
+      <c r="E14">
+        <v>2504</v>
+      </c>
+      <c r="F14">
+        <v>856</v>
+      </c>
+      <c r="G14">
+        <v>78</v>
+      </c>
+      <c r="H14" s="4">
+        <v>3.1E-2</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.34189999999999998</v>
+      </c>
+      <c r="J14" s="4">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="K14" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>9206</v>
+      </c>
+      <c r="E15">
+        <v>325</v>
+      </c>
+      <c r="F15">
+        <v>118</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15" s="4">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.36309999999999998</v>
+      </c>
+      <c r="J15" s="4">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="K15" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>62399</v>
+      </c>
+      <c r="E16">
+        <v>1116</v>
+      </c>
+      <c r="F16">
+        <v>1091</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.97760000000000002</v>
+      </c>
+      <c r="J16" s="4">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="K16" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>4851</v>
+      </c>
+      <c r="E17">
+        <v>187</v>
+      </c>
+      <c r="F17">
+        <v>21</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17" s="4">
+        <v>3.85E-2</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1123</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1429</v>
+      </c>
+      <c r="K17" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18">
+        <v>8</v>
+      </c>
+      <c r="D18">
+        <v>54655</v>
+      </c>
+      <c r="E18">
+        <v>991</v>
+      </c>
+      <c r="F18">
+        <v>961</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+      <c r="H18" s="4">
+        <v>1.8100000000000002E-2</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.96970000000000001</v>
+      </c>
+      <c r="J18" s="5">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="K18" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>43992</v>
+      </c>
+      <c r="E19">
+        <v>2249</v>
+      </c>
+      <c r="F19">
+        <v>248</v>
+      </c>
+      <c r="G19">
+        <v>124</v>
+      </c>
+      <c r="H19" s="4">
+        <v>5.11E-2</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.1103</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="K19" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>2937</v>
+      </c>
+      <c r="E20">
+        <v>66</v>
+      </c>
+      <c r="F20">
+        <v>14</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20" s="5">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.21210000000000001</v>
+      </c>
+      <c r="J20" s="5">
+        <v>7.0199999999999999E-2</v>
+      </c>
+      <c r="K20" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21">
+        <v>49</v>
+      </c>
+      <c r="D21">
+        <v>446</v>
+      </c>
+      <c r="E21">
+        <v>446</v>
+      </c>
+      <c r="F21">
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22">
+        <v>38082</v>
+      </c>
+      <c r="E22">
+        <v>1244</v>
+      </c>
+      <c r="F22">
+        <v>332</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>3.27E-2</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0.26690000000000003</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>11659</v>
+      </c>
+      <c r="E23">
+        <v>317</v>
+      </c>
+      <c r="F23">
+        <v>280</v>
+      </c>
+      <c r="G23">
+        <v>12</v>
+      </c>
+      <c r="H23" s="4">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0.88329999999999997</v>
+      </c>
+      <c r="J23" s="4">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="K23" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>21613</v>
+      </c>
+      <c r="E24">
+        <v>530</v>
+      </c>
+      <c r="F24">
+        <v>439</v>
+      </c>
+      <c r="G24">
+        <v>24</v>
+      </c>
+      <c r="H24" s="4">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0.82830000000000004</v>
+      </c>
+      <c r="J24" s="4">
+        <v>5.4699999999999999E-2</v>
+      </c>
+      <c r="K24" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>37445</v>
+      </c>
+      <c r="E25">
+        <v>1053</v>
+      </c>
+      <c r="F25">
+        <v>841</v>
+      </c>
+      <c r="G25">
+        <v>6</v>
+      </c>
+      <c r="H25" s="4">
+        <v>2.81E-2</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0.79869999999999997</v>
+      </c>
+      <c r="J25" s="5">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="K25" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>4924</v>
+      </c>
+      <c r="E26">
+        <v>224</v>
+      </c>
+      <c r="F26">
+        <v>20</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="I26" s="4">
+        <v>8.9300000000000004E-2</v>
+      </c>
+      <c r="J26" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="K26" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>15988</v>
+      </c>
+      <c r="E27">
+        <v>501</v>
+      </c>
+      <c r="F27">
+        <v>164</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27" s="4">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0.32729999999999998</v>
+      </c>
+      <c r="J27" s="4">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="K27" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28">
+        <v>30</v>
+      </c>
+      <c r="D28">
+        <v>94611</v>
+      </c>
+      <c r="E28">
+        <v>2585</v>
+      </c>
+      <c r="F28">
+        <v>852</v>
+      </c>
+      <c r="G28">
+        <v>31</v>
+      </c>
+      <c r="H28" s="4">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0.3296</v>
+      </c>
+      <c r="J28" s="5">
+        <v>1.34E-2</v>
+      </c>
+      <c r="K28" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>18511</v>
+      </c>
+      <c r="E29">
+        <v>1247</v>
+      </c>
+      <c r="F29">
+        <v>516</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4">
+        <v>6.7400000000000002E-2</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0.4138</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>19676</v>
+      </c>
+      <c r="E30">
+        <v>961</v>
+      </c>
+      <c r="F30">
+        <v>766</v>
+      </c>
+      <c r="G30">
+        <v>49</v>
+      </c>
+      <c r="H30" s="4">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0.79710000000000003</v>
+      </c>
+      <c r="J30" s="5">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="K30" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31">
+        <v>20998</v>
+      </c>
+      <c r="E31">
+        <v>457</v>
+      </c>
+      <c r="F31">
+        <v>176</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4">
+        <v>2.18E-2</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0.3851</v>
+      </c>
+      <c r="J31" s="4">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>1145</v>
+      </c>
+      <c r="E32">
+        <v>30</v>
+      </c>
+      <c r="F32">
+        <v>26</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32" s="4">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0.86670000000000003</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0.1154</v>
+      </c>
+      <c r="K32" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33">
+        <v>15</v>
+      </c>
+      <c r="D33">
+        <v>33011</v>
+      </c>
+      <c r="E33">
+        <v>1679</v>
+      </c>
+      <c r="F33">
+        <v>509</v>
+      </c>
+      <c r="G33">
+        <v>52</v>
+      </c>
+      <c r="H33" s="4">
+        <v>5.0900000000000001E-2</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0.30320000000000003</v>
+      </c>
+      <c r="J33" s="5">
+        <v>0.1022</v>
+      </c>
+      <c r="K33" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34">
+        <v>12</v>
+      </c>
+      <c r="D34">
+        <v>42520</v>
+      </c>
+      <c r="E34">
+        <v>1350</v>
+      </c>
+      <c r="F34">
+        <v>298</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="I34" s="4">
+        <v>0.22070000000000001</v>
+      </c>
+      <c r="J34" s="4">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35">
+        <v>9</v>
+      </c>
+      <c r="D35">
+        <v>51814</v>
+      </c>
+      <c r="E35">
+        <v>1128</v>
+      </c>
+      <c r="F35">
+        <v>909</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+      <c r="H35" s="4">
+        <v>2.18E-2</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0.80589999999999995</v>
+      </c>
+      <c r="J35" s="5">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="K35" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36">
+        <v>7</v>
+      </c>
+      <c r="D36">
+        <v>4388</v>
+      </c>
+      <c r="E36">
+        <v>97</v>
+      </c>
+      <c r="F36">
+        <v>50</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="I36" s="4">
+        <v>0.51549999999999996</v>
+      </c>
+      <c r="J36" s="4">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
+        <v>945</v>
+      </c>
+      <c r="E37">
+        <v>17</v>
+      </c>
+      <c r="F37">
+        <v>15</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0.88239999999999996</v>
+      </c>
+      <c r="J37" s="4">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="K37" s="3">
+        <v>9.6064814814814819E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B38" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38">
+        <v>6</v>
+      </c>
+      <c r="D38">
+        <v>10736</v>
+      </c>
+      <c r="E38">
+        <v>354</v>
+      </c>
+      <c r="F38">
+        <v>320</v>
+      </c>
+      <c r="G38">
+        <v>15</v>
+      </c>
+      <c r="H38" s="5">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="I38" s="5">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="J38" s="4">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="K38" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>47</v>
+      </c>
+      <c r="D39">
+        <v>411</v>
+      </c>
+      <c r="E39">
+        <v>411</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" s="4">
+        <v>1</v>
+      </c>
+      <c r="I39" s="4">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40">
+        <v>10</v>
+      </c>
+      <c r="D40">
+        <v>17536</v>
+      </c>
+      <c r="E40">
+        <v>1045</v>
+      </c>
+      <c r="F40">
+        <v>391</v>
+      </c>
+      <c r="G40">
+        <v>9</v>
+      </c>
+      <c r="H40" s="4">
+        <v>5.96E-2</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0.37419999999999998</v>
+      </c>
+      <c r="J40" s="4">
+        <v>2.3E-2</v>
+      </c>
+      <c r="K40" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41">
+        <v>31</v>
+      </c>
+      <c r="D41">
+        <v>73894</v>
+      </c>
+      <c r="E41">
+        <v>2758</v>
+      </c>
+      <c r="F41">
+        <v>972</v>
+      </c>
+      <c r="G41">
+        <v>68</v>
+      </c>
+      <c r="H41" s="4">
+        <v>3.73E-2</v>
+      </c>
+      <c r="I41" s="4">
+        <v>0.35239999999999999</v>
+      </c>
+      <c r="J41" s="4">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="K41" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42">
+        <v>9</v>
+      </c>
+      <c r="D42">
+        <v>21151</v>
+      </c>
+      <c r="E42">
+        <v>338</v>
+      </c>
+      <c r="F42">
+        <v>290</v>
+      </c>
+      <c r="G42">
+        <v>16</v>
+      </c>
+      <c r="H42" s="4">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I42" s="4">
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="J42" s="4">
+        <v>5.5199999999999999E-2</v>
+      </c>
+      <c r="K42" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43">
+        <v>7</v>
+      </c>
+      <c r="D43">
+        <v>61387</v>
+      </c>
+      <c r="E43">
+        <v>905</v>
+      </c>
+      <c r="F43">
+        <v>880</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
+      </c>
+      <c r="H43" s="4">
+        <v>1.47E-2</v>
+      </c>
+      <c r="I43" s="4">
+        <v>0.97240000000000004</v>
+      </c>
+      <c r="J43" s="5">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="K43" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44">
+        <v>6</v>
+      </c>
+      <c r="D44">
+        <v>25213</v>
+      </c>
+      <c r="E44">
+        <v>578</v>
+      </c>
+      <c r="F44">
+        <v>233</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" s="4">
+        <v>2.29E-2</v>
+      </c>
+      <c r="I44" s="4">
+        <v>0.40310000000000001</v>
+      </c>
+      <c r="J44" s="4">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45">
+        <v>13</v>
+      </c>
+      <c r="D45">
+        <v>34373</v>
+      </c>
+      <c r="E45">
+        <v>1464</v>
+      </c>
+      <c r="F45">
+        <v>436</v>
+      </c>
+      <c r="G45">
+        <v>19</v>
+      </c>
+      <c r="H45" s="4">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="I45" s="4">
+        <v>0.29780000000000001</v>
+      </c>
+      <c r="J45" s="4">
+        <v>4.36E-2</v>
+      </c>
+      <c r="K45" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46">
+        <v>8</v>
+      </c>
+      <c r="D46">
+        <v>18411</v>
+      </c>
+      <c r="E46">
+        <v>734</v>
+      </c>
+      <c r="F46">
+        <v>629</v>
+      </c>
+      <c r="G46">
+        <v>27</v>
+      </c>
+      <c r="H46" s="4">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="I46" s="4">
+        <v>0.8569</v>
+      </c>
+      <c r="J46" s="4">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="K46" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47">
+        <v>7</v>
+      </c>
+      <c r="D47">
+        <v>6104</v>
+      </c>
+      <c r="E47">
+        <v>147</v>
+      </c>
+      <c r="F47">
+        <v>27</v>
+      </c>
+      <c r="G47">
+        <v>13</v>
+      </c>
+      <c r="H47" s="4">
+        <v>2.41E-2</v>
+      </c>
+      <c r="I47" s="4">
+        <v>0.1837</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0.113</v>
+      </c>
+      <c r="K47" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B48" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48">
+        <v>16</v>
+      </c>
+      <c r="D48">
+        <v>62001</v>
+      </c>
+      <c r="E48">
+        <v>2475</v>
+      </c>
+      <c r="F48">
+        <v>183</v>
+      </c>
+      <c r="G48">
+        <v>80</v>
+      </c>
+      <c r="H48" s="4">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="I48" s="4">
+        <v>7.3899999999999993E-2</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0.43719999999999998</v>
+      </c>
+      <c r="K48" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49">
+        <v>6</v>
+      </c>
+      <c r="D49">
+        <v>11200</v>
+      </c>
+      <c r="E49">
+        <v>317</v>
+      </c>
+      <c r="F49">
+        <v>89</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49" s="4">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="I49" s="4">
+        <v>0.28079999999999999</v>
+      </c>
+      <c r="J49" s="5">
+        <v>3.3E-3</v>
+      </c>
+      <c r="K49" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B50" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
+        <v>4428</v>
+      </c>
+      <c r="E50">
+        <v>132</v>
+      </c>
+      <c r="F50">
+        <v>14</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50" s="5">
+        <v>2.98E-2</v>
+      </c>
+      <c r="I50" s="4">
+        <v>0.1061</v>
+      </c>
+      <c r="J50" s="5">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B51" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51">
+        <v>7</v>
+      </c>
+      <c r="D51">
+        <v>1901</v>
+      </c>
+      <c r="E51">
+        <v>38</v>
+      </c>
+      <c r="F51">
+        <v>20</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="I51" s="4">
+        <v>0.52629999999999999</v>
+      </c>
+      <c r="J51" s="4">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>46177</v>
+      </c>
+      <c r="B52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52">
+        <v>9</v>
+      </c>
+      <c r="D52">
+        <v>27615</v>
+      </c>
+      <c r="E52">
+        <v>809</v>
+      </c>
+      <c r="F52">
+        <v>275</v>
+      </c>
+      <c r="G52">
+        <v>24</v>
+      </c>
+      <c r="H52" s="5">
+        <v>2.93E-2</v>
+      </c>
+      <c r="I52" s="5">
+        <v>0.33989999999999998</v>
+      </c>
+      <c r="J52" s="4">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="K52" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>46177</v>
+      </c>
+      <c r="B53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53">
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <v>71</v>
+      </c>
+      <c r="E53">
+        <v>71</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4">
+        <v>1</v>
+      </c>
+      <c r="I53" s="4">
+        <v>0</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>46177</v>
+      </c>
+      <c r="B54" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54">
+        <v>505</v>
+      </c>
+      <c r="E54">
+        <v>13</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="I54" s="4">
+        <v>0.23080000000000001</v>
+      </c>
+      <c r="J54" s="5">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3">
+        <v>1.6203703703703703E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>46177</v>
+      </c>
+      <c r="B55" t="s">
+        <v>33</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>180</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55" s="4">
+        <v>0</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56">
+        <v>12</v>
+      </c>
+      <c r="D56">
+        <v>21550</v>
+      </c>
+      <c r="E56">
+        <v>1281</v>
+      </c>
+      <c r="F56">
+        <v>473</v>
+      </c>
+      <c r="G56">
+        <v>7</v>
+      </c>
+      <c r="H56" s="4">
+        <v>5.9400000000000001E-2</v>
+      </c>
+      <c r="I56" s="4">
+        <v>0.36919999999999997</v>
+      </c>
+      <c r="J56" s="5">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="K56" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57">
+        <v>3282</v>
+      </c>
+      <c r="E57">
+        <v>49</v>
+      </c>
+      <c r="F57">
+        <v>16</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4">
+        <v>1.49E-2</v>
+      </c>
+      <c r="I57" s="4">
+        <v>0.32650000000000001</v>
+      </c>
+      <c r="J57" s="4">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B58" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58">
+        <v>28</v>
+      </c>
+      <c r="D58">
+        <v>93099</v>
+      </c>
+      <c r="E58">
+        <v>1756</v>
+      </c>
+      <c r="F58">
+        <v>584</v>
+      </c>
+      <c r="G58">
+        <v>51</v>
+      </c>
+      <c r="H58" s="5">
+        <v>1.89E-2</v>
+      </c>
+      <c r="I58" s="4">
+        <v>0.33260000000000001</v>
+      </c>
+      <c r="J58" s="5">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="K58" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C59">
+        <v>8</v>
+      </c>
+      <c r="D59">
+        <v>41540</v>
+      </c>
+      <c r="E59">
+        <v>831</v>
+      </c>
+      <c r="F59">
+        <v>325</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="I59" s="4">
+        <v>0.3911</v>
+      </c>
+      <c r="J59" s="4">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60">
+        <v>8</v>
+      </c>
+      <c r="D60">
+        <v>52445</v>
+      </c>
+      <c r="E60">
+        <v>1066</v>
+      </c>
+      <c r="F60">
+        <v>889</v>
+      </c>
+      <c r="G60">
+        <v>6</v>
+      </c>
+      <c r="H60" s="4">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="I60" s="4">
+        <v>0.83399999999999996</v>
+      </c>
+      <c r="J60" s="4">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="K60" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B61" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61">
+        <v>8</v>
+      </c>
+      <c r="D61">
+        <v>64942</v>
+      </c>
+      <c r="E61">
+        <v>1080</v>
+      </c>
+      <c r="F61">
+        <v>1057</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4">
+        <v>1.66E-2</v>
+      </c>
+      <c r="I61" s="4">
+        <v>0.97870000000000001</v>
+      </c>
+      <c r="J61" s="4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="K61" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B62" t="s">
+        <v>42</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>2690</v>
+      </c>
+      <c r="E62">
+        <v>184</v>
+      </c>
+      <c r="F62">
+        <v>39</v>
+      </c>
+      <c r="G62">
+        <v>4</v>
+      </c>
+      <c r="H62" s="4">
+        <v>6.8400000000000002E-2</v>
+      </c>
+      <c r="I62" s="5">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="J62" s="4">
+        <v>0.1026</v>
+      </c>
+      <c r="K62" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B63" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63">
+        <v>3121</v>
+      </c>
+      <c r="E63">
+        <v>40</v>
+      </c>
+      <c r="F63">
+        <v>36</v>
+      </c>
+      <c r="G63">
+        <v>2</v>
+      </c>
+      <c r="H63" s="4">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="I63" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="J63" s="5">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="K63" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+      <c r="C64">
+        <v>12</v>
+      </c>
+      <c r="D64">
+        <v>13417</v>
+      </c>
+      <c r="E64">
+        <v>404</v>
+      </c>
+      <c r="F64">
+        <v>182</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64" s="4">
+        <v>3.0099999999999998E-2</v>
+      </c>
+      <c r="I64" s="4">
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="J64" s="5">
+        <v>0</v>
+      </c>
+      <c r="K64" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65">
+        <v>15</v>
+      </c>
+      <c r="D65">
+        <v>80989</v>
+      </c>
+      <c r="E65">
+        <v>1962</v>
+      </c>
+      <c r="F65">
+        <v>375</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65" s="5">
+        <v>2.4199999999999999E-2</v>
+      </c>
+      <c r="I65" s="4">
+        <v>0.19109999999999999</v>
+      </c>
+      <c r="J65" s="5">
+        <v>0</v>
+      </c>
+      <c r="K65" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B66" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66">
+        <v>47</v>
+      </c>
+      <c r="D66">
+        <v>562</v>
+      </c>
+      <c r="E66">
+        <v>562</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66" s="4">
+        <v>1</v>
+      </c>
+      <c r="I66" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="J66" s="4">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B67" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67">
+        <v>8</v>
+      </c>
+      <c r="D67">
+        <v>21903</v>
+      </c>
+      <c r="E67">
+        <v>859</v>
+      </c>
+      <c r="F67">
+        <v>735</v>
+      </c>
+      <c r="G67">
+        <v>18</v>
+      </c>
+      <c r="H67" s="4">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="I67" s="4">
+        <v>0.85560000000000003</v>
+      </c>
+      <c r="J67" s="4">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="K67" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B68" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68">
+        <v>4</v>
+      </c>
+      <c r="D68">
+        <v>1313</v>
+      </c>
+      <c r="E68">
+        <v>21</v>
+      </c>
+      <c r="F68">
+        <v>4</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68" s="4">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I68" s="4">
+        <v>0.1905</v>
+      </c>
+      <c r="J68" s="4">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="K68" s="3">
+        <v>2.0833333333333335E-4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B69" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69">
+        <v>13</v>
+      </c>
+      <c r="D69">
+        <v>50162</v>
+      </c>
+      <c r="E69">
+        <v>1371</v>
+      </c>
+      <c r="F69">
+        <v>461</v>
+      </c>
+      <c r="G69">
+        <v>27</v>
+      </c>
+      <c r="H69" s="4">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="I69" s="4">
+        <v>0.33629999999999999</v>
+      </c>
+      <c r="J69" s="4">
+        <v>5.8599999999999999E-2</v>
+      </c>
+      <c r="K69" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B70" t="s">
+        <v>34</v>
+      </c>
+      <c r="C70">
+        <v>10</v>
+      </c>
+      <c r="D70">
+        <v>28882</v>
+      </c>
+      <c r="E70">
+        <v>834</v>
+      </c>
+      <c r="F70">
+        <v>716</v>
+      </c>
+      <c r="G70">
+        <v>56</v>
+      </c>
+      <c r="H70" s="4">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="I70" s="4">
+        <v>0.85850000000000004</v>
+      </c>
+      <c r="J70" s="4">
+        <v>7.8200000000000006E-2</v>
+      </c>
+      <c r="K70" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B71" t="s">
+        <v>30</v>
+      </c>
+      <c r="C71">
+        <v>8</v>
+      </c>
+      <c r="D71">
+        <v>13364</v>
+      </c>
+      <c r="E71">
+        <v>293</v>
+      </c>
+      <c r="F71">
+        <v>265</v>
+      </c>
+      <c r="G71">
+        <v>7</v>
+      </c>
+      <c r="H71" s="4">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="I71" s="4">
+        <v>0.90439999999999998</v>
+      </c>
+      <c r="J71" s="4">
+        <v>2.64E-2</v>
+      </c>
+      <c r="K71" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B72" t="s">
+        <v>44</v>
+      </c>
+      <c r="C72">
+        <v>12</v>
+      </c>
+      <c r="D72">
+        <v>2631</v>
+      </c>
+      <c r="E72">
+        <v>120</v>
+      </c>
+      <c r="F72">
+        <v>59</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4">
+        <v>4.5600000000000002E-2</v>
+      </c>
+      <c r="I72" s="4">
+        <v>0.49170000000000003</v>
+      </c>
+      <c r="J72" s="4">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="K72" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C73">
+        <v>13</v>
+      </c>
+      <c r="D73">
+        <v>48039</v>
+      </c>
+      <c r="E73">
+        <v>1915</v>
+      </c>
+      <c r="F73">
+        <v>147</v>
+      </c>
+      <c r="G73">
+        <v>56</v>
+      </c>
+      <c r="H73" s="4">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="I73" s="4">
+        <v>7.6799999999999993E-2</v>
+      </c>
+      <c r="J73" s="5">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="K73" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B74" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74">
+        <v>4</v>
+      </c>
+      <c r="D74">
+        <v>218</v>
+      </c>
+      <c r="E74">
+        <v>7</v>
+      </c>
+      <c r="F74">
+        <v>6</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74" s="4">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="I74" s="4">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="J74" s="5">
+        <v>0</v>
+      </c>
+      <c r="K74" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B75" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75">
+        <v>5</v>
+      </c>
+      <c r="D75">
+        <v>1823</v>
+      </c>
+      <c r="E75">
+        <v>35</v>
+      </c>
+      <c r="F75">
+        <v>13</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75" s="4">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="I75" s="4">
+        <v>0.37140000000000001</v>
+      </c>
+      <c r="J75" s="4">
+        <v>0</v>
+      </c>
+      <c r="K75" s="3">
+        <v>1.0416666666666667E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B76" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76">
+        <v>2</v>
+      </c>
+      <c r="D76">
+        <v>2118</v>
+      </c>
+      <c r="E76">
+        <v>32</v>
+      </c>
+      <c r="F76">
+        <v>21</v>
+      </c>
+      <c r="G76">
+        <v>4</v>
+      </c>
+      <c r="H76" s="4">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="I76" s="4">
+        <v>0.65629999999999999</v>
+      </c>
+      <c r="J76" s="4">
+        <v>0.1905</v>
+      </c>
+      <c r="K76" s="3">
+        <v>7.5231481481481482E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B77" t="s">
+        <v>39</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>5440</v>
+      </c>
+      <c r="E77">
+        <v>107</v>
+      </c>
+      <c r="F77">
+        <v>48</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+      <c r="H77" s="4">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="I77" s="4">
+        <v>0.4486</v>
+      </c>
+      <c r="J77" s="5">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="K77" s="3">
+        <v>8.564814814814815E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B78" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>8489</v>
+      </c>
+      <c r="E78">
+        <v>91</v>
+      </c>
+      <c r="F78">
+        <v>21</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78" s="4">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="I78" s="4">
+        <v>0.23080000000000001</v>
+      </c>
+      <c r="J78" s="5">
+        <v>0</v>
+      </c>
+      <c r="K78" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B79" t="s">
+        <v>43</v>
+      </c>
+      <c r="C79">
+        <v>4</v>
+      </c>
+      <c r="D79">
+        <v>6642</v>
+      </c>
+      <c r="E79">
+        <v>223</v>
+      </c>
+      <c r="F79">
+        <v>108</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79" s="5">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="I79" s="5">
+        <v>0.48430000000000001</v>
+      </c>
+      <c r="J79" s="5">
+        <v>0</v>
+      </c>
+      <c r="K79" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B80" t="s">
+        <v>32</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80">
+        <v>37</v>
+      </c>
+      <c r="E80">
+        <v>37</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80" s="4">
+        <v>1</v>
+      </c>
+      <c r="I80" s="4">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K80" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B81" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81">
+        <v>6</v>
+      </c>
+      <c r="D81">
+        <v>17232</v>
+      </c>
+      <c r="E81">
+        <v>612</v>
+      </c>
+      <c r="F81">
+        <v>41</v>
+      </c>
+      <c r="G81">
+        <v>18</v>
+      </c>
+      <c r="H81" s="4">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="I81" s="4">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="J81" s="5">
+        <v>0.439</v>
+      </c>
+      <c r="K81" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B82" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>6417</v>
+      </c>
+      <c r="E82">
+        <v>105</v>
+      </c>
+      <c r="F82">
+        <v>44</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82" s="4">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="I82" s="5">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="J82" s="5">
+        <v>0</v>
+      </c>
+      <c r="K82" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B83" t="s">
+        <v>33</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>228</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83" s="4">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="I83" s="4">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B84" t="s">
+        <v>38</v>
+      </c>
+      <c r="C84">
+        <v>11</v>
+      </c>
+      <c r="D84">
+        <v>14810</v>
+      </c>
+      <c r="E84">
+        <v>935</v>
+      </c>
+      <c r="F84">
+        <v>413</v>
+      </c>
+      <c r="G84">
+        <v>3</v>
+      </c>
+      <c r="H84" s="4">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="I84" s="4">
+        <v>0.44169999999999998</v>
+      </c>
+      <c r="J84" s="4">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="K84" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B85" t="s">
+        <v>39</v>
+      </c>
+      <c r="C85">
+        <v>21</v>
+      </c>
+      <c r="D85">
+        <v>74990</v>
+      </c>
+      <c r="E85">
+        <v>2375</v>
+      </c>
+      <c r="F85">
+        <v>840</v>
+      </c>
+      <c r="G85">
+        <v>56</v>
+      </c>
+      <c r="H85" s="4">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="I85" s="4">
+        <v>0.35370000000000001</v>
+      </c>
+      <c r="J85" s="5">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="K85" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B86" t="s">
+        <v>36</v>
+      </c>
+      <c r="C86">
+        <v>8</v>
+      </c>
+      <c r="D86">
+        <v>33334</v>
+      </c>
+      <c r="E86">
+        <v>751</v>
+      </c>
+      <c r="F86">
+        <v>325</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86" s="4">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="I86" s="4">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="J86" s="4">
+        <v>0</v>
+      </c>
+      <c r="K86" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B87" t="s">
+        <v>42</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87">
+        <v>2632</v>
+      </c>
+      <c r="E87">
+        <v>170</v>
+      </c>
+      <c r="F87">
+        <v>22</v>
+      </c>
+      <c r="G87">
+        <v>4</v>
+      </c>
+      <c r="H87" s="4">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="I87" s="4">
+        <v>0.12939999999999999</v>
+      </c>
+      <c r="J87" s="4">
+        <v>0.18179999999999999</v>
+      </c>
+      <c r="K87" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B88" t="s">
+        <v>41</v>
+      </c>
+      <c r="C88">
+        <v>7</v>
+      </c>
+      <c r="D88">
+        <v>73594</v>
+      </c>
+      <c r="E88">
+        <v>1020</v>
+      </c>
+      <c r="F88">
+        <v>980</v>
+      </c>
+      <c r="G88">
+        <v>3</v>
+      </c>
+      <c r="H88" s="5">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="I88" s="4">
+        <v>0.96079999999999999</v>
+      </c>
+      <c r="J88" s="5">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="K88" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B89" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89">
+        <v>53</v>
+      </c>
+      <c r="D89">
+        <v>699</v>
+      </c>
+      <c r="E89">
+        <v>699</v>
+      </c>
+      <c r="F89">
+        <v>10</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89" s="4">
+        <v>1</v>
+      </c>
+      <c r="I89" s="4">
+        <v>1.43E-2</v>
+      </c>
+      <c r="J89" s="4">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B90" t="s">
+        <v>37</v>
+      </c>
+      <c r="C90">
+        <v>3</v>
+      </c>
+      <c r="D90">
+        <v>2233</v>
+      </c>
+      <c r="E90">
+        <v>39</v>
+      </c>
+      <c r="F90">
+        <v>32</v>
+      </c>
+      <c r="G90">
+        <v>4</v>
+      </c>
+      <c r="H90" s="4">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="I90" s="4">
+        <v>0.82050000000000001</v>
+      </c>
+      <c r="J90" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="K90" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B91" t="s">
+        <v>43</v>
+      </c>
+      <c r="C91">
+        <v>7</v>
+      </c>
+      <c r="D91">
+        <v>2649</v>
+      </c>
+      <c r="E91">
+        <v>86</v>
+      </c>
+      <c r="F91">
+        <v>38</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91" s="4">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="I91" s="4">
+        <v>0.44190000000000002</v>
+      </c>
+      <c r="J91" s="4">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B92" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92">
+        <v>9</v>
+      </c>
+      <c r="D92">
+        <v>48657</v>
+      </c>
+      <c r="E92">
+        <v>1277</v>
+      </c>
+      <c r="F92">
+        <v>1087</v>
+      </c>
+      <c r="G92">
+        <v>2</v>
+      </c>
+      <c r="H92" s="4">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="I92" s="4">
+        <v>0.85119999999999996</v>
+      </c>
+      <c r="J92" s="5">
+        <v>1.8E-3</v>
+      </c>
+      <c r="K92" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B93" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93">
+        <v>12</v>
+      </c>
+      <c r="D93">
+        <v>70452</v>
+      </c>
+      <c r="E93">
+        <v>1824</v>
+      </c>
+      <c r="F93">
+        <v>493</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93" s="4">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="I93" s="5">
+        <v>0.27029999999999998</v>
+      </c>
+      <c r="J93" s="4">
+        <v>0</v>
+      </c>
+      <c r="K93" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B94" t="s">
+        <v>33</v>
+      </c>
+      <c r="C94">
+        <v>6</v>
+      </c>
+      <c r="D94">
+        <v>3371</v>
+      </c>
+      <c r="E94">
+        <v>75</v>
+      </c>
+      <c r="F94">
+        <v>15</v>
+      </c>
+      <c r="G94">
+        <v>6</v>
+      </c>
+      <c r="H94" s="4">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="I94" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="J94" s="4">
+        <v>0.1053</v>
+      </c>
+      <c r="K94" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B95" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95">
+        <v>8</v>
+      </c>
+      <c r="D95">
+        <v>22987</v>
+      </c>
+      <c r="E95">
+        <v>912</v>
+      </c>
+      <c r="F95">
+        <v>763</v>
+      </c>
+      <c r="G95">
+        <v>23</v>
+      </c>
+      <c r="H95" s="4">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="I95" s="4">
+        <v>0.83660000000000001</v>
+      </c>
+      <c r="J95" s="4">
+        <v>3.0099999999999998E-2</v>
+      </c>
+      <c r="K95" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B96" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96">
+        <v>13</v>
+      </c>
+      <c r="D96">
+        <v>53083</v>
+      </c>
+      <c r="E96">
+        <v>1752</v>
+      </c>
+      <c r="F96">
+        <v>492</v>
+      </c>
+      <c r="G96">
+        <v>31</v>
+      </c>
+      <c r="H96" s="4">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="I96" s="4">
+        <v>0.28079999999999999</v>
+      </c>
+      <c r="J96" s="4">
+        <v>6.3E-2</v>
+      </c>
+      <c r="K96" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B97" t="s">
+        <v>30</v>
+      </c>
+      <c r="C97">
+        <v>8</v>
+      </c>
+      <c r="D97">
+        <v>16203</v>
+      </c>
+      <c r="E97">
+        <v>458</v>
+      </c>
+      <c r="F97">
+        <v>421</v>
+      </c>
+      <c r="G97">
+        <v>14</v>
+      </c>
+      <c r="H97" s="4">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="I97" s="4">
+        <v>0.91920000000000002</v>
+      </c>
+      <c r="J97" s="4">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="K97" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B98" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98">
+        <v>11</v>
+      </c>
+      <c r="D98">
+        <v>28059</v>
+      </c>
+      <c r="E98">
+        <v>963</v>
+      </c>
+      <c r="F98">
+        <v>856</v>
+      </c>
+      <c r="G98">
+        <v>60</v>
+      </c>
+      <c r="H98" s="4">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="I98" s="4">
+        <v>0.88890000000000002</v>
+      </c>
+      <c r="J98" s="5">
+        <v>7.0099999999999996E-2</v>
+      </c>
+      <c r="K98" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B99" t="s">
+        <v>44</v>
+      </c>
+      <c r="C99">
+        <v>7</v>
+      </c>
+      <c r="D99">
+        <v>475</v>
+      </c>
+      <c r="E99">
+        <v>21</v>
+      </c>
+      <c r="F99">
+        <v>12</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99" s="4">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="I99" s="4">
+        <v>0.57140000000000002</v>
+      </c>
+      <c r="J99" s="5">
+        <v>0</v>
+      </c>
+      <c r="K99" s="3">
+        <v>6.7129629629629625E-4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B100" t="s">
+        <v>35</v>
+      </c>
+      <c r="C100">
+        <v>8</v>
+      </c>
+      <c r="D100">
+        <v>30735</v>
+      </c>
+      <c r="E100">
+        <v>1107</v>
+      </c>
+      <c r="F100">
+        <v>75</v>
+      </c>
+      <c r="G100">
+        <v>42</v>
+      </c>
+      <c r="H100" s="4">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="I100" s="4">
+        <v>6.7799999999999999E-2</v>
+      </c>
+      <c r="J100" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K100" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B101" t="s">
+        <v>41</v>
+      </c>
+      <c r="C101">
+        <v>6</v>
+      </c>
+      <c r="D101">
+        <v>61415</v>
+      </c>
+      <c r="E101">
+        <v>1052</v>
+      </c>
+      <c r="F101">
+        <v>1038</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101" s="4">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="I101" s="4">
+        <v>0.98670000000000002</v>
+      </c>
+      <c r="J101" s="5">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B102" t="s">
+        <v>42</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102">
+        <v>2919</v>
+      </c>
+      <c r="E102">
+        <v>148</v>
+      </c>
+      <c r="F102">
+        <v>18</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102" s="4">
+        <v>5.0700000000000002E-2</v>
+      </c>
+      <c r="I102" s="4">
+        <v>0.1216</v>
+      </c>
+      <c r="J102" s="4">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B103" t="s">
+        <v>37</v>
+      </c>
+      <c r="C103">
+        <v>5</v>
+      </c>
+      <c r="D103">
+        <v>4448</v>
+      </c>
+      <c r="E103">
+        <v>85</v>
+      </c>
+      <c r="F103">
+        <v>73</v>
+      </c>
+      <c r="G103">
+        <v>6</v>
+      </c>
+      <c r="H103" s="4">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="I103" s="4">
+        <v>0.85880000000000001</v>
+      </c>
+      <c r="J103" s="5">
+        <v>8.2199999999999995E-2</v>
+      </c>
+      <c r="K103" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B104" t="s">
+        <v>28</v>
+      </c>
+      <c r="C104">
+        <v>11</v>
+      </c>
+      <c r="D104">
+        <v>66103</v>
+      </c>
+      <c r="E104">
+        <v>1741</v>
+      </c>
+      <c r="F104">
+        <v>372</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104" s="4">
+        <v>2.63E-2</v>
+      </c>
+      <c r="I104" s="4">
+        <v>0.2137</v>
+      </c>
+      <c r="J104" s="4">
+        <v>0</v>
+      </c>
+      <c r="K104" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B105" t="s">
+        <v>38</v>
+      </c>
+      <c r="C105">
+        <v>10</v>
+      </c>
+      <c r="D105">
+        <v>13227</v>
+      </c>
+      <c r="E105">
+        <v>800</v>
+      </c>
+      <c r="F105">
+        <v>337</v>
+      </c>
+      <c r="G105">
+        <v>4</v>
+      </c>
+      <c r="H105" s="4">
+        <v>6.0499999999999998E-2</v>
+      </c>
+      <c r="I105" s="4">
+        <v>0.42130000000000001</v>
+      </c>
+      <c r="J105" s="4">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="K105" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B106" t="s">
+        <v>39</v>
+      </c>
+      <c r="C106">
+        <v>20</v>
+      </c>
+      <c r="D106">
+        <v>65296</v>
+      </c>
+      <c r="E106">
+        <v>2492</v>
+      </c>
+      <c r="F106">
+        <v>603</v>
+      </c>
+      <c r="G106">
+        <v>45</v>
+      </c>
+      <c r="H106" s="4">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="I106" s="4">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="J106" s="4">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="K106" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B107" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107">
+        <v>12</v>
+      </c>
+      <c r="D107">
+        <v>47824</v>
+      </c>
+      <c r="E107">
+        <v>1729</v>
+      </c>
+      <c r="F107">
+        <v>532</v>
+      </c>
+      <c r="G107">
+        <v>62</v>
+      </c>
+      <c r="H107" s="4">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="I107" s="4">
+        <v>0.30769999999999997</v>
+      </c>
+      <c r="J107" s="4">
+        <v>0.11650000000000001</v>
+      </c>
+      <c r="K107" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C108">
+        <v>9</v>
+      </c>
+      <c r="D108">
+        <v>46380</v>
+      </c>
+      <c r="E108">
+        <v>1320</v>
+      </c>
+      <c r="F108">
+        <v>1117</v>
+      </c>
+      <c r="G108">
+        <v>5</v>
+      </c>
+      <c r="H108" s="5">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="I108" s="4">
+        <v>0.84619999999999995</v>
+      </c>
+      <c r="J108" s="4">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="K108" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B109" t="s">
+        <v>30</v>
+      </c>
+      <c r="C109">
+        <v>8</v>
+      </c>
+      <c r="D109">
+        <v>18049</v>
+      </c>
+      <c r="E109">
+        <v>542</v>
+      </c>
+      <c r="F109">
+        <v>498</v>
+      </c>
+      <c r="G109">
+        <v>16</v>
+      </c>
+      <c r="H109" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="I109" s="4">
+        <v>0.91879999999999995</v>
+      </c>
+      <c r="J109" s="5">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="K109" s="3">
+        <v>3.1250000000000001E-4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B110" t="s">
+        <v>36</v>
+      </c>
+      <c r="C110">
+        <v>8</v>
+      </c>
+      <c r="D110">
+        <v>30383</v>
+      </c>
+      <c r="E110">
+        <v>839</v>
+      </c>
+      <c r="F110">
+        <v>341</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110" s="5">
+        <v>2.76E-2</v>
+      </c>
+      <c r="I110" s="4">
+        <v>0.40639999999999998</v>
+      </c>
+      <c r="J110" s="5">
+        <v>0</v>
+      </c>
+      <c r="K110" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B111" t="s">
+        <v>32</v>
+      </c>
+      <c r="C111">
+        <v>47</v>
+      </c>
+      <c r="D111">
+        <v>338</v>
+      </c>
+      <c r="E111">
+        <v>338</v>
+      </c>
+      <c r="F111">
+        <v>10</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111" s="4">
+        <v>1</v>
+      </c>
+      <c r="I111" s="4">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="J111" s="4">
+        <v>0</v>
+      </c>
+      <c r="K111" s="3">
+        <v>4.2824074074074075E-4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B112" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112">
+        <v>8</v>
+      </c>
+      <c r="D112">
+        <v>21157</v>
+      </c>
+      <c r="E112">
+        <v>891</v>
+      </c>
+      <c r="F112">
+        <v>727</v>
+      </c>
+      <c r="G112">
+        <v>43</v>
+      </c>
+      <c r="H112" s="4">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="I112" s="4">
+        <v>0.81589999999999996</v>
+      </c>
+      <c r="J112" s="4">
+        <v>5.91E-2</v>
+      </c>
+      <c r="K112" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B113" t="s">
+        <v>35</v>
+      </c>
+      <c r="C113">
+        <v>15</v>
+      </c>
+      <c r="D113">
+        <v>52146</v>
+      </c>
+      <c r="E113">
+        <v>2528</v>
+      </c>
+      <c r="F113">
+        <v>264</v>
+      </c>
+      <c r="G113">
+        <v>99</v>
+      </c>
+      <c r="H113" s="4">
+        <v>4.8500000000000001E-2</v>
+      </c>
+      <c r="I113" s="4">
+        <v>0.10440000000000001</v>
+      </c>
+      <c r="J113" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="K113" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B114" t="s">
+        <v>34</v>
+      </c>
+      <c r="C114">
+        <v>11</v>
+      </c>
+      <c r="D114">
+        <v>30853</v>
+      </c>
+      <c r="E114">
+        <v>812</v>
+      </c>
+      <c r="F114">
+        <v>707</v>
+      </c>
+      <c r="G114">
+        <v>46</v>
+      </c>
+      <c r="H114" s="4">
+        <v>2.63E-2</v>
+      </c>
+      <c r="I114" s="4">
+        <v>0.87070000000000003</v>
+      </c>
+      <c r="J114" s="4">
+        <v>6.5100000000000005E-2</v>
+      </c>
+      <c r="K114" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B115" t="s">
+        <v>33</v>
+      </c>
+      <c r="C115">
+        <v>7</v>
+      </c>
+      <c r="D115">
+        <v>5711</v>
+      </c>
+      <c r="E115">
+        <v>172</v>
+      </c>
+      <c r="F115">
+        <v>20</v>
+      </c>
+      <c r="G115">
+        <v>5</v>
+      </c>
+      <c r="H115" s="4">
+        <v>3.0099999999999998E-2</v>
+      </c>
+      <c r="I115" s="4">
+        <v>0.1163</v>
+      </c>
+      <c r="J115" s="5">
+        <v>4.3099999999999999E-2</v>
+      </c>
+      <c r="K115" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B116" t="s">
+        <v>38</v>
+      </c>
+      <c r="C116">
+        <v>11</v>
+      </c>
+      <c r="D116">
+        <v>11408</v>
+      </c>
+      <c r="E116">
+        <v>739</v>
+      </c>
+      <c r="F116">
+        <v>244</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116" s="4">
+        <v>6.4799999999999996E-2</v>
+      </c>
+      <c r="I116" s="4">
+        <v>0.33019999999999999</v>
+      </c>
+      <c r="J116" s="4">
+        <v>0</v>
+      </c>
+      <c r="K116" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B117" t="s">
+        <v>39</v>
+      </c>
+      <c r="C117">
+        <v>21</v>
+      </c>
+      <c r="D117">
+        <v>51732</v>
+      </c>
+      <c r="E117">
+        <v>2145</v>
+      </c>
+      <c r="F117">
+        <v>567</v>
+      </c>
+      <c r="G117">
+        <v>54</v>
+      </c>
+      <c r="H117" s="4">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="I117" s="4">
+        <v>0.26429999999999998</v>
+      </c>
+      <c r="J117" s="4">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="K117" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B118" t="s">
+        <v>27</v>
+      </c>
+      <c r="C118">
+        <v>9</v>
+      </c>
+      <c r="D118">
+        <v>42831</v>
+      </c>
+      <c r="E118">
+        <v>923</v>
+      </c>
+      <c r="F118">
+        <v>721</v>
+      </c>
+      <c r="G118">
+        <v>7</v>
+      </c>
+      <c r="H118" s="4">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="I118" s="4">
+        <v>0.78110000000000002</v>
+      </c>
+      <c r="J118" s="5">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="K118" s="3">
+        <v>2.7777777777777778E-4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B119" t="s">
+        <v>41</v>
+      </c>
+      <c r="C119">
+        <v>6</v>
+      </c>
+      <c r="D119">
+        <v>40629</v>
+      </c>
+      <c r="E119">
+        <v>779</v>
+      </c>
+      <c r="F119">
+        <v>765</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119" s="4">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="I119" s="4">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="J119" s="4">
+        <v>0</v>
+      </c>
+      <c r="K119" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B120" t="s">
+        <v>42</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+      <c r="D120">
+        <v>2386</v>
+      </c>
+      <c r="E120">
+        <v>123</v>
+      </c>
+      <c r="F120">
+        <v>15</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+      <c r="H120" s="4">
+        <v>5.16E-2</v>
+      </c>
+      <c r="I120" s="4">
+        <v>0.122</v>
+      </c>
+      <c r="J120" s="4">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="K120" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B121" t="s">
+        <v>31</v>
+      </c>
+      <c r="C121">
+        <v>9</v>
+      </c>
+      <c r="D121">
+        <v>20047</v>
+      </c>
+      <c r="E121">
+        <v>918</v>
+      </c>
+      <c r="F121">
+        <v>770</v>
+      </c>
+      <c r="G121">
+        <v>30</v>
+      </c>
+      <c r="H121" s="4">
+        <v>4.58E-2</v>
+      </c>
+      <c r="I121" s="4">
+        <v>0.83879999999999999</v>
+      </c>
+      <c r="J121" s="5">
+        <v>3.9E-2</v>
+      </c>
+      <c r="K121" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B122" t="s">
+        <v>36</v>
+      </c>
+      <c r="C122">
+        <v>9</v>
+      </c>
+      <c r="D122">
+        <v>29321</v>
+      </c>
+      <c r="E122">
+        <v>822</v>
+      </c>
+      <c r="F122">
+        <v>262</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122" s="4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I122" s="4">
+        <v>0.31869999999999998</v>
+      </c>
+      <c r="J122" s="4">
+        <v>0</v>
+      </c>
+      <c r="K122" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B123" t="s">
+        <v>37</v>
+      </c>
+      <c r="C123">
+        <v>3</v>
+      </c>
+      <c r="D123">
+        <v>3533</v>
+      </c>
+      <c r="E123">
+        <v>84</v>
+      </c>
+      <c r="F123">
+        <v>77</v>
+      </c>
+      <c r="G123">
+        <v>3</v>
+      </c>
+      <c r="H123" s="4">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="I123" s="4">
+        <v>0.91669999999999996</v>
+      </c>
+      <c r="J123" s="4">
+        <v>3.9E-2</v>
+      </c>
+      <c r="K123" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B124" t="s">
+        <v>29</v>
+      </c>
+      <c r="C124">
+        <v>12</v>
+      </c>
+      <c r="D124">
+        <v>48950</v>
+      </c>
+      <c r="E124">
+        <v>1746</v>
+      </c>
+      <c r="F124">
+        <v>530</v>
+      </c>
+      <c r="G124">
+        <v>30</v>
+      </c>
+      <c r="H124" s="4">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="I124" s="4">
+        <v>0.30359999999999998</v>
+      </c>
+      <c r="J124" s="4">
+        <v>5.6599999999999998E-2</v>
+      </c>
+      <c r="K124" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B125" t="s">
+        <v>33</v>
+      </c>
+      <c r="C125">
+        <v>8</v>
+      </c>
+      <c r="D125">
+        <v>6299</v>
+      </c>
+      <c r="E125">
+        <v>314</v>
+      </c>
+      <c r="F125">
+        <v>52</v>
+      </c>
+      <c r="G125">
+        <v>10</v>
+      </c>
+      <c r="H125" s="5">
+        <v>4.9799999999999997E-2</v>
+      </c>
+      <c r="I125" s="4">
+        <v>0.1656</v>
+      </c>
+      <c r="J125" s="5">
+        <v>6.13E-2</v>
+      </c>
+      <c r="K125" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B126" t="s">
+        <v>32</v>
+      </c>
+      <c r="C126">
+        <v>51</v>
+      </c>
+      <c r="D126">
+        <v>545</v>
+      </c>
+      <c r="E126">
+        <v>545</v>
+      </c>
+      <c r="F126">
+        <v>5</v>
+      </c>
+      <c r="G126">
+        <v>2</v>
+      </c>
+      <c r="H126" s="4">
+        <v>1</v>
+      </c>
+      <c r="I126" s="4">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="J126" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="K126" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B127" t="s">
+        <v>28</v>
+      </c>
+      <c r="C127">
+        <v>11</v>
+      </c>
+      <c r="D127">
+        <v>47963</v>
+      </c>
+      <c r="E127">
+        <v>1491</v>
+      </c>
+      <c r="F127">
+        <v>243</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127" s="4">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="I127" s="4">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="J127" s="4">
+        <v>0</v>
+      </c>
+      <c r="K127" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B128" t="s">
+        <v>34</v>
+      </c>
+      <c r="C128">
+        <v>11</v>
+      </c>
+      <c r="D128">
+        <v>26644</v>
+      </c>
+      <c r="E128">
+        <v>881</v>
+      </c>
+      <c r="F128">
+        <v>718</v>
+      </c>
+      <c r="G128">
+        <v>41</v>
+      </c>
+      <c r="H128" s="4">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="I128" s="5">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="J128" s="5">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="K128" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B129" t="s">
+        <v>30</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+      <c r="D129">
+        <v>89</v>
+      </c>
+      <c r="E129">
+        <v>3</v>
+      </c>
+      <c r="F129">
+        <v>3</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129" s="4">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="I129" s="4">
+        <v>1</v>
+      </c>
+      <c r="J129" s="4">
+        <v>0</v>
+      </c>
+      <c r="K129" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B130" t="s">
+        <v>35</v>
+      </c>
+      <c r="C130">
+        <v>15</v>
+      </c>
+      <c r="D130">
+        <v>60843</v>
+      </c>
+      <c r="E130">
+        <v>2182</v>
+      </c>
+      <c r="F130">
+        <v>187</v>
+      </c>
+      <c r="G130">
+        <v>66</v>
+      </c>
+      <c r="H130" s="4">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="I130" s="4">
+        <v>8.5699999999999998E-2</v>
+      </c>
+      <c r="J130" s="4">
+        <v>0.35289999999999999</v>
+      </c>
+      <c r="K130" s="3">
+        <v>6.2500000000000001E-4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,21 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A2BC58-2B6D-4041-8000-2042C83BCB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F377EE5-82C0-48F4-A5CA-4C080AB126C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
-    <sheet name="Funil_3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="32">
   <si>
     <t>Data</t>
   </si>
@@ -104,6 +116,21 @@
   <si>
     <t>Locator_Template</t>
   </si>
+  <si>
+    <t>Logados</t>
+  </si>
+  <si>
+    <t>Cpc</t>
+  </si>
+  <si>
+    <t>Loc</t>
+  </si>
+  <si>
+    <t>Conver</t>
+  </si>
+  <si>
+    <t>SIMPLIC_FASE2</t>
+  </si>
 </sst>
 </file>
 
@@ -161,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -170,6 +197,7 @@
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4787,18 +4815,401 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FFF5342-4B63-4B01-A332-A226EA58A2DA}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0630EBC7-33B4-47C2-99A0-E48DD1341355}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="6">
+        <v>130813</v>
+      </c>
+      <c r="D2">
+        <v>28</v>
+      </c>
+      <c r="E2" s="6">
+        <v>80762</v>
+      </c>
+      <c r="F2" s="6">
+        <v>1085</v>
+      </c>
+      <c r="G2" s="6">
+        <v>229</v>
+      </c>
+      <c r="H2" s="6">
+        <v>74</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1.34E-2</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.21110000000000001</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0.3231</v>
+      </c>
+      <c r="L2" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="6">
+        <v>108263</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3" s="6">
+        <v>94611</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1064</v>
+      </c>
+      <c r="G3" s="6">
+        <v>174</v>
+      </c>
+      <c r="H3" s="6">
+        <v>28</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1.12E-2</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.16350000000000001</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0.16089999999999999</v>
+      </c>
+      <c r="L3" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="6">
+        <v>194003</v>
+      </c>
+      <c r="D4">
+        <v>31</v>
+      </c>
+      <c r="E4" s="6">
+        <v>73894</v>
+      </c>
+      <c r="F4" s="6">
+        <v>1205</v>
+      </c>
+      <c r="G4" s="6">
+        <v>190</v>
+      </c>
+      <c r="H4" s="6">
+        <v>66</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.15770000000000001</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0.34739999999999999</v>
+      </c>
+      <c r="L4" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46177</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="6">
+        <v>51583</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5" s="6">
+        <v>27615</v>
+      </c>
+      <c r="F5" s="6">
+        <v>352</v>
+      </c>
+      <c r="G5" s="6">
+        <v>60</v>
+      </c>
+      <c r="H5" s="6">
+        <v>22</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.17050000000000001</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0.36670000000000003</v>
+      </c>
+      <c r="L5" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="6">
+        <v>166160</v>
+      </c>
+      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="E6" s="6">
+        <v>93099</v>
+      </c>
+      <c r="F6" s="6">
+        <v>744</v>
+      </c>
+      <c r="G6" s="6">
+        <v>139</v>
+      </c>
+      <c r="H6" s="6">
+        <v>49</v>
+      </c>
+      <c r="I6" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.18679999999999999</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0.35249999999999998</v>
+      </c>
+      <c r="L6" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="6">
+        <v>192383</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6">
+        <v>5440</v>
+      </c>
+      <c r="F7" s="6">
+        <v>71</v>
+      </c>
+      <c r="G7" s="6">
+        <v>11</v>
+      </c>
+      <c r="H7" s="6">
+        <v>2</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.15490000000000001</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0.18179999999999999</v>
+      </c>
+      <c r="L7" s="3">
+        <v>8.564814814814815E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="6">
+        <v>192383</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8" s="6">
+        <v>74990</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1043</v>
+      </c>
+      <c r="G8" s="6">
+        <v>177</v>
+      </c>
+      <c r="H8" s="6">
+        <v>55</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.16969999999999999</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0.31069999999999998</v>
+      </c>
+      <c r="L8" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="6">
+        <v>102135</v>
+      </c>
+      <c r="D9">
+        <v>20</v>
+      </c>
+      <c r="E9" s="6">
+        <v>65296</v>
+      </c>
+      <c r="F9" s="6">
+        <v>967</v>
+      </c>
+      <c r="G9" s="6">
+        <v>137</v>
+      </c>
+      <c r="H9" s="6">
+        <v>42</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.14169999999999999</v>
+      </c>
+      <c r="K9" s="4">
+        <v>0.30659999999999998</v>
+      </c>
+      <c r="L9" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="6">
+        <v>186791</v>
+      </c>
+      <c r="D10">
+        <v>21</v>
+      </c>
+      <c r="E10" s="6">
+        <v>62106</v>
+      </c>
+      <c r="F10" s="6">
+        <v>899</v>
+      </c>
+      <c r="G10" s="6">
+        <v>183</v>
+      </c>
+      <c r="H10" s="6">
+        <v>58</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2036</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0.31690000000000002</v>
+      </c>
+      <c r="L10" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F377EE5-82C0-48F4-A5CA-4C080AB126C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C945BD-6068-4723-A263-AF8AF4A01AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="33">
   <si>
     <t>Data</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>SIMPLIC_FASE2</t>
+  </si>
+  <si>
+    <t>Locator_CPF_Template</t>
   </si>
 </sst>
 </file>
@@ -502,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W62"/>
+  <dimension ref="A1:W82"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -3604,13 +3607,13 @@
         <v>311</v>
       </c>
       <c r="K45">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L45">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N45">
         <v>2</v>
@@ -3619,22 +3622,22 @@
         <v>6.5972222222222224E-4</v>
       </c>
       <c r="P45" s="3">
-        <v>1.0185185185185184E-3</v>
+        <v>1.2731481481481483E-3</v>
       </c>
       <c r="Q45" s="4">
         <v>1.7500000000000002E-2</v>
       </c>
       <c r="R45" s="4">
-        <v>0.12859999999999999</v>
+        <v>0.1318</v>
       </c>
       <c r="S45" s="5">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="T45">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="U45" s="4">
-        <v>0.53129999999999999</v>
+        <v>0.51219999999999999</v>
       </c>
       <c r="V45" s="4">
         <v>1</v>
@@ -3666,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>11854</v>
+        <v>11986</v>
       </c>
       <c r="J46">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K46">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L46">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -3684,25 +3687,25 @@
         <v>0</v>
       </c>
       <c r="O46" s="3">
-        <v>7.6388888888888893E-4</v>
+        <v>7.5231481481481482E-4</v>
       </c>
       <c r="P46" t="s">
         <v>24</v>
       </c>
       <c r="Q46" s="4">
-        <v>1.4999999999999999E-2</v>
+        <v>1.54E-2</v>
       </c>
       <c r="R46" s="4">
-        <v>0.1517</v>
+        <v>0.1522</v>
       </c>
       <c r="S46" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="U46" s="5">
+        <v>1</v>
       </c>
       <c r="V46" t="s">
         <v>25</v>
@@ -4806,6 +4809,1366 @@
       </c>
       <c r="V62" s="4">
         <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B63">
+        <v>8</v>
+      </c>
+      <c r="C63">
+        <v>168</v>
+      </c>
+      <c r="D63">
+        <v>169</v>
+      </c>
+      <c r="E63" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63">
+        <v>75250</v>
+      </c>
+      <c r="G63">
+        <v>38</v>
+      </c>
+      <c r="H63">
+        <v>4</v>
+      </c>
+      <c r="I63">
+        <v>3708</v>
+      </c>
+      <c r="J63">
+        <v>434</v>
+      </c>
+      <c r="K63">
+        <v>18</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>12</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P63" s="3">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="Q63" s="4">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="R63" s="4">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="S63" s="5">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>6</v>
+      </c>
+      <c r="U63" s="4">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="V63" s="4">
+        <v>0.76470000000000005</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B64">
+        <v>9</v>
+      </c>
+      <c r="C64">
+        <v>166</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
+        <v>26</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>2</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>3</v>
+      </c>
+      <c r="J64">
+        <v>2</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P64" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q64" s="4">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="R64" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="S64" s="5">
+        <v>1</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64" t="s">
+        <v>25</v>
+      </c>
+      <c r="W64">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B65">
+        <v>9</v>
+      </c>
+      <c r="C65">
+        <v>168</v>
+      </c>
+      <c r="D65">
+        <v>169</v>
+      </c>
+      <c r="E65" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65">
+        <v>75250</v>
+      </c>
+      <c r="G65">
+        <v>38</v>
+      </c>
+      <c r="H65">
+        <v>4</v>
+      </c>
+      <c r="I65">
+        <v>13977</v>
+      </c>
+      <c r="J65">
+        <v>1034</v>
+      </c>
+      <c r="K65">
+        <v>65</v>
+      </c>
+      <c r="L65">
+        <v>2</v>
+      </c>
+      <c r="M65">
+        <v>33</v>
+      </c>
+      <c r="N65">
+        <v>5</v>
+      </c>
+      <c r="O65" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="P65" s="3">
+        <v>1.25E-3</v>
+      </c>
+      <c r="Q65" s="4">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="R65" s="4">
+        <v>6.2899999999999998E-2</v>
+      </c>
+      <c r="S65" s="4">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="T65">
+        <v>30</v>
+      </c>
+      <c r="U65" s="4">
+        <v>0.47620000000000001</v>
+      </c>
+      <c r="V65" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B66">
+        <v>10</v>
+      </c>
+      <c r="C66">
+        <v>166</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s">
+        <v>26</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>3</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="P66" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q66" s="4">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="R66" s="5">
+        <v>0</v>
+      </c>
+      <c r="S66" t="s">
+        <v>25</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66" t="s">
+        <v>25</v>
+      </c>
+      <c r="W66">
+        <v>2.75E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B67">
+        <v>10</v>
+      </c>
+      <c r="C67">
+        <v>168</v>
+      </c>
+      <c r="D67">
+        <v>169</v>
+      </c>
+      <c r="E67" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67">
+        <v>75250</v>
+      </c>
+      <c r="G67">
+        <v>38</v>
+      </c>
+      <c r="H67">
+        <v>5</v>
+      </c>
+      <c r="I67">
+        <v>11446</v>
+      </c>
+      <c r="J67">
+        <v>870</v>
+      </c>
+      <c r="K67">
+        <v>43</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>28</v>
+      </c>
+      <c r="N67">
+        <v>9</v>
+      </c>
+      <c r="O67" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="P67" s="3">
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="R67" s="4">
+        <v>4.9399999999999999E-2</v>
+      </c>
+      <c r="S67" s="4">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="T67">
+        <v>14</v>
+      </c>
+      <c r="U67" s="4">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="V67" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B68">
+        <v>11</v>
+      </c>
+      <c r="C68">
+        <v>159</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>32</v>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P68" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>1</v>
+      </c>
+      <c r="R68" s="5">
+        <v>0</v>
+      </c>
+      <c r="S68" t="s">
+        <v>25</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68" t="s">
+        <v>25</v>
+      </c>
+      <c r="W68">
+        <v>2.75E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B69">
+        <v>11</v>
+      </c>
+      <c r="C69">
+        <v>166</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>26</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>3</v>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P69" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q69" s="4">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="R69" s="5">
+        <v>0</v>
+      </c>
+      <c r="S69" t="s">
+        <v>25</v>
+      </c>
+      <c r="T69">
+        <v>0</v>
+      </c>
+      <c r="U69" t="s">
+        <v>25</v>
+      </c>
+      <c r="W69">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B70">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>168</v>
+      </c>
+      <c r="D70">
+        <v>169</v>
+      </c>
+      <c r="E70" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70">
+        <v>75250</v>
+      </c>
+      <c r="G70">
+        <v>38</v>
+      </c>
+      <c r="H70">
+        <v>4</v>
+      </c>
+      <c r="I70">
+        <v>7294</v>
+      </c>
+      <c r="J70">
+        <v>568</v>
+      </c>
+      <c r="K70">
+        <v>37</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>25</v>
+      </c>
+      <c r="N70">
+        <v>4</v>
+      </c>
+      <c r="O70" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="P70" s="3">
+        <v>1.3194444444444445E-3</v>
+      </c>
+      <c r="Q70" s="4">
+        <v>7.7899999999999997E-2</v>
+      </c>
+      <c r="R70" s="4">
+        <v>6.5100000000000005E-2</v>
+      </c>
+      <c r="S70" s="5">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>12</v>
+      </c>
+      <c r="U70" s="4">
+        <v>0.32429999999999998</v>
+      </c>
+      <c r="V70" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B71">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>168</v>
+      </c>
+      <c r="D71">
+        <v>169</v>
+      </c>
+      <c r="E71" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71">
+        <v>75250</v>
+      </c>
+      <c r="G71">
+        <v>38</v>
+      </c>
+      <c r="H71">
+        <v>3</v>
+      </c>
+      <c r="I71">
+        <v>8219</v>
+      </c>
+      <c r="J71">
+        <v>606</v>
+      </c>
+      <c r="K71">
+        <v>43</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>23</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>1.5046296296296297E-4</v>
+      </c>
+      <c r="P71" s="3">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="Q71" s="4">
+        <v>7.3700000000000002E-2</v>
+      </c>
+      <c r="R71" s="4">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="S71" s="5">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>20</v>
+      </c>
+      <c r="U71" s="4">
+        <v>0.46510000000000001</v>
+      </c>
+      <c r="V71" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B72">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>168</v>
+      </c>
+      <c r="D72">
+        <v>169</v>
+      </c>
+      <c r="E72" t="s">
+        <v>23</v>
+      </c>
+      <c r="F72">
+        <v>75250</v>
+      </c>
+      <c r="G72">
+        <v>38</v>
+      </c>
+      <c r="H72">
+        <v>2</v>
+      </c>
+      <c r="I72">
+        <v>8463</v>
+      </c>
+      <c r="J72">
+        <v>855</v>
+      </c>
+      <c r="K72">
+        <v>56</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>2</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P72" s="3">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="Q72" s="4">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="R72" s="4">
+        <v>6.5500000000000003E-2</v>
+      </c>
+      <c r="S72" s="5">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>54</v>
+      </c>
+      <c r="U72" s="4">
+        <v>0.96430000000000005</v>
+      </c>
+      <c r="V72" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B73">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>168</v>
+      </c>
+      <c r="D73">
+        <v>169</v>
+      </c>
+      <c r="E73" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73">
+        <v>75250</v>
+      </c>
+      <c r="G73">
+        <v>38</v>
+      </c>
+      <c r="H73">
+        <v>6</v>
+      </c>
+      <c r="I73">
+        <v>10798</v>
+      </c>
+      <c r="J73">
+        <v>1334</v>
+      </c>
+      <c r="K73">
+        <v>74</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>57</v>
+      </c>
+      <c r="N73">
+        <v>3</v>
+      </c>
+      <c r="O73" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="P73" s="3">
+        <v>1.0879629629629629E-3</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>0.1235</v>
+      </c>
+      <c r="R73" s="4">
+        <v>5.5500000000000001E-2</v>
+      </c>
+      <c r="S73" s="4">
+        <v>1.35E-2</v>
+      </c>
+      <c r="T73">
+        <v>16</v>
+      </c>
+      <c r="U73" s="4">
+        <v>0.21920000000000001</v>
+      </c>
+      <c r="V73" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B74">
+        <v>15</v>
+      </c>
+      <c r="C74">
+        <v>168</v>
+      </c>
+      <c r="D74">
+        <v>169</v>
+      </c>
+      <c r="E74" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74">
+        <v>75250</v>
+      </c>
+      <c r="G74">
+        <v>38</v>
+      </c>
+      <c r="H74">
+        <v>6</v>
+      </c>
+      <c r="I74">
+        <v>8353</v>
+      </c>
+      <c r="J74">
+        <v>1326</v>
+      </c>
+      <c r="K74">
+        <v>64</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>45</v>
+      </c>
+      <c r="N74">
+        <v>4</v>
+      </c>
+      <c r="O74" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="P74" s="3">
+        <v>1.5740740740740741E-3</v>
+      </c>
+      <c r="Q74" s="4">
+        <v>0.15870000000000001</v>
+      </c>
+      <c r="R74" s="4">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="S74" s="5">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>19</v>
+      </c>
+      <c r="U74" s="4">
+        <v>0.2969</v>
+      </c>
+      <c r="V74" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B75">
+        <v>16</v>
+      </c>
+      <c r="C75">
+        <v>168</v>
+      </c>
+      <c r="D75">
+        <v>169</v>
+      </c>
+      <c r="E75" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75">
+        <v>75250</v>
+      </c>
+      <c r="G75">
+        <v>38</v>
+      </c>
+      <c r="H75">
+        <v>6</v>
+      </c>
+      <c r="I75">
+        <v>6848</v>
+      </c>
+      <c r="J75">
+        <v>732</v>
+      </c>
+      <c r="K75">
+        <v>40</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>33</v>
+      </c>
+      <c r="N75">
+        <v>4</v>
+      </c>
+      <c r="O75" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P75" s="3">
+        <v>1.8287037037037037E-3</v>
+      </c>
+      <c r="Q75" s="4">
+        <v>0.1069</v>
+      </c>
+      <c r="R75" s="4">
+        <v>5.4600000000000003E-2</v>
+      </c>
+      <c r="S75" s="5">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>7</v>
+      </c>
+      <c r="U75" s="4">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="V75" s="4">
+        <v>0.54290000000000005</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B76">
+        <v>17</v>
+      </c>
+      <c r="C76">
+        <v>168</v>
+      </c>
+      <c r="D76">
+        <v>169</v>
+      </c>
+      <c r="E76" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76">
+        <v>75250</v>
+      </c>
+      <c r="G76">
+        <v>38</v>
+      </c>
+      <c r="H76">
+        <v>3</v>
+      </c>
+      <c r="I76">
+        <v>6029</v>
+      </c>
+      <c r="J76">
+        <v>822</v>
+      </c>
+      <c r="K76">
+        <v>58</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>37</v>
+      </c>
+      <c r="N76">
+        <v>8</v>
+      </c>
+      <c r="O76" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="P76" s="3">
+        <v>1.8634259259259259E-3</v>
+      </c>
+      <c r="Q76" s="4">
+        <v>0.1363</v>
+      </c>
+      <c r="R76" s="4">
+        <v>7.0599999999999996E-2</v>
+      </c>
+      <c r="S76" s="5">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>21</v>
+      </c>
+      <c r="U76" s="4">
+        <v>0.36209999999999998</v>
+      </c>
+      <c r="V76" s="4">
+        <v>0.42620000000000002</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B77">
+        <v>18</v>
+      </c>
+      <c r="C77">
+        <v>168</v>
+      </c>
+      <c r="D77">
+        <v>169</v>
+      </c>
+      <c r="E77" t="s">
+        <v>23</v>
+      </c>
+      <c r="F77">
+        <v>75250</v>
+      </c>
+      <c r="G77">
+        <v>38</v>
+      </c>
+      <c r="H77">
+        <v>3</v>
+      </c>
+      <c r="I77">
+        <v>6034</v>
+      </c>
+      <c r="J77">
+        <v>933</v>
+      </c>
+      <c r="K77">
+        <v>52</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>30</v>
+      </c>
+      <c r="N77">
+        <v>3</v>
+      </c>
+      <c r="O77" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="P77" s="3">
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="Q77" s="4">
+        <v>0.15459999999999999</v>
+      </c>
+      <c r="R77" s="4">
+        <v>5.57E-2</v>
+      </c>
+      <c r="S77" s="5">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>22</v>
+      </c>
+      <c r="U77" s="4">
+        <v>0.42309999999999998</v>
+      </c>
+      <c r="V77" s="4">
+        <v>0.48080000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B78">
+        <v>19</v>
+      </c>
+      <c r="C78">
+        <v>168</v>
+      </c>
+      <c r="D78">
+        <v>169</v>
+      </c>
+      <c r="E78" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78">
+        <v>75250</v>
+      </c>
+      <c r="G78">
+        <v>38</v>
+      </c>
+      <c r="H78">
+        <v>3</v>
+      </c>
+      <c r="I78">
+        <v>6195</v>
+      </c>
+      <c r="J78">
+        <v>767</v>
+      </c>
+      <c r="K78">
+        <v>21</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78">
+        <v>13</v>
+      </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
+      <c r="O78" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P78" s="3">
+        <v>1.724537037037037E-3</v>
+      </c>
+      <c r="Q78" s="4">
+        <v>0.12379999999999999</v>
+      </c>
+      <c r="R78" s="4">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="S78" s="4">
+        <v>4.7600000000000003E-2</v>
+      </c>
+      <c r="T78">
+        <v>7</v>
+      </c>
+      <c r="U78" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="V78" s="4">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B79">
+        <v>20</v>
+      </c>
+      <c r="C79">
+        <v>168</v>
+      </c>
+      <c r="D79">
+        <v>169</v>
+      </c>
+      <c r="E79" t="s">
+        <v>23</v>
+      </c>
+      <c r="F79">
+        <v>75250</v>
+      </c>
+      <c r="G79">
+        <v>38</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>3992</v>
+      </c>
+      <c r="J79">
+        <v>578</v>
+      </c>
+      <c r="K79">
+        <v>37</v>
+      </c>
+      <c r="L79">
+        <v>18</v>
+      </c>
+      <c r="M79">
+        <v>11</v>
+      </c>
+      <c r="N79">
+        <v>1</v>
+      </c>
+      <c r="O79" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="P79" s="3">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="Q79" s="4">
+        <v>0.14480000000000001</v>
+      </c>
+      <c r="R79" s="4">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="S79" s="4">
+        <v>0.48649999999999999</v>
+      </c>
+      <c r="T79">
+        <v>8</v>
+      </c>
+      <c r="U79" s="4">
+        <v>0.42109999999999997</v>
+      </c>
+      <c r="V79" s="4">
+        <v>0.33329999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B80">
+        <v>8</v>
+      </c>
+      <c r="C80">
+        <v>168</v>
+      </c>
+      <c r="D80">
+        <v>169</v>
+      </c>
+      <c r="E80" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80">
+        <v>75250</v>
+      </c>
+      <c r="G80">
+        <v>38</v>
+      </c>
+      <c r="H80">
+        <v>2</v>
+      </c>
+      <c r="I80">
+        <v>3846</v>
+      </c>
+      <c r="J80">
+        <v>358</v>
+      </c>
+      <c r="K80">
+        <v>15</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>12</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="P80" s="3">
+        <v>8.7962962962962962E-4</v>
+      </c>
+      <c r="Q80" s="4">
+        <v>9.3100000000000002E-2</v>
+      </c>
+      <c r="R80" s="4">
+        <v>4.19E-2</v>
+      </c>
+      <c r="S80" s="5">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>3</v>
+      </c>
+      <c r="U80" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="V80" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B81">
+        <v>9</v>
+      </c>
+      <c r="C81">
+        <v>168</v>
+      </c>
+      <c r="D81">
+        <v>169</v>
+      </c>
+      <c r="E81" t="s">
+        <v>23</v>
+      </c>
+      <c r="F81">
+        <v>75250</v>
+      </c>
+      <c r="G81">
+        <v>38</v>
+      </c>
+      <c r="H81">
+        <v>4</v>
+      </c>
+      <c r="I81">
+        <v>6619</v>
+      </c>
+      <c r="J81">
+        <v>745</v>
+      </c>
+      <c r="K81">
+        <v>45</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
+        <v>40</v>
+      </c>
+      <c r="N81">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P81" s="3">
+        <v>1.0995370370370371E-3</v>
+      </c>
+      <c r="Q81" s="4">
+        <v>0.11260000000000001</v>
+      </c>
+      <c r="R81" s="4">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="S81" s="4">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="T81">
+        <v>4</v>
+      </c>
+      <c r="U81" s="4">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="V81" s="4">
+        <v>0.61360000000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B82">
+        <v>10</v>
+      </c>
+      <c r="C82">
+        <v>168</v>
+      </c>
+      <c r="D82">
+        <v>169</v>
+      </c>
+      <c r="E82" t="s">
+        <v>23</v>
+      </c>
+      <c r="F82">
+        <v>75250</v>
+      </c>
+      <c r="G82">
+        <v>38</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>3780</v>
+      </c>
+      <c r="J82">
+        <v>512</v>
+      </c>
+      <c r="K82">
+        <v>12</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="P82" s="3">
+        <v>2.2800925925925927E-3</v>
+      </c>
+      <c r="Q82" s="4">
+        <v>0.13539999999999999</v>
+      </c>
+      <c r="R82" s="4">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="S82" s="5">
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <v>11</v>
+      </c>
+      <c r="U82" s="4">
+        <v>0.91669999999999996</v>
+      </c>
+      <c r="V82" s="4">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -4815,7 +6178,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FFF5342-4B63-4B01-A332-A226EA58A2DA}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -5209,6 +6572,44 @@
         <v>4.6296296296296298E-4</v>
       </c>
     </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11">
+        <v>48299</v>
+      </c>
+      <c r="D11">
+        <v>25</v>
+      </c>
+      <c r="E11">
+        <v>76114</v>
+      </c>
+      <c r="F11">
+        <v>1010</v>
+      </c>
+      <c r="G11">
+        <v>204</v>
+      </c>
+      <c r="H11" s="6">
+        <v>57</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0.27939999999999998</v>
+      </c>
+      <c r="L11" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C945BD-6068-4723-A263-AF8AF4A01AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578EA0A7-5089-49A5-AA64-B3441D621578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="33">
   <si>
     <t>Data</t>
   </si>
@@ -505,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W82"/>
+  <dimension ref="A1:W98"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -6129,13 +6129,13 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>3780</v>
+        <v>3787</v>
       </c>
       <c r="J82">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K82">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -6153,22 +6153,1107 @@
         <v>2.2800925925925927E-3</v>
       </c>
       <c r="Q82" s="4">
-        <v>0.13539999999999999</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="R82" s="4">
-        <v>2.3400000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="S82" s="5">
         <v>0</v>
       </c>
       <c r="T82">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U82" s="4">
-        <v>0.91669999999999996</v>
+        <v>0.92310000000000003</v>
       </c>
       <c r="V82" s="4">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B83">
+        <v>12</v>
+      </c>
+      <c r="C83">
+        <v>168</v>
+      </c>
+      <c r="D83">
+        <v>169</v>
+      </c>
+      <c r="E83" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83">
+        <v>23394</v>
+      </c>
+      <c r="G83">
+        <v>38</v>
+      </c>
+      <c r="H83">
+        <v>4</v>
+      </c>
+      <c r="I83">
+        <v>5551</v>
+      </c>
+      <c r="J83">
+        <v>445</v>
+      </c>
+      <c r="K83">
+        <v>19</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>18</v>
+      </c>
+      <c r="N83">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="P83" s="3">
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="Q83" s="4">
+        <v>8.0199999999999994E-2</v>
+      </c>
+      <c r="R83" s="4">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="S83" s="5">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>1</v>
+      </c>
+      <c r="U83" s="4">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="V83" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B84">
+        <v>13</v>
+      </c>
+      <c r="C84">
+        <v>168</v>
+      </c>
+      <c r="D84">
+        <v>169</v>
+      </c>
+      <c r="E84" t="s">
+        <v>23</v>
+      </c>
+      <c r="F84">
+        <v>23394</v>
+      </c>
+      <c r="G84">
+        <v>38</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>1018</v>
+      </c>
+      <c r="J84">
+        <v>101</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P84" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>9.9199999999999997E-2</v>
+      </c>
+      <c r="R84" s="4">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="S84" s="5">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>1</v>
+      </c>
+      <c r="U84" s="5">
+        <v>1</v>
+      </c>
+      <c r="V84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B85">
+        <v>14</v>
+      </c>
+      <c r="C85">
+        <v>168</v>
+      </c>
+      <c r="D85">
+        <v>169</v>
+      </c>
+      <c r="E85" t="s">
+        <v>23</v>
+      </c>
+      <c r="F85">
+        <v>23394</v>
+      </c>
+      <c r="G85">
+        <v>38</v>
+      </c>
+      <c r="H85">
+        <v>4</v>
+      </c>
+      <c r="I85">
+        <v>8121</v>
+      </c>
+      <c r="J85">
+        <v>706</v>
+      </c>
+      <c r="K85">
+        <v>21</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>21</v>
+      </c>
+      <c r="N85">
+        <v>5</v>
+      </c>
+      <c r="O85" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="P85" s="3">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="R85" s="4">
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="S85" s="5">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85" s="5">
+        <v>0</v>
+      </c>
+      <c r="V85" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B86">
+        <v>15</v>
+      </c>
+      <c r="C86">
+        <v>168</v>
+      </c>
+      <c r="D86">
+        <v>169</v>
+      </c>
+      <c r="E86" t="s">
+        <v>23</v>
+      </c>
+      <c r="F86">
+        <v>23394</v>
+      </c>
+      <c r="G86">
+        <v>38</v>
+      </c>
+      <c r="H86">
+        <v>3</v>
+      </c>
+      <c r="I86">
+        <v>8674</v>
+      </c>
+      <c r="J86">
+        <v>764</v>
+      </c>
+      <c r="K86">
+        <v>26</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>23</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="P86" s="3">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="Q86" s="4">
+        <v>8.8099999999999998E-2</v>
+      </c>
+      <c r="R86" s="4">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="S86" s="4">
+        <v>3.85E-2</v>
+      </c>
+      <c r="T86">
+        <v>2</v>
+      </c>
+      <c r="U86" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="V86" s="4">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B87">
+        <v>16</v>
+      </c>
+      <c r="C87">
+        <v>168</v>
+      </c>
+      <c r="D87">
+        <v>169</v>
+      </c>
+      <c r="E87" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87">
+        <v>23394</v>
+      </c>
+      <c r="G87">
+        <v>38</v>
+      </c>
+      <c r="H87">
+        <v>2</v>
+      </c>
+      <c r="I87">
+        <v>8515</v>
+      </c>
+      <c r="J87">
+        <v>985</v>
+      </c>
+      <c r="K87">
+        <v>28</v>
+      </c>
+      <c r="L87">
+        <v>2</v>
+      </c>
+      <c r="M87">
+        <v>9</v>
+      </c>
+      <c r="N87">
+        <v>3</v>
+      </c>
+      <c r="O87" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P87" s="3">
+        <v>2.2916666666666667E-3</v>
+      </c>
+      <c r="Q87" s="4">
+        <v>0.1157</v>
+      </c>
+      <c r="R87" s="4">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="S87" s="4">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="T87">
+        <v>17</v>
+      </c>
+      <c r="U87" s="4">
+        <v>0.65380000000000005</v>
+      </c>
+      <c r="V87" s="4">
+        <v>0.45450000000000002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B88">
+        <v>17</v>
+      </c>
+      <c r="C88">
+        <v>168</v>
+      </c>
+      <c r="D88">
+        <v>169</v>
+      </c>
+      <c r="E88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88">
+        <v>23394</v>
+      </c>
+      <c r="G88">
+        <v>38</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>7587</v>
+      </c>
+      <c r="J88">
+        <v>830</v>
+      </c>
+      <c r="K88">
+        <v>24</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P88" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q88" s="4">
+        <v>0.1094</v>
+      </c>
+      <c r="R88" s="4">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="S88" s="4">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="T88">
+        <v>23</v>
+      </c>
+      <c r="U88" s="5">
+        <v>1</v>
+      </c>
+      <c r="V88" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B89">
+        <v>18</v>
+      </c>
+      <c r="C89">
+        <v>168</v>
+      </c>
+      <c r="D89">
+        <v>169</v>
+      </c>
+      <c r="E89" t="s">
+        <v>23</v>
+      </c>
+      <c r="F89">
+        <v>23394</v>
+      </c>
+      <c r="G89">
+        <v>38</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>8197</v>
+      </c>
+      <c r="J89">
+        <v>896</v>
+      </c>
+      <c r="K89">
+        <v>31</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P89" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q89" s="4">
+        <v>0.10929999999999999</v>
+      </c>
+      <c r="R89" s="4">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="S89" s="4">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="T89">
+        <v>30</v>
+      </c>
+      <c r="U89" s="5">
+        <v>1</v>
+      </c>
+      <c r="V89" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B90">
+        <v>19</v>
+      </c>
+      <c r="C90">
+        <v>168</v>
+      </c>
+      <c r="D90">
+        <v>169</v>
+      </c>
+      <c r="E90" t="s">
+        <v>23</v>
+      </c>
+      <c r="F90">
+        <v>23394</v>
+      </c>
+      <c r="G90">
+        <v>38</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>7771</v>
+      </c>
+      <c r="J90">
+        <v>926</v>
+      </c>
+      <c r="K90">
+        <v>16</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P90" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q90" s="4">
+        <v>0.1192</v>
+      </c>
+      <c r="R90" s="4">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="S90" s="5">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>16</v>
+      </c>
+      <c r="U90" s="5">
+        <v>1</v>
+      </c>
+      <c r="V90" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B91">
+        <v>20</v>
+      </c>
+      <c r="C91">
+        <v>168</v>
+      </c>
+      <c r="D91">
+        <v>169</v>
+      </c>
+      <c r="E91" t="s">
+        <v>23</v>
+      </c>
+      <c r="F91">
+        <v>23394</v>
+      </c>
+      <c r="G91">
+        <v>38</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>4160</v>
+      </c>
+      <c r="J91">
+        <v>572</v>
+      </c>
+      <c r="K91">
+        <v>14</v>
+      </c>
+      <c r="L91">
+        <v>14</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="P91" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q91" s="4">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="R91" s="4">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="S91" s="5">
+        <v>1</v>
+      </c>
+      <c r="T91">
+        <v>0</v>
+      </c>
+      <c r="U91" t="s">
+        <v>25</v>
+      </c>
+      <c r="V91" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B92">
+        <v>8</v>
+      </c>
+      <c r="C92">
+        <v>168</v>
+      </c>
+      <c r="D92">
+        <v>169</v>
+      </c>
+      <c r="E92" t="s">
+        <v>23</v>
+      </c>
+      <c r="F92">
+        <v>23394</v>
+      </c>
+      <c r="G92">
+        <v>38</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>8022</v>
+      </c>
+      <c r="J92">
+        <v>524</v>
+      </c>
+      <c r="K92">
+        <v>20</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="P92" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q92" s="4">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="R92" s="4">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="S92" s="5">
+        <v>0</v>
+      </c>
+      <c r="T92">
+        <v>20</v>
+      </c>
+      <c r="U92" s="5">
+        <v>1</v>
+      </c>
+      <c r="V92" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B93">
+        <v>9</v>
+      </c>
+      <c r="C93">
+        <v>168</v>
+      </c>
+      <c r="D93">
+        <v>169</v>
+      </c>
+      <c r="E93" t="s">
+        <v>23</v>
+      </c>
+      <c r="F93">
+        <v>23394</v>
+      </c>
+      <c r="G93">
+        <v>38</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>8265</v>
+      </c>
+      <c r="J93">
+        <v>816</v>
+      </c>
+      <c r="K93">
+        <v>26</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="P93" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q93" s="4">
+        <v>9.8699999999999996E-2</v>
+      </c>
+      <c r="R93" s="4">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="S93" s="5">
+        <v>0</v>
+      </c>
+      <c r="T93">
+        <v>26</v>
+      </c>
+      <c r="U93" s="5">
+        <v>1</v>
+      </c>
+      <c r="V93" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B94">
+        <v>10</v>
+      </c>
+      <c r="C94">
+        <v>168</v>
+      </c>
+      <c r="D94">
+        <v>169</v>
+      </c>
+      <c r="E94" t="s">
+        <v>23</v>
+      </c>
+      <c r="F94">
+        <v>23394</v>
+      </c>
+      <c r="G94">
+        <v>38</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>2177</v>
+      </c>
+      <c r="J94">
+        <v>569</v>
+      </c>
+      <c r="K94">
+        <v>6</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="P94" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q94" s="4">
+        <v>0.26140000000000002</v>
+      </c>
+      <c r="R94" s="4">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="S94" s="5">
+        <v>0</v>
+      </c>
+      <c r="T94">
+        <v>6</v>
+      </c>
+      <c r="U94" s="5">
+        <v>1</v>
+      </c>
+      <c r="V94" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B95">
+        <v>11</v>
+      </c>
+      <c r="C95">
+        <v>168</v>
+      </c>
+      <c r="D95">
+        <v>169</v>
+      </c>
+      <c r="E95" t="s">
+        <v>23</v>
+      </c>
+      <c r="F95">
+        <v>23394</v>
+      </c>
+      <c r="G95">
+        <v>38</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>6103</v>
+      </c>
+      <c r="J95">
+        <v>561</v>
+      </c>
+      <c r="K95">
+        <v>19</v>
+      </c>
+      <c r="L95">
+        <v>2</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="P95" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q95" s="4">
+        <v>9.1899999999999996E-2</v>
+      </c>
+      <c r="R95" s="4">
+        <v>3.39E-2</v>
+      </c>
+      <c r="S95" s="4">
+        <v>0.1053</v>
+      </c>
+      <c r="T95">
+        <v>17</v>
+      </c>
+      <c r="U95" s="5">
+        <v>1</v>
+      </c>
+      <c r="V95" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B96">
+        <v>12</v>
+      </c>
+      <c r="C96">
+        <v>168</v>
+      </c>
+      <c r="D96">
+        <v>169</v>
+      </c>
+      <c r="E96" t="s">
+        <v>23</v>
+      </c>
+      <c r="F96">
+        <v>23394</v>
+      </c>
+      <c r="G96">
+        <v>38</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>5565</v>
+      </c>
+      <c r="J96">
+        <v>516</v>
+      </c>
+      <c r="K96">
+        <v>11</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="P96" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q96" s="4">
+        <v>9.2700000000000005E-2</v>
+      </c>
+      <c r="R96" s="4">
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="S96" s="4">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="T96">
+        <v>10</v>
+      </c>
+      <c r="U96" s="5">
+        <v>1</v>
+      </c>
+      <c r="V96" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B97">
+        <v>13</v>
+      </c>
+      <c r="C97">
+        <v>168</v>
+      </c>
+      <c r="D97">
+        <v>169</v>
+      </c>
+      <c r="E97" t="s">
+        <v>23</v>
+      </c>
+      <c r="F97">
+        <v>23394</v>
+      </c>
+      <c r="G97">
+        <v>38</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>1683</v>
+      </c>
+      <c r="J97">
+        <v>354</v>
+      </c>
+      <c r="K97">
+        <v>5</v>
+      </c>
+      <c r="L97">
+        <v>5</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="P97" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q97" s="4">
+        <v>0.21029999999999999</v>
+      </c>
+      <c r="R97" s="4">
+        <v>1.41E-2</v>
+      </c>
+      <c r="S97" s="5">
+        <v>1</v>
+      </c>
+      <c r="T97">
+        <v>0</v>
+      </c>
+      <c r="U97" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B98">
+        <v>8</v>
+      </c>
+      <c r="C98">
+        <v>168</v>
+      </c>
+      <c r="D98">
+        <v>169</v>
+      </c>
+      <c r="E98" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98">
+        <v>23394</v>
+      </c>
+      <c r="G98">
+        <v>38</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>7074</v>
+      </c>
+      <c r="J98">
+        <v>430</v>
+      </c>
+      <c r="K98">
+        <v>21</v>
+      </c>
+      <c r="L98">
+        <v>21</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="P98" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q98" s="4">
+        <v>6.08E-2</v>
+      </c>
+      <c r="R98" s="4">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="S98" s="5">
+        <v>1</v>
+      </c>
+      <c r="T98">
+        <v>0</v>
+      </c>
+      <c r="U98" t="s">
+        <v>25</v>
+      </c>
+      <c r="V98" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578EA0A7-5089-49A5-AA64-B3441D621578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C945BD-6068-4723-A263-AF8AF4A01AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="33">
   <si>
     <t>Data</t>
   </si>
@@ -505,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W98"/>
+  <dimension ref="A1:W82"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -6129,13 +6129,13 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>3787</v>
+        <v>3780</v>
       </c>
       <c r="J82">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="K82">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -6153,1107 +6153,22 @@
         <v>2.2800925925925927E-3</v>
       </c>
       <c r="Q82" s="4">
-        <v>0.13700000000000001</v>
+        <v>0.13539999999999999</v>
       </c>
       <c r="R82" s="4">
-        <v>2.5000000000000001E-2</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="S82" s="5">
         <v>0</v>
       </c>
       <c r="T82">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U82" s="4">
-        <v>0.92310000000000003</v>
+        <v>0.91669999999999996</v>
       </c>
       <c r="V82" s="4">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B83">
-        <v>12</v>
-      </c>
-      <c r="C83">
-        <v>168</v>
-      </c>
-      <c r="D83">
-        <v>169</v>
-      </c>
-      <c r="E83" t="s">
-        <v>23</v>
-      </c>
-      <c r="F83">
-        <v>23394</v>
-      </c>
-      <c r="G83">
-        <v>38</v>
-      </c>
-      <c r="H83">
-        <v>4</v>
-      </c>
-      <c r="I83">
-        <v>5551</v>
-      </c>
-      <c r="J83">
-        <v>445</v>
-      </c>
-      <c r="K83">
-        <v>19</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>18</v>
-      </c>
-      <c r="N83">
-        <v>4</v>
-      </c>
-      <c r="O83" s="3">
-        <v>1.3888888888888889E-4</v>
-      </c>
-      <c r="P83" s="3">
-        <v>1.5046296296296296E-3</v>
-      </c>
-      <c r="Q83" s="4">
-        <v>8.0199999999999994E-2</v>
-      </c>
-      <c r="R83" s="4">
-        <v>4.2700000000000002E-2</v>
-      </c>
-      <c r="S83" s="5">
-        <v>0</v>
-      </c>
-      <c r="T83">
-        <v>1</v>
-      </c>
-      <c r="U83" s="4">
-        <v>5.2600000000000001E-2</v>
-      </c>
-      <c r="V83" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B84">
-        <v>13</v>
-      </c>
-      <c r="C84">
-        <v>168</v>
-      </c>
-      <c r="D84">
-        <v>169</v>
-      </c>
-      <c r="E84" t="s">
-        <v>23</v>
-      </c>
-      <c r="F84">
-        <v>23394</v>
-      </c>
-      <c r="G84">
-        <v>38</v>
-      </c>
-      <c r="H84">
-        <v>0</v>
-      </c>
-      <c r="I84">
-        <v>1018</v>
-      </c>
-      <c r="J84">
-        <v>101</v>
-      </c>
-      <c r="K84">
-        <v>1</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84" s="3">
-        <v>1.0416666666666667E-4</v>
-      </c>
-      <c r="P84" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q84" s="4">
-        <v>9.9199999999999997E-2</v>
-      </c>
-      <c r="R84" s="4">
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="S84" s="5">
-        <v>0</v>
-      </c>
-      <c r="T84">
-        <v>1</v>
-      </c>
-      <c r="U84" s="5">
-        <v>1</v>
-      </c>
-      <c r="V84" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B85">
-        <v>14</v>
-      </c>
-      <c r="C85">
-        <v>168</v>
-      </c>
-      <c r="D85">
-        <v>169</v>
-      </c>
-      <c r="E85" t="s">
-        <v>23</v>
-      </c>
-      <c r="F85">
-        <v>23394</v>
-      </c>
-      <c r="G85">
-        <v>38</v>
-      </c>
-      <c r="H85">
-        <v>4</v>
-      </c>
-      <c r="I85">
-        <v>8121</v>
-      </c>
-      <c r="J85">
-        <v>706</v>
-      </c>
-      <c r="K85">
-        <v>21</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>21</v>
-      </c>
-      <c r="N85">
-        <v>5</v>
-      </c>
-      <c r="O85" s="3">
-        <v>1.273148148148148E-4</v>
-      </c>
-      <c r="P85" s="3">
-        <v>1.6666666666666668E-3</v>
-      </c>
-      <c r="Q85" s="4">
-        <v>8.6900000000000005E-2</v>
-      </c>
-      <c r="R85" s="4">
-        <v>2.9700000000000001E-2</v>
-      </c>
-      <c r="S85" s="5">
-        <v>0</v>
-      </c>
-      <c r="T85">
-        <v>0</v>
-      </c>
-      <c r="U85" s="5">
-        <v>0</v>
-      </c>
-      <c r="V85" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B86">
-        <v>15</v>
-      </c>
-      <c r="C86">
-        <v>168</v>
-      </c>
-      <c r="D86">
-        <v>169</v>
-      </c>
-      <c r="E86" t="s">
-        <v>23</v>
-      </c>
-      <c r="F86">
-        <v>23394</v>
-      </c>
-      <c r="G86">
-        <v>38</v>
-      </c>
-      <c r="H86">
-        <v>3</v>
-      </c>
-      <c r="I86">
-        <v>8674</v>
-      </c>
-      <c r="J86">
-        <v>764</v>
-      </c>
-      <c r="K86">
-        <v>26</v>
-      </c>
-      <c r="L86">
-        <v>1</v>
-      </c>
-      <c r="M86">
-        <v>23</v>
-      </c>
-      <c r="N86">
-        <v>1</v>
-      </c>
-      <c r="O86" s="3">
-        <v>1.273148148148148E-4</v>
-      </c>
-      <c r="P86" s="3">
-        <v>9.0277777777777774E-4</v>
-      </c>
-      <c r="Q86" s="4">
-        <v>8.8099999999999998E-2</v>
-      </c>
-      <c r="R86" s="4">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="S86" s="4">
-        <v>3.85E-2</v>
-      </c>
-      <c r="T86">
-        <v>2</v>
-      </c>
-      <c r="U86" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="V86" s="4">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B87">
-        <v>16</v>
-      </c>
-      <c r="C87">
-        <v>168</v>
-      </c>
-      <c r="D87">
-        <v>169</v>
-      </c>
-      <c r="E87" t="s">
-        <v>23</v>
-      </c>
-      <c r="F87">
-        <v>23394</v>
-      </c>
-      <c r="G87">
-        <v>38</v>
-      </c>
-      <c r="H87">
-        <v>2</v>
-      </c>
-      <c r="I87">
-        <v>8515</v>
-      </c>
-      <c r="J87">
-        <v>985</v>
-      </c>
-      <c r="K87">
-        <v>28</v>
-      </c>
-      <c r="L87">
-        <v>2</v>
-      </c>
-      <c r="M87">
-        <v>9</v>
-      </c>
-      <c r="N87">
-        <v>3</v>
-      </c>
-      <c r="O87" s="3">
-        <v>9.2592592592592588E-5</v>
-      </c>
-      <c r="P87" s="3">
-        <v>2.2916666666666667E-3</v>
-      </c>
-      <c r="Q87" s="4">
-        <v>0.1157</v>
-      </c>
-      <c r="R87" s="4">
-        <v>2.8400000000000002E-2</v>
-      </c>
-      <c r="S87" s="4">
-        <v>7.1400000000000005E-2</v>
-      </c>
-      <c r="T87">
-        <v>17</v>
-      </c>
-      <c r="U87" s="4">
-        <v>0.65380000000000005</v>
-      </c>
-      <c r="V87" s="4">
-        <v>0.45450000000000002</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B88">
-        <v>17</v>
-      </c>
-      <c r="C88">
-        <v>168</v>
-      </c>
-      <c r="D88">
-        <v>169</v>
-      </c>
-      <c r="E88" t="s">
-        <v>23</v>
-      </c>
-      <c r="F88">
-        <v>23394</v>
-      </c>
-      <c r="G88">
-        <v>38</v>
-      </c>
-      <c r="H88">
-        <v>0</v>
-      </c>
-      <c r="I88">
-        <v>7587</v>
-      </c>
-      <c r="J88">
-        <v>830</v>
-      </c>
-      <c r="K88">
-        <v>24</v>
-      </c>
-      <c r="L88">
-        <v>1</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88" s="3">
-        <v>1.0416666666666667E-4</v>
-      </c>
-      <c r="P88" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q88" s="4">
-        <v>0.1094</v>
-      </c>
-      <c r="R88" s="4">
-        <v>2.8899999999999999E-2</v>
-      </c>
-      <c r="S88" s="4">
-        <v>4.1700000000000001E-2</v>
-      </c>
-      <c r="T88">
-        <v>23</v>
-      </c>
-      <c r="U88" s="5">
-        <v>1</v>
-      </c>
-      <c r="V88" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B89">
-        <v>18</v>
-      </c>
-      <c r="C89">
-        <v>168</v>
-      </c>
-      <c r="D89">
-        <v>169</v>
-      </c>
-      <c r="E89" t="s">
-        <v>23</v>
-      </c>
-      <c r="F89">
-        <v>23394</v>
-      </c>
-      <c r="G89">
-        <v>38</v>
-      </c>
-      <c r="H89">
-        <v>0</v>
-      </c>
-      <c r="I89">
-        <v>8197</v>
-      </c>
-      <c r="J89">
-        <v>896</v>
-      </c>
-      <c r="K89">
-        <v>31</v>
-      </c>
-      <c r="L89">
-        <v>1</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3">
-        <v>1.0416666666666667E-4</v>
-      </c>
-      <c r="P89" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q89" s="4">
-        <v>0.10929999999999999</v>
-      </c>
-      <c r="R89" s="4">
-        <v>3.4599999999999999E-2</v>
-      </c>
-      <c r="S89" s="4">
-        <v>3.2300000000000002E-2</v>
-      </c>
-      <c r="T89">
-        <v>30</v>
-      </c>
-      <c r="U89" s="5">
-        <v>1</v>
-      </c>
-      <c r="V89" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B90">
-        <v>19</v>
-      </c>
-      <c r="C90">
-        <v>168</v>
-      </c>
-      <c r="D90">
-        <v>169</v>
-      </c>
-      <c r="E90" t="s">
-        <v>23</v>
-      </c>
-      <c r="F90">
-        <v>23394</v>
-      </c>
-      <c r="G90">
-        <v>38</v>
-      </c>
-      <c r="H90">
-        <v>0</v>
-      </c>
-      <c r="I90">
-        <v>7771</v>
-      </c>
-      <c r="J90">
-        <v>926</v>
-      </c>
-      <c r="K90">
-        <v>16</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90" s="3">
-        <v>9.2592592592592588E-5</v>
-      </c>
-      <c r="P90" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q90" s="4">
-        <v>0.1192</v>
-      </c>
-      <c r="R90" s="4">
-        <v>1.7299999999999999E-2</v>
-      </c>
-      <c r="S90" s="5">
-        <v>0</v>
-      </c>
-      <c r="T90">
-        <v>16</v>
-      </c>
-      <c r="U90" s="5">
-        <v>1</v>
-      </c>
-      <c r="V90" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
-        <v>46185</v>
-      </c>
-      <c r="B91">
-        <v>20</v>
-      </c>
-      <c r="C91">
-        <v>168</v>
-      </c>
-      <c r="D91">
-        <v>169</v>
-      </c>
-      <c r="E91" t="s">
-        <v>23</v>
-      </c>
-      <c r="F91">
-        <v>23394</v>
-      </c>
-      <c r="G91">
-        <v>38</v>
-      </c>
-      <c r="H91">
-        <v>0</v>
-      </c>
-      <c r="I91">
-        <v>4160</v>
-      </c>
-      <c r="J91">
-        <v>572</v>
-      </c>
-      <c r="K91">
-        <v>14</v>
-      </c>
-      <c r="L91">
-        <v>14</v>
-      </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>8.1018518518518516E-5</v>
-      </c>
-      <c r="P91" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q91" s="4">
-        <v>0.13750000000000001</v>
-      </c>
-      <c r="R91" s="4">
-        <v>2.4500000000000001E-2</v>
-      </c>
-      <c r="S91" s="5">
-        <v>1</v>
-      </c>
-      <c r="T91">
-        <v>0</v>
-      </c>
-      <c r="U91" t="s">
-        <v>25</v>
-      </c>
-      <c r="V91" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <v>46186</v>
-      </c>
-      <c r="B92">
-        <v>8</v>
-      </c>
-      <c r="C92">
-        <v>168</v>
-      </c>
-      <c r="D92">
-        <v>169</v>
-      </c>
-      <c r="E92" t="s">
-        <v>23</v>
-      </c>
-      <c r="F92">
-        <v>23394</v>
-      </c>
-      <c r="G92">
-        <v>38</v>
-      </c>
-      <c r="H92">
-        <v>0</v>
-      </c>
-      <c r="I92">
-        <v>8022</v>
-      </c>
-      <c r="J92">
-        <v>524</v>
-      </c>
-      <c r="K92">
-        <v>20</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92" s="3">
-        <v>1.7361111111111112E-4</v>
-      </c>
-      <c r="P92" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q92" s="4">
-        <v>6.5299999999999997E-2</v>
-      </c>
-      <c r="R92" s="4">
-        <v>3.8199999999999998E-2</v>
-      </c>
-      <c r="S92" s="5">
-        <v>0</v>
-      </c>
-      <c r="T92">
-        <v>20</v>
-      </c>
-      <c r="U92" s="5">
-        <v>1</v>
-      </c>
-      <c r="V92" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
-        <v>46186</v>
-      </c>
-      <c r="B93">
-        <v>9</v>
-      </c>
-      <c r="C93">
-        <v>168</v>
-      </c>
-      <c r="D93">
-        <v>169</v>
-      </c>
-      <c r="E93" t="s">
-        <v>23</v>
-      </c>
-      <c r="F93">
-        <v>23394</v>
-      </c>
-      <c r="G93">
-        <v>38</v>
-      </c>
-      <c r="H93">
-        <v>0</v>
-      </c>
-      <c r="I93">
-        <v>8265</v>
-      </c>
-      <c r="J93">
-        <v>816</v>
-      </c>
-      <c r="K93">
-        <v>26</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93" s="3">
-        <v>1.1574074074074075E-4</v>
-      </c>
-      <c r="P93" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q93" s="4">
-        <v>9.8699999999999996E-2</v>
-      </c>
-      <c r="R93" s="4">
-        <v>3.1899999999999998E-2</v>
-      </c>
-      <c r="S93" s="5">
-        <v>0</v>
-      </c>
-      <c r="T93">
-        <v>26</v>
-      </c>
-      <c r="U93" s="5">
-        <v>1</v>
-      </c>
-      <c r="V93" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
-        <v>46186</v>
-      </c>
-      <c r="B94">
-        <v>10</v>
-      </c>
-      <c r="C94">
-        <v>168</v>
-      </c>
-      <c r="D94">
-        <v>169</v>
-      </c>
-      <c r="E94" t="s">
-        <v>23</v>
-      </c>
-      <c r="F94">
-        <v>23394</v>
-      </c>
-      <c r="G94">
-        <v>38</v>
-      </c>
-      <c r="H94">
-        <v>0</v>
-      </c>
-      <c r="I94">
-        <v>2177</v>
-      </c>
-      <c r="J94">
-        <v>569</v>
-      </c>
-      <c r="K94">
-        <v>6</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>0</v>
-      </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>3.4722222222222222E-5</v>
-      </c>
-      <c r="P94" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q94" s="4">
-        <v>0.26140000000000002</v>
-      </c>
-      <c r="R94" s="4">
-        <v>1.0500000000000001E-2</v>
-      </c>
-      <c r="S94" s="5">
-        <v>0</v>
-      </c>
-      <c r="T94">
-        <v>6</v>
-      </c>
-      <c r="U94" s="5">
-        <v>1</v>
-      </c>
-      <c r="V94" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A95" s="2">
-        <v>46186</v>
-      </c>
-      <c r="B95">
-        <v>11</v>
-      </c>
-      <c r="C95">
-        <v>168</v>
-      </c>
-      <c r="D95">
-        <v>169</v>
-      </c>
-      <c r="E95" t="s">
-        <v>23</v>
-      </c>
-      <c r="F95">
-        <v>23394</v>
-      </c>
-      <c r="G95">
-        <v>38</v>
-      </c>
-      <c r="H95">
-        <v>0</v>
-      </c>
-      <c r="I95">
-        <v>6103</v>
-      </c>
-      <c r="J95">
-        <v>561</v>
-      </c>
-      <c r="K95">
-        <v>19</v>
-      </c>
-      <c r="L95">
-        <v>2</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95" s="3">
-        <v>1.1574074074074075E-4</v>
-      </c>
-      <c r="P95" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q95" s="4">
-        <v>9.1899999999999996E-2</v>
-      </c>
-      <c r="R95" s="4">
-        <v>3.39E-2</v>
-      </c>
-      <c r="S95" s="4">
-        <v>0.1053</v>
-      </c>
-      <c r="T95">
-        <v>17</v>
-      </c>
-      <c r="U95" s="5">
-        <v>1</v>
-      </c>
-      <c r="V95" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A96" s="2">
-        <v>46186</v>
-      </c>
-      <c r="B96">
-        <v>12</v>
-      </c>
-      <c r="C96">
-        <v>168</v>
-      </c>
-      <c r="D96">
-        <v>169</v>
-      </c>
-      <c r="E96" t="s">
-        <v>23</v>
-      </c>
-      <c r="F96">
-        <v>23394</v>
-      </c>
-      <c r="G96">
-        <v>38</v>
-      </c>
-      <c r="H96">
-        <v>0</v>
-      </c>
-      <c r="I96">
-        <v>5565</v>
-      </c>
-      <c r="J96">
-        <v>516</v>
-      </c>
-      <c r="K96">
-        <v>11</v>
-      </c>
-      <c r="L96">
-        <v>1</v>
-      </c>
-      <c r="M96">
-        <v>0</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>1.1574074074074075E-4</v>
-      </c>
-      <c r="P96" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q96" s="4">
-        <v>9.2700000000000005E-2</v>
-      </c>
-      <c r="R96" s="4">
-        <v>2.1299999999999999E-2</v>
-      </c>
-      <c r="S96" s="4">
-        <v>9.0899999999999995E-2</v>
-      </c>
-      <c r="T96">
-        <v>10</v>
-      </c>
-      <c r="U96" s="5">
-        <v>1</v>
-      </c>
-      <c r="V96" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A97" s="2">
-        <v>46186</v>
-      </c>
-      <c r="B97">
-        <v>13</v>
-      </c>
-      <c r="C97">
-        <v>168</v>
-      </c>
-      <c r="D97">
-        <v>169</v>
-      </c>
-      <c r="E97" t="s">
-        <v>23</v>
-      </c>
-      <c r="F97">
-        <v>23394</v>
-      </c>
-      <c r="G97">
-        <v>38</v>
-      </c>
-      <c r="H97">
-        <v>0</v>
-      </c>
-      <c r="I97">
-        <v>1683</v>
-      </c>
-      <c r="J97">
-        <v>354</v>
-      </c>
-      <c r="K97">
-        <v>5</v>
-      </c>
-      <c r="L97">
-        <v>5</v>
-      </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
-      <c r="O97" s="3">
-        <v>4.6296296296296294E-5</v>
-      </c>
-      <c r="P97" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q97" s="4">
-        <v>0.21029999999999999</v>
-      </c>
-      <c r="R97" s="4">
-        <v>1.41E-2</v>
-      </c>
-      <c r="S97" s="5">
-        <v>1</v>
-      </c>
-      <c r="T97">
-        <v>0</v>
-      </c>
-      <c r="U97" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
-        <v>46188</v>
-      </c>
-      <c r="B98">
-        <v>8</v>
-      </c>
-      <c r="C98">
-        <v>168</v>
-      </c>
-      <c r="D98">
-        <v>169</v>
-      </c>
-      <c r="E98" t="s">
-        <v>23</v>
-      </c>
-      <c r="F98">
-        <v>23394</v>
-      </c>
-      <c r="G98">
-        <v>38</v>
-      </c>
-      <c r="H98">
-        <v>0</v>
-      </c>
-      <c r="I98">
-        <v>7074</v>
-      </c>
-      <c r="J98">
-        <v>430</v>
-      </c>
-      <c r="K98">
-        <v>21</v>
-      </c>
-      <c r="L98">
-        <v>21</v>
-      </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
-      <c r="O98" s="3">
-        <v>1.8518518518518518E-4</v>
-      </c>
-      <c r="P98" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q98" s="4">
-        <v>6.08E-2</v>
-      </c>
-      <c r="R98" s="4">
-        <v>4.8800000000000003E-2</v>
-      </c>
-      <c r="S98" s="5">
-        <v>1</v>
-      </c>
-      <c r="T98">
-        <v>0</v>
-      </c>
-      <c r="U98" t="s">
-        <v>25</v>
-      </c>
-      <c r="V98" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C945BD-6068-4723-A263-AF8AF4A01AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C384E87-47F3-4D8F-A86A-99EB32394C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="33">
   <si>
     <t>Data</t>
   </si>
@@ -505,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W82"/>
+  <dimension ref="A1:W112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -6129,13 +6129,13 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>3780</v>
+        <v>3787</v>
       </c>
       <c r="J82">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K82">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -6153,22 +6153,2086 @@
         <v>2.2800925925925927E-3</v>
       </c>
       <c r="Q82" s="4">
-        <v>0.13539999999999999</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="R82" s="4">
-        <v>2.3400000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="S82" s="5">
         <v>0</v>
       </c>
       <c r="T82">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U82" s="4">
-        <v>0.91669999999999996</v>
+        <v>0.92310000000000003</v>
       </c>
       <c r="V82" s="4">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B83">
+        <v>12</v>
+      </c>
+      <c r="C83">
+        <v>168</v>
+      </c>
+      <c r="D83">
+        <v>169</v>
+      </c>
+      <c r="E83" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83">
+        <v>23394</v>
+      </c>
+      <c r="G83">
+        <v>38</v>
+      </c>
+      <c r="H83">
+        <v>4</v>
+      </c>
+      <c r="I83">
+        <v>5551</v>
+      </c>
+      <c r="J83">
+        <v>445</v>
+      </c>
+      <c r="K83">
+        <v>19</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>18</v>
+      </c>
+      <c r="N83">
+        <v>4</v>
+      </c>
+      <c r="O83" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="P83" s="3">
+        <v>1.5046296296296296E-3</v>
+      </c>
+      <c r="Q83" s="4">
+        <v>8.0199999999999994E-2</v>
+      </c>
+      <c r="R83" s="4">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="S83" s="5">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>1</v>
+      </c>
+      <c r="U83" s="4">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="V83" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B84">
+        <v>13</v>
+      </c>
+      <c r="C84">
+        <v>168</v>
+      </c>
+      <c r="D84">
+        <v>169</v>
+      </c>
+      <c r="E84" t="s">
+        <v>23</v>
+      </c>
+      <c r="F84">
+        <v>23394</v>
+      </c>
+      <c r="G84">
+        <v>38</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>1018</v>
+      </c>
+      <c r="J84">
+        <v>101</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P84" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>9.9199999999999997E-2</v>
+      </c>
+      <c r="R84" s="4">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="S84" s="5">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>1</v>
+      </c>
+      <c r="U84" s="5">
+        <v>1</v>
+      </c>
+      <c r="V84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B85">
+        <v>14</v>
+      </c>
+      <c r="C85">
+        <v>168</v>
+      </c>
+      <c r="D85">
+        <v>169</v>
+      </c>
+      <c r="E85" t="s">
+        <v>23</v>
+      </c>
+      <c r="F85">
+        <v>23394</v>
+      </c>
+      <c r="G85">
+        <v>38</v>
+      </c>
+      <c r="H85">
+        <v>4</v>
+      </c>
+      <c r="I85">
+        <v>8121</v>
+      </c>
+      <c r="J85">
+        <v>706</v>
+      </c>
+      <c r="K85">
+        <v>21</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>21</v>
+      </c>
+      <c r="N85">
+        <v>5</v>
+      </c>
+      <c r="O85" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="P85" s="3">
+        <v>1.6666666666666668E-3</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="R85" s="4">
+        <v>2.9700000000000001E-2</v>
+      </c>
+      <c r="S85" s="5">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85" s="5">
+        <v>0</v>
+      </c>
+      <c r="V85" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B86">
+        <v>15</v>
+      </c>
+      <c r="C86">
+        <v>168</v>
+      </c>
+      <c r="D86">
+        <v>169</v>
+      </c>
+      <c r="E86" t="s">
+        <v>23</v>
+      </c>
+      <c r="F86">
+        <v>23394</v>
+      </c>
+      <c r="G86">
+        <v>38</v>
+      </c>
+      <c r="H86">
+        <v>3</v>
+      </c>
+      <c r="I86">
+        <v>8674</v>
+      </c>
+      <c r="J86">
+        <v>764</v>
+      </c>
+      <c r="K86">
+        <v>26</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>23</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="P86" s="3">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="Q86" s="4">
+        <v>8.8099999999999998E-2</v>
+      </c>
+      <c r="R86" s="4">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="S86" s="4">
+        <v>3.85E-2</v>
+      </c>
+      <c r="T86">
+        <v>2</v>
+      </c>
+      <c r="U86" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="V86" s="4">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B87">
+        <v>16</v>
+      </c>
+      <c r="C87">
+        <v>168</v>
+      </c>
+      <c r="D87">
+        <v>169</v>
+      </c>
+      <c r="E87" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87">
+        <v>23394</v>
+      </c>
+      <c r="G87">
+        <v>38</v>
+      </c>
+      <c r="H87">
+        <v>2</v>
+      </c>
+      <c r="I87">
+        <v>8515</v>
+      </c>
+      <c r="J87">
+        <v>985</v>
+      </c>
+      <c r="K87">
+        <v>28</v>
+      </c>
+      <c r="L87">
+        <v>2</v>
+      </c>
+      <c r="M87">
+        <v>9</v>
+      </c>
+      <c r="N87">
+        <v>3</v>
+      </c>
+      <c r="O87" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P87" s="3">
+        <v>2.2916666666666667E-3</v>
+      </c>
+      <c r="Q87" s="4">
+        <v>0.1157</v>
+      </c>
+      <c r="R87" s="4">
+        <v>2.8400000000000002E-2</v>
+      </c>
+      <c r="S87" s="4">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="T87">
+        <v>17</v>
+      </c>
+      <c r="U87" s="4">
+        <v>0.65380000000000005</v>
+      </c>
+      <c r="V87" s="4">
+        <v>0.45450000000000002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B88">
+        <v>17</v>
+      </c>
+      <c r="C88">
+        <v>168</v>
+      </c>
+      <c r="D88">
+        <v>169</v>
+      </c>
+      <c r="E88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88">
+        <v>23394</v>
+      </c>
+      <c r="G88">
+        <v>38</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>7587</v>
+      </c>
+      <c r="J88">
+        <v>830</v>
+      </c>
+      <c r="K88">
+        <v>24</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P88" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q88" s="4">
+        <v>0.1094</v>
+      </c>
+      <c r="R88" s="4">
+        <v>2.8899999999999999E-2</v>
+      </c>
+      <c r="S88" s="4">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="T88">
+        <v>23</v>
+      </c>
+      <c r="U88" s="5">
+        <v>1</v>
+      </c>
+      <c r="V88" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B89">
+        <v>18</v>
+      </c>
+      <c r="C89">
+        <v>168</v>
+      </c>
+      <c r="D89">
+        <v>169</v>
+      </c>
+      <c r="E89" t="s">
+        <v>23</v>
+      </c>
+      <c r="F89">
+        <v>23394</v>
+      </c>
+      <c r="G89">
+        <v>38</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>8197</v>
+      </c>
+      <c r="J89">
+        <v>896</v>
+      </c>
+      <c r="K89">
+        <v>31</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P89" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q89" s="4">
+        <v>0.10929999999999999</v>
+      </c>
+      <c r="R89" s="4">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="S89" s="4">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="T89">
+        <v>30</v>
+      </c>
+      <c r="U89" s="5">
+        <v>1</v>
+      </c>
+      <c r="V89" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B90">
+        <v>19</v>
+      </c>
+      <c r="C90">
+        <v>168</v>
+      </c>
+      <c r="D90">
+        <v>169</v>
+      </c>
+      <c r="E90" t="s">
+        <v>23</v>
+      </c>
+      <c r="F90">
+        <v>23394</v>
+      </c>
+      <c r="G90">
+        <v>38</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>7771</v>
+      </c>
+      <c r="J90">
+        <v>926</v>
+      </c>
+      <c r="K90">
+        <v>16</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P90" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q90" s="4">
+        <v>0.1192</v>
+      </c>
+      <c r="R90" s="4">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="S90" s="5">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>16</v>
+      </c>
+      <c r="U90" s="5">
+        <v>1</v>
+      </c>
+      <c r="V90" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B91">
+        <v>20</v>
+      </c>
+      <c r="C91">
+        <v>168</v>
+      </c>
+      <c r="D91">
+        <v>169</v>
+      </c>
+      <c r="E91" t="s">
+        <v>23</v>
+      </c>
+      <c r="F91">
+        <v>23394</v>
+      </c>
+      <c r="G91">
+        <v>38</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>4160</v>
+      </c>
+      <c r="J91">
+        <v>572</v>
+      </c>
+      <c r="K91">
+        <v>14</v>
+      </c>
+      <c r="L91">
+        <v>14</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="P91" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q91" s="4">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="R91" s="4">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="S91" s="5">
+        <v>1</v>
+      </c>
+      <c r="T91">
+        <v>0</v>
+      </c>
+      <c r="U91" t="s">
+        <v>25</v>
+      </c>
+      <c r="V91" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B92">
+        <v>8</v>
+      </c>
+      <c r="C92">
+        <v>168</v>
+      </c>
+      <c r="D92">
+        <v>169</v>
+      </c>
+      <c r="E92" t="s">
+        <v>23</v>
+      </c>
+      <c r="F92">
+        <v>23394</v>
+      </c>
+      <c r="G92">
+        <v>38</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>8022</v>
+      </c>
+      <c r="J92">
+        <v>524</v>
+      </c>
+      <c r="K92">
+        <v>20</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="P92" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q92" s="4">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="R92" s="4">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="S92" s="5">
+        <v>0</v>
+      </c>
+      <c r="T92">
+        <v>20</v>
+      </c>
+      <c r="U92" s="5">
+        <v>1</v>
+      </c>
+      <c r="V92" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B93">
+        <v>9</v>
+      </c>
+      <c r="C93">
+        <v>168</v>
+      </c>
+      <c r="D93">
+        <v>169</v>
+      </c>
+      <c r="E93" t="s">
+        <v>23</v>
+      </c>
+      <c r="F93">
+        <v>23394</v>
+      </c>
+      <c r="G93">
+        <v>38</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>8265</v>
+      </c>
+      <c r="J93">
+        <v>816</v>
+      </c>
+      <c r="K93">
+        <v>26</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="P93" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q93" s="4">
+        <v>9.8699999999999996E-2</v>
+      </c>
+      <c r="R93" s="4">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="S93" s="5">
+        <v>0</v>
+      </c>
+      <c r="T93">
+        <v>26</v>
+      </c>
+      <c r="U93" s="5">
+        <v>1</v>
+      </c>
+      <c r="V93" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B94">
+        <v>10</v>
+      </c>
+      <c r="C94">
+        <v>168</v>
+      </c>
+      <c r="D94">
+        <v>169</v>
+      </c>
+      <c r="E94" t="s">
+        <v>23</v>
+      </c>
+      <c r="F94">
+        <v>23394</v>
+      </c>
+      <c r="G94">
+        <v>38</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>2177</v>
+      </c>
+      <c r="J94">
+        <v>569</v>
+      </c>
+      <c r="K94">
+        <v>6</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="P94" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q94" s="4">
+        <v>0.26140000000000002</v>
+      </c>
+      <c r="R94" s="4">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="S94" s="5">
+        <v>0</v>
+      </c>
+      <c r="T94">
+        <v>6</v>
+      </c>
+      <c r="U94" s="5">
+        <v>1</v>
+      </c>
+      <c r="V94" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B95">
+        <v>11</v>
+      </c>
+      <c r="C95">
+        <v>168</v>
+      </c>
+      <c r="D95">
+        <v>169</v>
+      </c>
+      <c r="E95" t="s">
+        <v>23</v>
+      </c>
+      <c r="F95">
+        <v>23394</v>
+      </c>
+      <c r="G95">
+        <v>38</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>6103</v>
+      </c>
+      <c r="J95">
+        <v>561</v>
+      </c>
+      <c r="K95">
+        <v>19</v>
+      </c>
+      <c r="L95">
+        <v>2</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="P95" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q95" s="4">
+        <v>9.1899999999999996E-2</v>
+      </c>
+      <c r="R95" s="4">
+        <v>3.39E-2</v>
+      </c>
+      <c r="S95" s="4">
+        <v>0.1053</v>
+      </c>
+      <c r="T95">
+        <v>17</v>
+      </c>
+      <c r="U95" s="5">
+        <v>1</v>
+      </c>
+      <c r="V95" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B96">
+        <v>12</v>
+      </c>
+      <c r="C96">
+        <v>168</v>
+      </c>
+      <c r="D96">
+        <v>169</v>
+      </c>
+      <c r="E96" t="s">
+        <v>23</v>
+      </c>
+      <c r="F96">
+        <v>23394</v>
+      </c>
+      <c r="G96">
+        <v>38</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>5565</v>
+      </c>
+      <c r="J96">
+        <v>516</v>
+      </c>
+      <c r="K96">
+        <v>11</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="P96" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q96" s="4">
+        <v>9.2700000000000005E-2</v>
+      </c>
+      <c r="R96" s="4">
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="S96" s="4">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="T96">
+        <v>10</v>
+      </c>
+      <c r="U96" s="5">
+        <v>1</v>
+      </c>
+      <c r="V96" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>46186</v>
+      </c>
+      <c r="B97">
+        <v>13</v>
+      </c>
+      <c r="C97">
+        <v>168</v>
+      </c>
+      <c r="D97">
+        <v>169</v>
+      </c>
+      <c r="E97" t="s">
+        <v>23</v>
+      </c>
+      <c r="F97">
+        <v>23394</v>
+      </c>
+      <c r="G97">
+        <v>38</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>1683</v>
+      </c>
+      <c r="J97">
+        <v>354</v>
+      </c>
+      <c r="K97">
+        <v>5</v>
+      </c>
+      <c r="L97">
+        <v>5</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="P97" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q97" s="4">
+        <v>0.21029999999999999</v>
+      </c>
+      <c r="R97" s="4">
+        <v>1.41E-2</v>
+      </c>
+      <c r="S97" s="5">
+        <v>1</v>
+      </c>
+      <c r="T97">
+        <v>0</v>
+      </c>
+      <c r="U97" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B98">
+        <v>8</v>
+      </c>
+      <c r="C98">
+        <v>168</v>
+      </c>
+      <c r="D98">
+        <v>169</v>
+      </c>
+      <c r="E98" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98">
+        <v>16714</v>
+      </c>
+      <c r="G98">
+        <v>38</v>
+      </c>
+      <c r="H98">
+        <v>2</v>
+      </c>
+      <c r="I98">
+        <v>7078</v>
+      </c>
+      <c r="J98">
+        <v>433</v>
+      </c>
+      <c r="K98">
+        <v>23</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>14</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98" s="3">
+        <v>1.8518518518518518E-4</v>
+      </c>
+      <c r="P98" s="3">
+        <v>2.1296296296296298E-3</v>
+      </c>
+      <c r="Q98" s="4">
+        <v>6.1199999999999997E-2</v>
+      </c>
+      <c r="R98" s="4">
+        <v>5.3100000000000001E-2</v>
+      </c>
+      <c r="S98" s="5">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="T98">
+        <v>8</v>
+      </c>
+      <c r="U98" s="4">
+        <v>0.36359999999999998</v>
+      </c>
+      <c r="V98" s="4">
+        <v>0.52629999999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B99">
+        <v>9</v>
+      </c>
+      <c r="C99">
+        <v>168</v>
+      </c>
+      <c r="D99">
+        <v>169</v>
+      </c>
+      <c r="E99" t="s">
+        <v>23</v>
+      </c>
+      <c r="F99">
+        <v>16714</v>
+      </c>
+      <c r="G99">
+        <v>38</v>
+      </c>
+      <c r="H99">
+        <v>3</v>
+      </c>
+      <c r="I99">
+        <v>831</v>
+      </c>
+      <c r="J99">
+        <v>207</v>
+      </c>
+      <c r="K99">
+        <v>7</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>6</v>
+      </c>
+      <c r="N99">
+        <v>2</v>
+      </c>
+      <c r="O99" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="P99" s="3">
+        <v>1.8749999999999999E-3</v>
+      </c>
+      <c r="Q99" s="4">
+        <v>0.24909999999999999</v>
+      </c>
+      <c r="R99" s="4">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="S99" s="5">
+        <v>0</v>
+      </c>
+      <c r="T99">
+        <v>1</v>
+      </c>
+      <c r="U99" s="4">
+        <v>0.1429</v>
+      </c>
+      <c r="V99" s="4">
+        <v>0.88890000000000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B100">
+        <v>10</v>
+      </c>
+      <c r="C100">
+        <v>159</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100" t="s">
+        <v>32</v>
+      </c>
+      <c r="F100">
+        <v>8</v>
+      </c>
+      <c r="G100">
+        <v>2</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>3</v>
+      </c>
+      <c r="J100">
+        <v>2</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P100" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q100" s="4">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="R100" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="S100" s="5">
+        <v>1</v>
+      </c>
+      <c r="T100">
+        <v>0</v>
+      </c>
+      <c r="U100" t="s">
+        <v>25</v>
+      </c>
+      <c r="W100">
+        <v>0.13750000000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B101">
+        <v>10</v>
+      </c>
+      <c r="C101">
+        <v>166</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101" t="s">
+        <v>26</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>2</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101">
+        <v>2</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>1</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P101" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q101" s="5">
+        <v>1</v>
+      </c>
+      <c r="R101" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="S101" s="5">
+        <v>1</v>
+      </c>
+      <c r="T101">
+        <v>0</v>
+      </c>
+      <c r="U101" t="s">
+        <v>25</v>
+      </c>
+      <c r="W101">
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B102">
+        <v>10</v>
+      </c>
+      <c r="C102">
+        <v>168</v>
+      </c>
+      <c r="D102">
+        <v>169</v>
+      </c>
+      <c r="E102" t="s">
+        <v>23</v>
+      </c>
+      <c r="F102">
+        <v>16714</v>
+      </c>
+      <c r="G102">
+        <v>38</v>
+      </c>
+      <c r="H102">
+        <v>3</v>
+      </c>
+      <c r="I102">
+        <v>5242</v>
+      </c>
+      <c r="J102">
+        <v>329</v>
+      </c>
+      <c r="K102">
+        <v>16</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>16</v>
+      </c>
+      <c r="N102">
+        <v>2</v>
+      </c>
+      <c r="O102" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="P102" s="3">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="Q102" s="4">
+        <v>6.2799999999999995E-2</v>
+      </c>
+      <c r="R102" s="4">
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="S102" s="5">
+        <v>0</v>
+      </c>
+      <c r="T102">
+        <v>0</v>
+      </c>
+      <c r="U102" s="5">
+        <v>0</v>
+      </c>
+      <c r="V102" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="W102">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B103">
+        <v>11</v>
+      </c>
+      <c r="C103">
+        <v>159</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103" t="s">
+        <v>32</v>
+      </c>
+      <c r="F103">
+        <v>8</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103" t="s">
+        <v>24</v>
+      </c>
+      <c r="P103" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q103" s="5">
+        <v>0</v>
+      </c>
+      <c r="R103" t="s">
+        <v>25</v>
+      </c>
+      <c r="S103" t="s">
+        <v>25</v>
+      </c>
+      <c r="T103">
+        <v>0</v>
+      </c>
+      <c r="U103" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B104">
+        <v>11</v>
+      </c>
+      <c r="C104">
+        <v>168</v>
+      </c>
+      <c r="D104">
+        <v>169</v>
+      </c>
+      <c r="E104" t="s">
+        <v>23</v>
+      </c>
+      <c r="F104">
+        <v>16714</v>
+      </c>
+      <c r="G104">
+        <v>38</v>
+      </c>
+      <c r="H104">
+        <v>3</v>
+      </c>
+      <c r="I104">
+        <v>8462</v>
+      </c>
+      <c r="J104">
+        <v>544</v>
+      </c>
+      <c r="K104">
+        <v>37</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>33</v>
+      </c>
+      <c r="N104">
+        <v>6</v>
+      </c>
+      <c r="O104" s="3">
+        <v>1.7361111111111112E-4</v>
+      </c>
+      <c r="P104" s="3">
+        <v>1.5393518518518519E-3</v>
+      </c>
+      <c r="Q104" s="4">
+        <v>6.4299999999999996E-2</v>
+      </c>
+      <c r="R104" s="4">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="S104" s="5">
+        <v>0</v>
+      </c>
+      <c r="T104">
+        <v>4</v>
+      </c>
+      <c r="U104" s="4">
+        <v>0.1081</v>
+      </c>
+      <c r="V104" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="W104">
+        <v>28.449000000000002</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B105">
+        <v>12</v>
+      </c>
+      <c r="C105">
+        <v>168</v>
+      </c>
+      <c r="D105">
+        <v>169</v>
+      </c>
+      <c r="E105" t="s">
+        <v>23</v>
+      </c>
+      <c r="F105">
+        <v>16714</v>
+      </c>
+      <c r="G105">
+        <v>38</v>
+      </c>
+      <c r="H105">
+        <v>3</v>
+      </c>
+      <c r="I105">
+        <v>8838</v>
+      </c>
+      <c r="J105">
+        <v>774</v>
+      </c>
+      <c r="K105">
+        <v>55</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>39</v>
+      </c>
+      <c r="N105">
+        <v>4</v>
+      </c>
+      <c r="O105" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="P105" s="3">
+        <v>1.4467592592592592E-3</v>
+      </c>
+      <c r="Q105" s="4">
+        <v>8.7599999999999997E-2</v>
+      </c>
+      <c r="R105" s="4">
+        <v>7.1099999999999997E-2</v>
+      </c>
+      <c r="S105" s="5">
+        <v>0</v>
+      </c>
+      <c r="T105">
+        <v>16</v>
+      </c>
+      <c r="U105" s="4">
+        <v>0.29089999999999999</v>
+      </c>
+      <c r="V105" s="4">
+        <v>0.51849999999999996</v>
+      </c>
+      <c r="W105">
+        <v>43.47</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B106">
+        <v>13</v>
+      </c>
+      <c r="C106">
+        <v>168</v>
+      </c>
+      <c r="D106">
+        <v>169</v>
+      </c>
+      <c r="E106" t="s">
+        <v>23</v>
+      </c>
+      <c r="F106">
+        <v>16714</v>
+      </c>
+      <c r="G106">
+        <v>38</v>
+      </c>
+      <c r="H106">
+        <v>3</v>
+      </c>
+      <c r="I106">
+        <v>8844</v>
+      </c>
+      <c r="J106">
+        <v>999</v>
+      </c>
+      <c r="K106">
+        <v>56</v>
+      </c>
+      <c r="L106">
+        <v>2</v>
+      </c>
+      <c r="M106">
+        <v>3</v>
+      </c>
+      <c r="N106">
+        <v>1</v>
+      </c>
+      <c r="O106" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P106" s="3">
+        <v>2.8935185185185184E-3</v>
+      </c>
+      <c r="Q106" s="4">
+        <v>0.113</v>
+      </c>
+      <c r="R106" s="4">
+        <v>5.6099999999999997E-2</v>
+      </c>
+      <c r="S106" s="4">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="T106">
+        <v>51</v>
+      </c>
+      <c r="U106" s="4">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="V106" s="4">
+        <v>0.1111</v>
+      </c>
+      <c r="W106">
+        <v>57.122999999999998</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B107">
+        <v>14</v>
+      </c>
+      <c r="C107">
+        <v>168</v>
+      </c>
+      <c r="D107">
+        <v>169</v>
+      </c>
+      <c r="E107" t="s">
+        <v>23</v>
+      </c>
+      <c r="F107">
+        <v>16714</v>
+      </c>
+      <c r="G107">
+        <v>38</v>
+      </c>
+      <c r="H107">
+        <v>4</v>
+      </c>
+      <c r="I107">
+        <v>5804</v>
+      </c>
+      <c r="J107">
+        <v>864</v>
+      </c>
+      <c r="K107">
+        <v>46</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107">
+        <v>34</v>
+      </c>
+      <c r="N107">
+        <v>4</v>
+      </c>
+      <c r="O107" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="P107" s="3">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="Q107" s="4">
+        <v>0.1489</v>
+      </c>
+      <c r="R107" s="4">
+        <v>5.3199999999999997E-2</v>
+      </c>
+      <c r="S107" s="4">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="T107">
+        <v>11</v>
+      </c>
+      <c r="U107" s="4">
+        <v>0.24440000000000001</v>
+      </c>
+      <c r="V107" s="4">
+        <v>0.46810000000000002</v>
+      </c>
+      <c r="W107">
+        <v>40.707000000000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B108">
+        <v>15</v>
+      </c>
+      <c r="C108">
+        <v>168</v>
+      </c>
+      <c r="D108">
+        <v>169</v>
+      </c>
+      <c r="E108" t="s">
+        <v>23</v>
+      </c>
+      <c r="F108">
+        <v>16714</v>
+      </c>
+      <c r="G108">
+        <v>38</v>
+      </c>
+      <c r="H108">
+        <v>4</v>
+      </c>
+      <c r="I108">
+        <v>8549</v>
+      </c>
+      <c r="J108">
+        <v>705</v>
+      </c>
+      <c r="K108">
+        <v>47</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>39</v>
+      </c>
+      <c r="N108">
+        <v>5</v>
+      </c>
+      <c r="O108" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="P108" s="3">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="Q108" s="4">
+        <v>8.2500000000000004E-2</v>
+      </c>
+      <c r="R108" s="4">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="S108" s="5">
+        <v>0</v>
+      </c>
+      <c r="T108">
+        <v>8</v>
+      </c>
+      <c r="U108" s="4">
+        <v>0.17019999999999999</v>
+      </c>
+      <c r="V108" s="4">
+        <v>0.71109999999999995</v>
+      </c>
+      <c r="W108">
+        <v>37.962000000000003</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B109">
+        <v>16</v>
+      </c>
+      <c r="C109">
+        <v>168</v>
+      </c>
+      <c r="D109">
+        <v>169</v>
+      </c>
+      <c r="E109" t="s">
+        <v>23</v>
+      </c>
+      <c r="F109">
+        <v>16714</v>
+      </c>
+      <c r="G109">
+        <v>38</v>
+      </c>
+      <c r="H109">
+        <v>4</v>
+      </c>
+      <c r="I109">
+        <v>6631</v>
+      </c>
+      <c r="J109">
+        <v>867</v>
+      </c>
+      <c r="K109">
+        <v>40</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="M109">
+        <v>21</v>
+      </c>
+      <c r="N109">
+        <v>3</v>
+      </c>
+      <c r="O109" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="P109" s="3">
+        <v>1.4120370370370369E-3</v>
+      </c>
+      <c r="Q109" s="4">
+        <v>0.13070000000000001</v>
+      </c>
+      <c r="R109" s="4">
+        <v>4.6100000000000002E-2</v>
+      </c>
+      <c r="S109" s="4">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="T109">
+        <v>18</v>
+      </c>
+      <c r="U109" s="4">
+        <v>0.46150000000000002</v>
+      </c>
+      <c r="V109" s="4">
+        <v>0.41460000000000002</v>
+      </c>
+      <c r="W109">
+        <v>44.531999999999996</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B110">
+        <v>17</v>
+      </c>
+      <c r="C110">
+        <v>168</v>
+      </c>
+      <c r="D110">
+        <v>169</v>
+      </c>
+      <c r="E110" t="s">
+        <v>23</v>
+      </c>
+      <c r="F110">
+        <v>16714</v>
+      </c>
+      <c r="G110">
+        <v>38</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <v>2309</v>
+      </c>
+      <c r="J110">
+        <v>569</v>
+      </c>
+      <c r="K110">
+        <v>12</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110" s="3">
+        <v>4.6296296296296294E-5</v>
+      </c>
+      <c r="P110" s="3">
+        <v>2.2569444444444442E-3</v>
+      </c>
+      <c r="Q110" s="4">
+        <v>0.24640000000000001</v>
+      </c>
+      <c r="R110" s="4">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="S110" s="5">
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <v>11</v>
+      </c>
+      <c r="U110" s="4">
+        <v>0.91669999999999996</v>
+      </c>
+      <c r="V110" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="W110">
+        <v>25.339500000000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B111">
+        <v>18</v>
+      </c>
+      <c r="C111">
+        <v>168</v>
+      </c>
+      <c r="D111">
+        <v>169</v>
+      </c>
+      <c r="E111" t="s">
+        <v>23</v>
+      </c>
+      <c r="F111">
+        <v>16714</v>
+      </c>
+      <c r="G111">
+        <v>38</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>8011</v>
+      </c>
+      <c r="J111">
+        <v>758</v>
+      </c>
+      <c r="K111">
+        <v>25</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>2</v>
+      </c>
+      <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="P111" s="3">
+        <v>2.9166666666666668E-3</v>
+      </c>
+      <c r="Q111" s="4">
+        <v>9.4600000000000004E-2</v>
+      </c>
+      <c r="R111" s="4">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="S111" s="5">
+        <v>0</v>
+      </c>
+      <c r="T111">
+        <v>23</v>
+      </c>
+      <c r="U111" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="V111" s="4">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="W111">
+        <v>34.011000000000003</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B112">
+        <v>19</v>
+      </c>
+      <c r="C112">
+        <v>168</v>
+      </c>
+      <c r="D112">
+        <v>169</v>
+      </c>
+      <c r="E112" t="s">
+        <v>23</v>
+      </c>
+      <c r="F112">
+        <v>16714</v>
+      </c>
+      <c r="G112">
+        <v>38</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112">
+        <v>5772</v>
+      </c>
+      <c r="J112">
+        <v>728</v>
+      </c>
+      <c r="K112">
+        <v>27</v>
+      </c>
+      <c r="L112">
+        <v>5</v>
+      </c>
+      <c r="M112">
+        <v>1</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="P112" s="3">
+        <v>4.1203703703703706E-3</v>
+      </c>
+      <c r="Q112" s="4">
+        <v>0.12609999999999999</v>
+      </c>
+      <c r="R112" s="4">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="S112" s="4">
+        <v>0.1852</v>
+      </c>
+      <c r="T112">
+        <v>21</v>
+      </c>
+      <c r="U112" s="4">
+        <v>0.95450000000000002</v>
+      </c>
+      <c r="V112" s="4">
+        <v>0</v>
+      </c>
+      <c r="W112">
+        <v>30.876000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6178,7 +8242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FFF5342-4B63-4B01-A332-A226EA58A2DA}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -6504,7 +8568,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="6">
-        <v>102135</v>
+        <v>192383</v>
       </c>
       <c r="D9">
         <v>20</v>
@@ -6542,7 +8606,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="6">
-        <v>186791</v>
+        <v>50059</v>
       </c>
       <c r="D10">
         <v>21</v>
@@ -6608,6 +8672,82 @@
       </c>
       <c r="L11" s="3">
         <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12">
+        <v>58756</v>
+      </c>
+      <c r="D12">
+        <v>26</v>
+      </c>
+      <c r="E12">
+        <v>115201</v>
+      </c>
+      <c r="F12">
+        <v>1162</v>
+      </c>
+      <c r="G12">
+        <v>277</v>
+      </c>
+      <c r="H12" s="6">
+        <v>79</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1.01E-2</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2384</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0.28520000000000001</v>
+      </c>
+      <c r="L12" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13">
+        <v>41876</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>16800</v>
+      </c>
+      <c r="F13">
+        <v>184</v>
+      </c>
+      <c r="G13">
+        <v>42</v>
+      </c>
+      <c r="H13" s="6">
+        <v>10</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2283</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0.23810000000000001</v>
+      </c>
+      <c r="L13" s="3">
+        <v>4.2824074074074075E-4</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C384E87-47F3-4D8F-A86A-99EB32394C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6B278F-AE4D-478F-898D-CF0ACBD9EFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="33">
   <si>
     <t>Data</t>
   </si>
@@ -505,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W112"/>
+  <dimension ref="A1:W126"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -8190,10 +8190,10 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>5772</v>
+        <v>5785</v>
       </c>
       <c r="J112">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="K112">
         <v>27</v>
@@ -8214,10 +8214,10 @@
         <v>4.1203703703703706E-3</v>
       </c>
       <c r="Q112" s="4">
-        <v>0.12609999999999999</v>
+        <v>0.12740000000000001</v>
       </c>
       <c r="R112" s="4">
-        <v>3.7100000000000001E-2</v>
+        <v>3.6600000000000001E-2</v>
       </c>
       <c r="S112" s="4">
         <v>0.1852</v>
@@ -8232,7 +8232,980 @@
         <v>0</v>
       </c>
       <c r="W112">
-        <v>30.876000000000001</v>
+        <v>31.366499999999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B113">
+        <v>20</v>
+      </c>
+      <c r="C113">
+        <v>168</v>
+      </c>
+      <c r="D113">
+        <v>169</v>
+      </c>
+      <c r="E113" t="s">
+        <v>23</v>
+      </c>
+      <c r="F113">
+        <v>16714</v>
+      </c>
+      <c r="G113">
+        <v>38</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>1208</v>
+      </c>
+      <c r="J113">
+        <v>399</v>
+      </c>
+      <c r="K113">
+        <v>12</v>
+      </c>
+      <c r="L113">
+        <v>12</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="P113" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q113" s="4">
+        <v>0.33029999999999998</v>
+      </c>
+      <c r="R113" s="4">
+        <v>3.0099999999999998E-2</v>
+      </c>
+      <c r="S113" s="5">
+        <v>1</v>
+      </c>
+      <c r="T113">
+        <v>0</v>
+      </c>
+      <c r="U113" t="s">
+        <v>25</v>
+      </c>
+      <c r="W113">
+        <v>15.250500000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B114">
+        <v>8</v>
+      </c>
+      <c r="C114">
+        <v>168</v>
+      </c>
+      <c r="D114">
+        <v>169</v>
+      </c>
+      <c r="E114" t="s">
+        <v>23</v>
+      </c>
+      <c r="F114">
+        <v>50433</v>
+      </c>
+      <c r="G114">
+        <v>38</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>7606</v>
+      </c>
+      <c r="J114">
+        <v>715</v>
+      </c>
+      <c r="K114">
+        <v>40</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>13</v>
+      </c>
+      <c r="N114">
+        <v>1</v>
+      </c>
+      <c r="O114" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="P114" s="3">
+        <v>2.0370370370370369E-3</v>
+      </c>
+      <c r="Q114" s="4">
+        <v>9.4E-2</v>
+      </c>
+      <c r="R114" s="4">
+        <v>5.5899999999999998E-2</v>
+      </c>
+      <c r="S114" s="5">
+        <v>0</v>
+      </c>
+      <c r="T114">
+        <v>27</v>
+      </c>
+      <c r="U114" s="4">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="V114" s="4">
+        <v>0.25580000000000003</v>
+      </c>
+      <c r="W114">
+        <v>33.533999999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B115">
+        <v>9</v>
+      </c>
+      <c r="C115">
+        <v>166</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115" t="s">
+        <v>26</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115" t="s">
+        <v>24</v>
+      </c>
+      <c r="P115" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q115" s="5">
+        <v>0</v>
+      </c>
+      <c r="R115" t="s">
+        <v>25</v>
+      </c>
+      <c r="S115" t="s">
+        <v>25</v>
+      </c>
+      <c r="T115">
+        <v>0</v>
+      </c>
+      <c r="U115" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B116">
+        <v>9</v>
+      </c>
+      <c r="C116">
+        <v>168</v>
+      </c>
+      <c r="D116">
+        <v>169</v>
+      </c>
+      <c r="E116" t="s">
+        <v>23</v>
+      </c>
+      <c r="F116">
+        <v>50433</v>
+      </c>
+      <c r="G116">
+        <v>38</v>
+      </c>
+      <c r="H116">
+        <v>8</v>
+      </c>
+      <c r="I116">
+        <v>7118</v>
+      </c>
+      <c r="J116">
+        <v>1046</v>
+      </c>
+      <c r="K116">
+        <v>67</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="M116">
+        <v>47</v>
+      </c>
+      <c r="N116">
+        <v>5</v>
+      </c>
+      <c r="O116" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="P116" s="3">
+        <v>1.0416666666666667E-3</v>
+      </c>
+      <c r="Q116" s="4">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="R116" s="4">
+        <v>6.4100000000000004E-2</v>
+      </c>
+      <c r="S116" s="4">
+        <v>1.49E-2</v>
+      </c>
+      <c r="T116">
+        <v>19</v>
+      </c>
+      <c r="U116" s="4">
+        <v>0.28789999999999999</v>
+      </c>
+      <c r="V116" s="4">
+        <v>0.59379999999999999</v>
+      </c>
+      <c r="W116">
+        <v>51.718499999999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B117">
+        <v>10</v>
+      </c>
+      <c r="C117">
+        <v>168</v>
+      </c>
+      <c r="D117">
+        <v>169</v>
+      </c>
+      <c r="E117" t="s">
+        <v>23</v>
+      </c>
+      <c r="F117">
+        <v>50433</v>
+      </c>
+      <c r="G117">
+        <v>38</v>
+      </c>
+      <c r="H117">
+        <v>6</v>
+      </c>
+      <c r="I117">
+        <v>14898</v>
+      </c>
+      <c r="J117">
+        <v>2232</v>
+      </c>
+      <c r="K117">
+        <v>158</v>
+      </c>
+      <c r="L117">
+        <v>2</v>
+      </c>
+      <c r="M117">
+        <v>113</v>
+      </c>
+      <c r="N117">
+        <v>17</v>
+      </c>
+      <c r="O117" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="P117" s="3">
+        <v>1.3425925925925925E-3</v>
+      </c>
+      <c r="Q117" s="4">
+        <v>0.14979999999999999</v>
+      </c>
+      <c r="R117" s="4">
+        <v>7.0800000000000002E-2</v>
+      </c>
+      <c r="S117" s="4">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="T117">
+        <v>43</v>
+      </c>
+      <c r="U117" s="4">
+        <v>0.27560000000000001</v>
+      </c>
+      <c r="V117" s="4">
+        <v>0.57530000000000003</v>
+      </c>
+      <c r="W117">
+        <v>120.804</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B118">
+        <v>11</v>
+      </c>
+      <c r="C118">
+        <v>168</v>
+      </c>
+      <c r="D118">
+        <v>169</v>
+      </c>
+      <c r="E118" t="s">
+        <v>23</v>
+      </c>
+      <c r="F118">
+        <v>50433</v>
+      </c>
+      <c r="G118">
+        <v>38</v>
+      </c>
+      <c r="H118">
+        <v>6</v>
+      </c>
+      <c r="I118">
+        <v>11997</v>
+      </c>
+      <c r="J118">
+        <v>2067</v>
+      </c>
+      <c r="K118">
+        <v>107</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <v>93</v>
+      </c>
+      <c r="N118">
+        <v>14</v>
+      </c>
+      <c r="O118" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="P118" s="3">
+        <v>1.238425925925926E-3</v>
+      </c>
+      <c r="Q118" s="4">
+        <v>0.17230000000000001</v>
+      </c>
+      <c r="R118" s="4">
+        <v>5.1799999999999999E-2</v>
+      </c>
+      <c r="S118" s="4">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="T118">
+        <v>13</v>
+      </c>
+      <c r="U118" s="4">
+        <v>0.1226</v>
+      </c>
+      <c r="V118" s="4">
+        <v>0.59289999999999998</v>
+      </c>
+      <c r="W118">
+        <v>102.37050000000001</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B119">
+        <v>12</v>
+      </c>
+      <c r="C119">
+        <v>166</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119" t="s">
+        <v>26</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119" t="s">
+        <v>24</v>
+      </c>
+      <c r="P119" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q119" s="5">
+        <v>0</v>
+      </c>
+      <c r="R119" t="s">
+        <v>25</v>
+      </c>
+      <c r="S119" t="s">
+        <v>25</v>
+      </c>
+      <c r="T119">
+        <v>0</v>
+      </c>
+      <c r="U119" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B120">
+        <v>12</v>
+      </c>
+      <c r="C120">
+        <v>168</v>
+      </c>
+      <c r="D120">
+        <v>169</v>
+      </c>
+      <c r="E120" t="s">
+        <v>23</v>
+      </c>
+      <c r="F120">
+        <v>50433</v>
+      </c>
+      <c r="G120">
+        <v>38</v>
+      </c>
+      <c r="H120">
+        <v>6</v>
+      </c>
+      <c r="I120">
+        <v>6933</v>
+      </c>
+      <c r="J120">
+        <v>1218</v>
+      </c>
+      <c r="K120">
+        <v>65</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <v>56</v>
+      </c>
+      <c r="N120">
+        <v>9</v>
+      </c>
+      <c r="O120" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="P120" s="3">
+        <v>9.9537037037037042E-4</v>
+      </c>
+      <c r="Q120" s="4">
+        <v>0.1757</v>
+      </c>
+      <c r="R120" s="4">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="S120" s="4">
+        <v>1.54E-2</v>
+      </c>
+      <c r="T120">
+        <v>8</v>
+      </c>
+      <c r="U120" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="V120" s="4">
+        <v>0.64710000000000001</v>
+      </c>
+      <c r="W120">
+        <v>57.734999999999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B121">
+        <v>13</v>
+      </c>
+      <c r="C121">
+        <v>168</v>
+      </c>
+      <c r="D121">
+        <v>169</v>
+      </c>
+      <c r="E121" t="s">
+        <v>23</v>
+      </c>
+      <c r="F121">
+        <v>50433</v>
+      </c>
+      <c r="G121">
+        <v>38</v>
+      </c>
+      <c r="H121">
+        <v>6</v>
+      </c>
+      <c r="I121">
+        <v>13029</v>
+      </c>
+      <c r="J121">
+        <v>1595</v>
+      </c>
+      <c r="K121">
+        <v>108</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>85</v>
+      </c>
+      <c r="N121">
+        <v>18</v>
+      </c>
+      <c r="O121" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="P121" s="3">
+        <v>1.0763888888888889E-3</v>
+      </c>
+      <c r="Q121" s="4">
+        <v>0.12239999999999999</v>
+      </c>
+      <c r="R121" s="4">
+        <v>6.7699999999999996E-2</v>
+      </c>
+      <c r="S121" s="5">
+        <v>0</v>
+      </c>
+      <c r="T121">
+        <v>23</v>
+      </c>
+      <c r="U121" s="4">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="V121" s="4">
+        <v>0.64490000000000003</v>
+      </c>
+      <c r="W121">
+        <v>89.689499999999995</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B122">
+        <v>14</v>
+      </c>
+      <c r="C122">
+        <v>168</v>
+      </c>
+      <c r="D122">
+        <v>169</v>
+      </c>
+      <c r="E122" t="s">
+        <v>23</v>
+      </c>
+      <c r="F122">
+        <v>50433</v>
+      </c>
+      <c r="G122">
+        <v>38</v>
+      </c>
+      <c r="H122">
+        <v>12</v>
+      </c>
+      <c r="I122">
+        <v>7175</v>
+      </c>
+      <c r="J122">
+        <v>1185</v>
+      </c>
+      <c r="K122">
+        <v>71</v>
+      </c>
+      <c r="L122">
+        <v>4</v>
+      </c>
+      <c r="M122">
+        <v>54</v>
+      </c>
+      <c r="N122">
+        <v>2</v>
+      </c>
+      <c r="O122" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="P122" s="3">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="Q122" s="4">
+        <v>0.16520000000000001</v>
+      </c>
+      <c r="R122" s="4">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="S122" s="4">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="T122">
+        <v>13</v>
+      </c>
+      <c r="U122" s="4">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="V122" s="4">
+        <v>0.746</v>
+      </c>
+      <c r="W122">
+        <v>55.642499999999998</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B123">
+        <v>15</v>
+      </c>
+      <c r="C123">
+        <v>166</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123" t="s">
+        <v>26</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123" t="s">
+        <v>24</v>
+      </c>
+      <c r="P123" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q123" s="5">
+        <v>0</v>
+      </c>
+      <c r="R123" t="s">
+        <v>25</v>
+      </c>
+      <c r="S123" t="s">
+        <v>25</v>
+      </c>
+      <c r="T123">
+        <v>0</v>
+      </c>
+      <c r="U123" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B124">
+        <v>15</v>
+      </c>
+      <c r="C124">
+        <v>168</v>
+      </c>
+      <c r="D124">
+        <v>169</v>
+      </c>
+      <c r="E124" t="s">
+        <v>23</v>
+      </c>
+      <c r="F124">
+        <v>50433</v>
+      </c>
+      <c r="G124">
+        <v>38</v>
+      </c>
+      <c r="H124">
+        <v>8</v>
+      </c>
+      <c r="I124">
+        <v>15028</v>
+      </c>
+      <c r="J124">
+        <v>1903</v>
+      </c>
+      <c r="K124">
+        <v>115</v>
+      </c>
+      <c r="L124">
+        <v>3</v>
+      </c>
+      <c r="M124">
+        <v>103</v>
+      </c>
+      <c r="N124">
+        <v>14</v>
+      </c>
+      <c r="O124" s="3">
+        <v>8.1018518518518516E-5</v>
+      </c>
+      <c r="P124" s="3">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="Q124" s="4">
+        <v>0.12659999999999999</v>
+      </c>
+      <c r="R124" s="4">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="S124" s="4">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="T124">
+        <v>9</v>
+      </c>
+      <c r="U124" s="4">
+        <v>8.0399999999999999E-2</v>
+      </c>
+      <c r="V124" s="4">
+        <v>0.67859999999999998</v>
+      </c>
+      <c r="W124">
+        <v>98.905500000000004</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B125">
+        <v>16</v>
+      </c>
+      <c r="C125">
+        <v>168</v>
+      </c>
+      <c r="D125">
+        <v>169</v>
+      </c>
+      <c r="E125" t="s">
+        <v>23</v>
+      </c>
+      <c r="F125">
+        <v>50433</v>
+      </c>
+      <c r="G125">
+        <v>38</v>
+      </c>
+      <c r="H125">
+        <v>8</v>
+      </c>
+      <c r="I125">
+        <v>16087</v>
+      </c>
+      <c r="J125">
+        <v>1596</v>
+      </c>
+      <c r="K125">
+        <v>92</v>
+      </c>
+      <c r="L125">
+        <v>2</v>
+      </c>
+      <c r="M125">
+        <v>83</v>
+      </c>
+      <c r="N125">
+        <v>8</v>
+      </c>
+      <c r="O125" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P125" s="3">
+        <v>1.2731481481481483E-3</v>
+      </c>
+      <c r="Q125" s="4">
+        <v>9.9199999999999997E-2</v>
+      </c>
+      <c r="R125" s="4">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="S125" s="4">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="T125">
+        <v>7</v>
+      </c>
+      <c r="U125" s="4">
+        <v>7.7799999999999994E-2</v>
+      </c>
+      <c r="V125" s="4">
+        <v>0.6804</v>
+      </c>
+      <c r="W125">
+        <v>94.724000000000004</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B126">
+        <v>17</v>
+      </c>
+      <c r="C126">
+        <v>168</v>
+      </c>
+      <c r="D126">
+        <v>169</v>
+      </c>
+      <c r="E126" t="s">
+        <v>23</v>
+      </c>
+      <c r="F126">
+        <v>50433</v>
+      </c>
+      <c r="G126">
+        <v>38</v>
+      </c>
+      <c r="H126">
+        <v>8</v>
+      </c>
+      <c r="I126">
+        <v>19186</v>
+      </c>
+      <c r="J126">
+        <v>1574</v>
+      </c>
+      <c r="K126">
+        <v>97</v>
+      </c>
+      <c r="L126">
+        <v>19</v>
+      </c>
+      <c r="M126">
+        <v>74</v>
+      </c>
+      <c r="N126">
+        <v>10</v>
+      </c>
+      <c r="O126" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="P126" s="3">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="Q126" s="4">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="R126" s="4">
+        <v>6.1600000000000002E-2</v>
+      </c>
+      <c r="S126" s="4">
+        <v>0.19589999999999999</v>
+      </c>
+      <c r="T126">
+        <v>4</v>
+      </c>
+      <c r="U126" s="4">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="V126" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="W126">
+        <v>84.043999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6B278F-AE4D-478F-898D-CF0ACBD9EFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D14A4C1-3F9A-48E7-9714-C89C36A5EF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="35">
   <si>
     <t>Data</t>
   </si>
@@ -134,6 +134,12 @@
   <si>
     <t>Locator_CPF_Template</t>
   </si>
+  <si>
+    <t>Acordo</t>
+  </si>
+  <si>
+    <t>TMA</t>
+  </si>
 </sst>
 </file>
 
@@ -191,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -200,7 +206,21 @@
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W126"/>
+  <dimension ref="A1:W127"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -9163,49 +9183,120 @@
         <v>8</v>
       </c>
       <c r="I126">
-        <v>19186</v>
+        <v>19399</v>
       </c>
       <c r="J126">
-        <v>1574</v>
+        <v>1593</v>
       </c>
       <c r="K126">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L126">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="M126">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N126">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O126" s="3">
         <v>1.3888888888888889E-4</v>
       </c>
       <c r="P126" s="3">
-        <v>1.3078703703703703E-3</v>
+        <v>1.3657407407407407E-3</v>
       </c>
       <c r="Q126" s="4">
-        <v>8.2000000000000003E-2</v>
+        <v>8.2100000000000006E-2</v>
       </c>
       <c r="R126" s="4">
-        <v>6.1600000000000002E-2</v>
+        <v>6.1499999999999999E-2</v>
       </c>
       <c r="S126" s="4">
-        <v>0.19589999999999999</v>
+        <v>3.0599999999999999E-2</v>
       </c>
       <c r="T126">
         <v>4</v>
       </c>
       <c r="U126" s="4">
-        <v>5.1299999999999998E-2</v>
+        <v>4.2099999999999999E-2</v>
       </c>
       <c r="V126" s="4">
-        <v>0.8</v>
+        <v>0.78949999999999998</v>
       </c>
       <c r="W126">
-        <v>84.043999999999997</v>
+        <v>85.218500000000006</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B127">
+        <v>18</v>
+      </c>
+      <c r="C127">
+        <v>168</v>
+      </c>
+      <c r="D127">
+        <v>169</v>
+      </c>
+      <c r="E127" t="s">
+        <v>23</v>
+      </c>
+      <c r="F127">
+        <v>50433</v>
+      </c>
+      <c r="G127">
+        <v>38</v>
+      </c>
+      <c r="H127">
+        <v>7</v>
+      </c>
+      <c r="I127">
+        <v>12375</v>
+      </c>
+      <c r="J127">
+        <v>1030</v>
+      </c>
+      <c r="K127">
+        <v>73</v>
+      </c>
+      <c r="L127">
+        <v>46</v>
+      </c>
+      <c r="M127">
+        <v>25</v>
+      </c>
+      <c r="N127">
+        <v>6</v>
+      </c>
+      <c r="O127" s="3">
+        <v>1.273148148148148E-4</v>
+      </c>
+      <c r="P127" s="3">
+        <v>1.4351851851851852E-3</v>
+      </c>
+      <c r="Q127" s="4">
+        <v>8.3199999999999996E-2</v>
+      </c>
+      <c r="R127" s="4">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="S127" s="4">
+        <v>0.63009999999999999</v>
+      </c>
+      <c r="T127">
+        <v>2</v>
+      </c>
+      <c r="U127" s="4">
+        <v>7.4099999999999999E-2</v>
+      </c>
+      <c r="V127" s="4">
+        <v>0.62070000000000003</v>
+      </c>
+      <c r="W127">
+        <v>51.031999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -9215,18 +9306,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FFF5342-4B63-4B01-A332-A226EA58A2DA}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="9.44140625" style="10" customWidth="1"/>
+    <col min="9" max="12" width="8.77734375" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -9236,35 +9322,35 @@
       <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="H1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="L1" t="s">
-        <v>15</v>
+      <c r="L1" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -9274,34 +9360,34 @@
       <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="6">
-        <v>130813</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="10">
+        <v>24715</v>
+      </c>
+      <c r="D2" s="10">
         <v>28</v>
       </c>
-      <c r="E2" s="6">
-        <v>80762</v>
-      </c>
-      <c r="F2" s="6">
-        <v>1085</v>
-      </c>
-      <c r="G2" s="6">
-        <v>229</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="E2" s="10">
+        <v>78309</v>
+      </c>
+      <c r="F2" s="10">
+        <v>2158</v>
+      </c>
+      <c r="G2" s="10">
+        <v>221</v>
+      </c>
+      <c r="H2" s="10">
         <v>74</v>
       </c>
-      <c r="I2" s="4">
-        <v>1.34E-2</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0.21110000000000001</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0.3231</v>
-      </c>
-      <c r="L2" s="3">
+      <c r="I2" s="7">
+        <v>2.76E-2</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0.1024</v>
+      </c>
+      <c r="K2" s="7">
+        <v>0.33479999999999999</v>
+      </c>
+      <c r="L2" s="8">
         <v>5.0925925925925921E-4</v>
       </c>
     </row>
@@ -9312,34 +9398,34 @@
       <c r="B3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="6">
-        <v>108263</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="10">
+        <v>23837</v>
+      </c>
+      <c r="D3" s="10">
         <v>30</v>
       </c>
-      <c r="E3" s="6">
-        <v>94611</v>
-      </c>
-      <c r="F3" s="6">
-        <v>1064</v>
-      </c>
-      <c r="G3" s="6">
-        <v>174</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="E3" s="10">
+        <v>92078</v>
+      </c>
+      <c r="F3" s="10">
+        <v>2306</v>
+      </c>
+      <c r="G3" s="10">
+        <v>199</v>
+      </c>
+      <c r="H3" s="10">
         <v>28</v>
       </c>
-      <c r="I3" s="4">
-        <v>1.12E-2</v>
-      </c>
-      <c r="J3" s="4">
-        <v>0.16350000000000001</v>
-      </c>
-      <c r="K3" s="4">
-        <v>0.16089999999999999</v>
-      </c>
-      <c r="L3" s="3">
+      <c r="I3" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J3" s="7">
+        <v>8.6300000000000002E-2</v>
+      </c>
+      <c r="K3" s="7">
+        <v>0.14069999999999999</v>
+      </c>
+      <c r="L3" s="8">
         <v>3.9351851851851852E-4</v>
       </c>
     </row>
@@ -9350,34 +9436,34 @@
       <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="6">
-        <v>194003</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="10">
+        <v>44041</v>
+      </c>
+      <c r="D4" s="10">
         <v>31</v>
       </c>
-      <c r="E4" s="6">
-        <v>73894</v>
-      </c>
-      <c r="F4" s="6">
-        <v>1205</v>
-      </c>
-      <c r="G4" s="6">
-        <v>190</v>
-      </c>
-      <c r="H4" s="6">
+      <c r="E4" s="10">
+        <v>71179</v>
+      </c>
+      <c r="F4" s="10">
+        <v>2463</v>
+      </c>
+      <c r="G4" s="10">
+        <v>186</v>
+      </c>
+      <c r="H4" s="10">
         <v>66</v>
       </c>
-      <c r="I4" s="4">
-        <v>1.6299999999999999E-2</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0.15770000000000001</v>
-      </c>
-      <c r="K4" s="4">
-        <v>0.34739999999999999</v>
-      </c>
-      <c r="L4" s="3">
+      <c r="I4" s="7">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="J4" s="7">
+        <v>7.5499999999999998E-2</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0.3548</v>
+      </c>
+      <c r="L4" s="8">
         <v>4.7453703703703704E-4</v>
       </c>
     </row>
@@ -9388,34 +9474,34 @@
       <c r="B5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="6">
-        <v>51583</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="10">
+        <v>45963</v>
+      </c>
+      <c r="D5" s="10">
         <v>9</v>
       </c>
-      <c r="E5" s="6">
-        <v>27615</v>
-      </c>
-      <c r="F5" s="6">
-        <v>352</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="E5" s="10">
+        <v>26814</v>
+      </c>
+      <c r="F5" s="10">
+        <v>719</v>
+      </c>
+      <c r="G5" s="10">
         <v>60</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="10">
         <v>22</v>
       </c>
-      <c r="I5" s="4">
-        <v>1.2699999999999999E-2</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0.17050000000000001</v>
-      </c>
-      <c r="K5" s="4">
+      <c r="I5" s="7">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="J5" s="7">
+        <v>8.3400000000000002E-2</v>
+      </c>
+      <c r="K5" s="7">
         <v>0.36670000000000003</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="8">
         <v>5.2083333333333333E-4</v>
       </c>
     </row>
@@ -9426,34 +9512,34 @@
       <c r="B6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="6">
-        <v>166160</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="10">
+        <v>60593</v>
+      </c>
+      <c r="D6" s="10">
         <v>28</v>
       </c>
-      <c r="E6" s="6">
-        <v>93099</v>
-      </c>
-      <c r="F6" s="6">
-        <v>744</v>
-      </c>
-      <c r="G6" s="6">
-        <v>139</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="E6" s="10">
+        <v>91384</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1526</v>
+      </c>
+      <c r="G6" s="10">
+        <v>140</v>
+      </c>
+      <c r="H6" s="10">
         <v>49</v>
       </c>
-      <c r="I6" s="4">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="J6" s="4">
-        <v>0.18679999999999999</v>
-      </c>
-      <c r="K6" s="4">
-        <v>0.35249999999999998</v>
-      </c>
-      <c r="L6" s="3">
+      <c r="I6" s="7">
+        <v>1.67E-2</v>
+      </c>
+      <c r="J6" s="7">
+        <v>9.1700000000000004E-2</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="L6" s="8">
         <v>5.3240740740740744E-4</v>
       </c>
     </row>
@@ -9464,34 +9550,34 @@
       <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="6">
-        <v>192383</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="10">
+        <v>39005</v>
+      </c>
+      <c r="D7" s="10">
         <v>2</v>
       </c>
-      <c r="E7" s="6">
-        <v>5440</v>
-      </c>
-      <c r="F7" s="6">
-        <v>71</v>
-      </c>
-      <c r="G7" s="6">
-        <v>11</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="E7" s="10">
+        <v>5342</v>
+      </c>
+      <c r="F7" s="10">
+        <v>87</v>
+      </c>
+      <c r="G7" s="10">
+        <v>9</v>
+      </c>
+      <c r="H7" s="10">
         <v>2</v>
       </c>
-      <c r="I7" s="4">
-        <v>1.3100000000000001E-2</v>
-      </c>
-      <c r="J7" s="4">
-        <v>0.15490000000000001</v>
-      </c>
-      <c r="K7" s="4">
-        <v>0.18179999999999999</v>
-      </c>
-      <c r="L7" s="3">
+      <c r="I7" s="7">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.10340000000000001</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="L7" s="8">
         <v>8.564814814814815E-4</v>
       </c>
     </row>
@@ -9502,34 +9588,34 @@
       <c r="B8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="6">
-        <v>192383</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="10">
+        <v>39005</v>
+      </c>
+      <c r="D8" s="10">
         <v>21</v>
       </c>
-      <c r="E8" s="6">
-        <v>74990</v>
-      </c>
-      <c r="F8" s="6">
-        <v>1043</v>
-      </c>
-      <c r="G8" s="6">
-        <v>177</v>
-      </c>
-      <c r="H8" s="6">
+      <c r="E8" s="10">
+        <v>72669</v>
+      </c>
+      <c r="F8" s="10">
+        <v>2083</v>
+      </c>
+      <c r="G8" s="10">
+        <v>183</v>
+      </c>
+      <c r="H8" s="10">
         <v>55</v>
       </c>
-      <c r="I8" s="4">
-        <v>1.3899999999999999E-2</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0.16969999999999999</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0.31069999999999998</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="I8" s="7">
+        <v>2.87E-2</v>
+      </c>
+      <c r="J8" s="7">
+        <v>8.7900000000000006E-2</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0.30049999999999999</v>
+      </c>
+      <c r="L8" s="8">
         <v>4.3981481481481481E-4</v>
       </c>
     </row>
@@ -9540,34 +9626,34 @@
       <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="6">
-        <v>192383</v>
-      </c>
-      <c r="D9">
+      <c r="C9" s="10">
+        <v>26876</v>
+      </c>
+      <c r="D9" s="10">
         <v>20</v>
       </c>
-      <c r="E9" s="6">
-        <v>65296</v>
-      </c>
-      <c r="F9" s="6">
-        <v>967</v>
-      </c>
-      <c r="G9" s="6">
-        <v>137</v>
-      </c>
-      <c r="H9" s="6">
+      <c r="E9" s="10">
+        <v>63128</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1983</v>
+      </c>
+      <c r="G9" s="10">
+        <v>143</v>
+      </c>
+      <c r="H9" s="10">
         <v>42</v>
       </c>
-      <c r="I9" s="4">
-        <v>1.4800000000000001E-2</v>
-      </c>
-      <c r="J9" s="4">
-        <v>0.14169999999999999</v>
-      </c>
-      <c r="K9" s="4">
-        <v>0.30659999999999998</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="I9" s="7">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="J9" s="7">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0.29370000000000002</v>
+      </c>
+      <c r="L9" s="8">
         <v>3.7037037037037035E-4</v>
       </c>
     </row>
@@ -9578,34 +9664,34 @@
       <c r="B10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="6">
-        <v>50059</v>
-      </c>
-      <c r="D10">
+      <c r="C10" s="10">
+        <v>3353</v>
+      </c>
+      <c r="D10" s="10">
         <v>21</v>
       </c>
-      <c r="E10" s="6">
-        <v>62106</v>
-      </c>
-      <c r="F10" s="6">
-        <v>899</v>
-      </c>
-      <c r="G10" s="6">
-        <v>183</v>
-      </c>
-      <c r="H10" s="6">
+      <c r="E10" s="10">
+        <v>59919</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1939</v>
+      </c>
+      <c r="G10" s="10">
+        <v>190</v>
+      </c>
+      <c r="H10" s="10">
         <v>58</v>
       </c>
-      <c r="I10" s="4">
-        <v>1.4500000000000001E-2</v>
-      </c>
-      <c r="J10" s="4">
-        <v>0.2036</v>
-      </c>
-      <c r="K10" s="4">
-        <v>0.31690000000000002</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="I10" s="7">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="J10" s="7">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0.30530000000000002</v>
+      </c>
+      <c r="L10" s="8">
         <v>4.6296296296296298E-4</v>
       </c>
     </row>
@@ -9616,34 +9702,34 @@
       <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11">
-        <v>48299</v>
-      </c>
-      <c r="D11">
+      <c r="C11" s="10">
+        <v>5275</v>
+      </c>
+      <c r="D11" s="10">
         <v>25</v>
       </c>
-      <c r="E11">
-        <v>76114</v>
-      </c>
-      <c r="F11">
-        <v>1010</v>
-      </c>
-      <c r="G11">
-        <v>204</v>
-      </c>
-      <c r="H11" s="6">
+      <c r="E11" s="10">
+        <v>73793</v>
+      </c>
+      <c r="F11" s="10">
+        <v>2062</v>
+      </c>
+      <c r="G11" s="10">
+        <v>202</v>
+      </c>
+      <c r="H11" s="10">
         <v>57</v>
       </c>
-      <c r="I11" s="4">
-        <v>1.3299999999999999E-2</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0.20200000000000001</v>
-      </c>
-      <c r="K11" s="4">
-        <v>0.27939999999999998</v>
-      </c>
-      <c r="L11" s="3">
+      <c r="I11" s="7">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="J11" s="7">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="K11" s="7">
+        <v>0.28220000000000001</v>
+      </c>
+      <c r="L11" s="8">
         <v>4.7453703703703704E-4</v>
       </c>
     </row>
@@ -9654,34 +9740,34 @@
       <c r="B12" t="s">
         <v>31</v>
       </c>
-      <c r="C12">
-        <v>58756</v>
-      </c>
-      <c r="D12">
+      <c r="C12" s="10">
+        <v>21410</v>
+      </c>
+      <c r="D12" s="10">
         <v>26</v>
       </c>
-      <c r="E12">
-        <v>115201</v>
-      </c>
-      <c r="F12">
-        <v>1162</v>
-      </c>
-      <c r="G12">
-        <v>277</v>
-      </c>
-      <c r="H12" s="6">
+      <c r="E12" s="10">
+        <v>112419</v>
+      </c>
+      <c r="F12" s="10">
+        <v>2432</v>
+      </c>
+      <c r="G12" s="10">
+        <v>271</v>
+      </c>
+      <c r="H12" s="10">
         <v>79</v>
       </c>
-      <c r="I12" s="4">
-        <v>1.01E-2</v>
-      </c>
-      <c r="J12" s="4">
-        <v>0.2384</v>
-      </c>
-      <c r="K12" s="4">
-        <v>0.28520000000000001</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="I12" s="7">
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.1114</v>
+      </c>
+      <c r="K12" s="7">
+        <v>0.29149999999999998</v>
+      </c>
+      <c r="L12" s="8">
         <v>4.7453703703703704E-4</v>
       </c>
     </row>
@@ -9692,35 +9778,73 @@
       <c r="B13" t="s">
         <v>31</v>
       </c>
-      <c r="C13">
-        <v>41876</v>
-      </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
-      <c r="E13">
-        <v>16800</v>
-      </c>
-      <c r="F13">
-        <v>184</v>
-      </c>
-      <c r="G13">
-        <v>42</v>
-      </c>
-      <c r="H13" s="6">
-        <v>10</v>
-      </c>
-      <c r="I13" s="4">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0.2283</v>
-      </c>
-      <c r="K13" s="4">
-        <v>0.23810000000000001</v>
-      </c>
-      <c r="L13" s="3">
-        <v>4.2824074074074075E-4</v>
+      <c r="C13" s="10">
+        <v>22626</v>
+      </c>
+      <c r="D13" s="10">
+        <v>25</v>
+      </c>
+      <c r="E13" s="10">
+        <v>120096</v>
+      </c>
+      <c r="F13" s="10">
+        <v>2264</v>
+      </c>
+      <c r="G13" s="10">
+        <v>215</v>
+      </c>
+      <c r="H13" s="10">
+        <v>54</v>
+      </c>
+      <c r="I13" s="7">
+        <v>1.89E-2</v>
+      </c>
+      <c r="J13" s="7">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="K13" s="7">
+        <v>0.25119999999999998</v>
+      </c>
+      <c r="L13" s="8">
+        <v>4.1666666666666669E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="10">
+        <v>101542</v>
+      </c>
+      <c r="D14" s="10">
+        <v>23</v>
+      </c>
+      <c r="E14" s="10">
+        <v>51597</v>
+      </c>
+      <c r="F14" s="10">
+        <v>1001</v>
+      </c>
+      <c r="G14" s="10">
+        <v>100</v>
+      </c>
+      <c r="H14" s="10">
+        <v>21</v>
+      </c>
+      <c r="I14" s="7">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="J14" s="7">
+        <v>9.9900000000000003E-2</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="L14" s="8">
+        <v>4.1666666666666669E-4</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D14A4C1-3F9A-48E7-9714-C89C36A5EF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AE1C8B-BA15-41E8-A2D9-1CFA1FEDA91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="35">
   <si>
     <t>Data</t>
   </si>
@@ -525,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W127"/>
+  <dimension ref="A1:W129"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -9254,49 +9254,191 @@
         <v>7</v>
       </c>
       <c r="I127">
-        <v>12375</v>
+        <v>12535</v>
       </c>
       <c r="J127">
-        <v>1030</v>
+        <v>1039</v>
       </c>
       <c r="K127">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L127">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="M127">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N127">
+        <v>7</v>
+      </c>
+      <c r="O127" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+      <c r="P127" s="3">
+        <v>1.6319444444444445E-3</v>
+      </c>
+      <c r="Q127" s="4">
+        <v>8.2900000000000001E-2</v>
+      </c>
+      <c r="R127" s="4">
+        <v>7.4099999999999999E-2</v>
+      </c>
+      <c r="S127" s="4">
+        <v>5.1900000000000002E-2</v>
+      </c>
+      <c r="T127">
+        <v>12</v>
+      </c>
+      <c r="U127" s="4">
+        <v>0.16439999999999999</v>
+      </c>
+      <c r="V127" s="4">
+        <v>0.55879999999999996</v>
+      </c>
+      <c r="W127">
+        <v>52.836500000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B128">
+        <v>19</v>
+      </c>
+      <c r="C128">
+        <v>168</v>
+      </c>
+      <c r="D128">
+        <v>169</v>
+      </c>
+      <c r="E128" t="s">
+        <v>23</v>
+      </c>
+      <c r="F128">
+        <v>50433</v>
+      </c>
+      <c r="G128">
+        <v>38</v>
+      </c>
+      <c r="H128">
+        <v>7</v>
+      </c>
+      <c r="I128">
+        <v>13388</v>
+      </c>
+      <c r="J128">
+        <v>1159</v>
+      </c>
+      <c r="K128">
+        <v>77</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>69</v>
+      </c>
+      <c r="N128">
         <v>6</v>
       </c>
-      <c r="O127" s="3">
+      <c r="O128" s="3">
         <v>1.273148148148148E-4</v>
       </c>
-      <c r="P127" s="3">
-        <v>1.4351851851851852E-3</v>
-      </c>
-      <c r="Q127" s="4">
-        <v>8.3199999999999996E-2</v>
-      </c>
-      <c r="R127" s="4">
-        <v>7.0900000000000005E-2</v>
-      </c>
-      <c r="S127" s="4">
-        <v>0.63009999999999999</v>
-      </c>
-      <c r="T127">
-        <v>2</v>
-      </c>
-      <c r="U127" s="4">
-        <v>7.4099999999999999E-2</v>
-      </c>
-      <c r="V127" s="4">
-        <v>0.62070000000000003</v>
-      </c>
-      <c r="W127">
-        <v>51.031999999999996</v>
+      <c r="P128" s="3">
+        <v>1.2962962962962963E-3</v>
+      </c>
+      <c r="Q128" s="4">
+        <v>8.6599999999999996E-2</v>
+      </c>
+      <c r="R128" s="4">
+        <v>6.6400000000000001E-2</v>
+      </c>
+      <c r="S128" s="5">
+        <v>0</v>
+      </c>
+      <c r="T128">
+        <v>8</v>
+      </c>
+      <c r="U128" s="4">
+        <v>0.10390000000000001</v>
+      </c>
+      <c r="V128" s="4">
+        <v>0.8125</v>
+      </c>
+      <c r="W128">
+        <v>70.966999999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B129">
+        <v>20</v>
+      </c>
+      <c r="C129">
+        <v>168</v>
+      </c>
+      <c r="D129">
+        <v>169</v>
+      </c>
+      <c r="E129" t="s">
+        <v>23</v>
+      </c>
+      <c r="F129">
+        <v>50433</v>
+      </c>
+      <c r="G129">
+        <v>38</v>
+      </c>
+      <c r="H129">
+        <v>4</v>
+      </c>
+      <c r="I129">
+        <v>8198</v>
+      </c>
+      <c r="J129">
+        <v>848</v>
+      </c>
+      <c r="K129">
+        <v>48</v>
+      </c>
+      <c r="L129">
+        <v>30</v>
+      </c>
+      <c r="M129">
+        <v>14</v>
+      </c>
+      <c r="N129">
+        <v>1</v>
+      </c>
+      <c r="O129" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P129" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="Q129" s="4">
+        <v>0.10340000000000001</v>
+      </c>
+      <c r="R129" s="4">
+        <v>5.6599999999999998E-2</v>
+      </c>
+      <c r="S129" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="T129">
+        <v>4</v>
+      </c>
+      <c r="U129" s="4">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="V129" s="4">
+        <v>0.72729999999999995</v>
+      </c>
+      <c r="W129">
+        <v>39.487499999999997</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AE1C8B-BA15-41E8-A2D9-1CFA1FEDA91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3916419-790D-42C4-842F-4C8E699C64DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A7AE6A-CB83-47C1-80FD-20F4596FFD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4A7D76-AF1B-4983-B794-C6166F877244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12928,7 +12928,7 @@
         <v>36</v>
       </c>
       <c r="K179">
-        <v>1307</v>
+        <v>6</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -12949,16 +12949,16 @@
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="R179" s="4">
-        <v>36.299999999999997</v>
+        <v>0.16669999999999999</v>
       </c>
       <c r="S179" s="5">
         <v>0</v>
       </c>
       <c r="T179">
-        <v>1301</v>
+        <v>0</v>
       </c>
       <c r="U179" s="4">
-        <v>0.99539999999999995</v>
+        <v>0</v>
       </c>
       <c r="V179" s="4">
         <v>1</v>
@@ -12999,7 +12999,7 @@
         <v>318</v>
       </c>
       <c r="K180">
-        <v>10854</v>
+        <v>44</v>
       </c>
       <c r="L180">
         <v>0</v>
@@ -13020,16 +13020,16 @@
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="R180" s="4">
-        <v>34.130000000000003</v>
+        <v>0.1384</v>
       </c>
       <c r="S180" s="5">
         <v>0</v>
       </c>
       <c r="T180">
-        <v>10810</v>
+        <v>0</v>
       </c>
       <c r="U180" s="4">
-        <v>0.99590000000000001</v>
+        <v>0</v>
       </c>
       <c r="V180" s="4">
         <v>1</v>
@@ -13070,7 +13070,7 @@
         <v>310</v>
       </c>
       <c r="K181">
-        <v>7205</v>
+        <v>50</v>
       </c>
       <c r="L181">
         <v>1</v>
@@ -13091,16 +13091,16 @@
         <v>3.0999999999999999E-3</v>
       </c>
       <c r="R181" s="4">
-        <v>23.24</v>
+        <v>0.1613</v>
       </c>
       <c r="S181" s="4">
-        <v>1E-4</v>
+        <v>0.02</v>
       </c>
       <c r="T181">
-        <v>7158</v>
+        <v>3</v>
       </c>
       <c r="U181" s="4">
-        <v>0.99360000000000004</v>
+        <v>6.1199999999999997E-2</v>
       </c>
       <c r="V181" s="4">
         <v>0.86960000000000004</v>
@@ -13141,7 +13141,7 @@
         <v>243</v>
       </c>
       <c r="K182">
-        <v>8951</v>
+        <v>31</v>
       </c>
       <c r="L182">
         <v>0</v>
@@ -13162,16 +13162,16 @@
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="R182" s="4">
-        <v>36.83</v>
+        <v>0.12759999999999999</v>
       </c>
       <c r="S182" s="5">
         <v>0</v>
       </c>
       <c r="T182">
-        <v>8926</v>
+        <v>6</v>
       </c>
       <c r="U182" s="4">
-        <v>0.99719999999999998</v>
+        <v>0.19350000000000001</v>
       </c>
       <c r="V182" s="4">
         <v>0.73529999999999995</v>
@@ -13212,7 +13212,7 @@
         <v>294</v>
       </c>
       <c r="K183">
-        <v>6989</v>
+        <v>40</v>
       </c>
       <c r="L183">
         <v>0</v>
@@ -13233,16 +13233,16 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="R183" s="4">
-        <v>23.77</v>
+        <v>0.1361</v>
       </c>
       <c r="S183" s="5">
         <v>0</v>
       </c>
       <c r="T183">
-        <v>6955</v>
+        <v>6</v>
       </c>
       <c r="U183" s="4">
-        <v>0.99509999999999998</v>
+        <v>0.15</v>
       </c>
       <c r="V183" s="4">
         <v>0.8</v>
@@ -13283,7 +13283,7 @@
         <v>123</v>
       </c>
       <c r="K184">
-        <v>5991</v>
+        <v>15</v>
       </c>
       <c r="L184">
         <v>0</v>
@@ -13304,16 +13304,16 @@
         <v>1.9E-3</v>
       </c>
       <c r="R184" s="4">
-        <v>48.7</v>
+        <v>0.122</v>
       </c>
       <c r="S184" s="5">
         <v>0</v>
       </c>
       <c r="T184">
-        <v>5976</v>
+        <v>0</v>
       </c>
       <c r="U184" s="4">
-        <v>0.99750000000000005</v>
+        <v>0</v>
       </c>
       <c r="V184" s="4">
         <v>0.93330000000000002</v>

--- a/data/base_link.xlsx
+++ b/data/base_link.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4A7D76-AF1B-4983-B794-C6166F877244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A955B1E-C628-4C5B-A65D-12D69473E376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
